--- a/registry.xlsx.xlsx
+++ b/registry.xlsx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\szamyatin\Desktop\Реестр\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2204CEFB-E5F3-41ED-8738-7FE74A5220E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F16DA1D-E666-4380-A9F6-9D49AD960423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="960" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="📊 Дашборд" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="217">
   <si>
     <t>РЕЕСТР ЗАДАЧ АВТОМАТИЗАЦИИ СЦ СОЛВО 2026</t>
   </si>
@@ -255,9 +255,6 @@
     <t>Средний</t>
   </si>
   <si>
-    <t>3323631</t>
-  </si>
-  <si>
     <t>Некорректный вес в ген. Акте из-за дублирования веса тары</t>
   </si>
   <si>
@@ -357,9 +354,6 @@
     <t>ЖД импорт: ДО1, ДО2, ком. акт, растарки</t>
   </si>
   <si>
-    <t>4SC-RQ-CR-987 #4073944</t>
-  </si>
-  <si>
     <t>Прием импорта на авто</t>
   </si>
   <si>
@@ -369,9 +363,6 @@
     <t>ОФОРМЛЕНИЕ ЭКСПОРТНЫХ ГРУЗОВ</t>
   </si>
   <si>
-    <t>4SC-1-RQ-CR-409 #2489904</t>
-  </si>
-  <si>
     <t>Fill-Bill приемка ПнП через ЛКК</t>
   </si>
   <si>
@@ -405,9 +396,6 @@
     <t>Реализация в ЛКК КТСП функционала по оформлению возврата контейнера</t>
   </si>
   <si>
-    <t>4SC-1-RQ-CR-794 #3307597</t>
-  </si>
-  <si>
     <t>Оформление заявки на смену владельца</t>
   </si>
   <si>
@@ -510,9 +498,6 @@
     <t>Связана с задачей «Услуги контейнерного сервиса»</t>
   </si>
   <si>
-    <t>4SC-RQ-CR-902 #3782828</t>
-  </si>
-  <si>
     <t>Генерация номера заявки на услуги</t>
   </si>
   <si>
@@ -540,9 +525,6 @@
     <t>2027</t>
   </si>
   <si>
-    <t>4SC-RQ-CR-812 №3333318</t>
-  </si>
-  <si>
     <t>Функционал удаления АВ на WEB портале</t>
   </si>
   <si>
@@ -582,9 +564,6 @@
     <t>ОПЭ (нояб. 2026)</t>
   </si>
   <si>
-    <t>4SC-RQ-CR-951 #3940390</t>
-  </si>
-  <si>
     <t>План ж.д. работ (Excel)</t>
   </si>
   <si>
@@ -600,9 +579,6 @@
     <t>Автоматическое создание АОФ после внесения повреждений тальманом</t>
   </si>
   <si>
-    <t>4SC-RQ-CR-933 #3895614</t>
-  </si>
-  <si>
     <t>Фиксация годности/брака платформ в СОЛВО</t>
   </si>
   <si>
@@ -706,6 +682,27 @@
   </si>
   <si>
     <t>Кол-во задач</t>
+  </si>
+  <si>
+    <t>4SC-RQ-CR-859 #3985850</t>
+  </si>
+  <si>
+    <t>4SC-1-RQ-CR-794 #3307598</t>
+  </si>
+  <si>
+    <t>4SC-RQ-CR-902 #3782827</t>
+  </si>
+  <si>
+    <t>4SC-RQ-CR-812 #3333318</t>
+  </si>
+  <si>
+    <t>Н/Д</t>
+  </si>
+  <si>
+    <t>#3895614</t>
+  </si>
+  <si>
+    <t>Выставлено</t>
   </si>
 </sst>
 </file>
@@ -1208,7 +1205,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="0"/>
         <bgColor rgb="FFF8FAFC"/>
       </patternFill>
     </fill>
@@ -1434,9 +1431,6 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1606,33 +1600,6 @@
     <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="10" fillId="19" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1646,6 +1613,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="34" fillId="10" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1705,13 +1681,34 @@
     <xf numFmtId="0" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1719,77 +1716,7 @@
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Финансовый" xfId="1" builtinId="3"/>
   </cellStyles>
-  <dxfs count="87">
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="82">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2425,6 +2352,26 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -2688,7 +2635,7 @@
   <sheetPr>
     <tabColor rgb="FF2563EB"/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="77.77734375" bestFit="1" customWidth="1"/>
@@ -2702,17 +2649,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="112" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="120"/>
-      <c r="C1" s="120"/>
-      <c r="D1" s="120"/>
-      <c r="E1" s="120"/>
-      <c r="F1" s="120"/>
-      <c r="G1" s="120"/>
-      <c r="H1" s="120"/>
-      <c r="I1" s="120"/>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
+      <c r="I1" s="113"/>
     </row>
     <row r="2" spans="1:9" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="22"/>
@@ -2763,19 +2710,19 @@
       </c>
       <c r="B5" s="30">
         <f>'Судовые документы'!B4+'Таможенные документы'!B4+'Экспортные грузы'!B4+Терминал!B4+'ЖД грузы'!B4</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" s="31">
         <f>'Судовые документы'!C4+'Таможенные документы'!C4+'Экспортные грузы'!C4+Терминал!C4+'ЖД грузы'!C4</f>
         <v>7</v>
       </c>
-      <c r="D5" s="101">
+      <c r="D5" s="100">
         <f>'Судовые документы'!D4+'Таможенные документы'!D4+'Экспортные грузы'!D4+Терминал!D4+'ЖД грузы'!D4</f>
-        <v>6385</v>
+        <v>3231</v>
       </c>
       <c r="E5" s="32">
         <f>IF(('Судовые документы'!A4+'Таможенные документы'!A4+'Экспортные грузы'!A4+Терминал!A4+'ЖД грузы'!A4)=0,0,('Судовые документы'!B4+'Таможенные документы'!B4+'Экспортные грузы'!B4+Терминал!B4+'ЖД грузы'!B4)/('Судовые документы'!A4+'Таможенные документы'!A4+'Экспортные грузы'!A4+Терминал!A4+'ЖД грузы'!A4))</f>
-        <v>0.34883720930232559</v>
+        <v>0.32558139534883723</v>
       </c>
       <c r="G5" s="23"/>
       <c r="H5" s="23"/>
@@ -2827,19 +2774,19 @@
       </c>
       <c r="C8" s="34">
         <f>'Судовые документы'!B4</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" s="34">
         <f>'Судовые документы'!C4</f>
         <v>3</v>
       </c>
-      <c r="E8" s="140">
+      <c r="E8" s="109">
         <f>'Судовые документы'!D4</f>
-        <v>553</v>
+        <v>513</v>
       </c>
       <c r="F8" s="35">
         <f>IF('Судовые документы'!A4=0,0,'Судовые документы'!B4/'Судовые документы'!A4)</f>
-        <v>0.42857142857142855</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="H8" s="23"/>
       <c r="I8" s="23"/>
@@ -2860,9 +2807,9 @@
         <f>'Таможенные документы'!C4</f>
         <v>0</v>
       </c>
-      <c r="E9" s="141">
+      <c r="E9" s="110">
         <f>'Таможенные документы'!D4</f>
-        <v>2400</v>
+        <v>780</v>
       </c>
       <c r="F9" s="38">
         <f>IF('Таможенные документы'!A4=0,0,'Таможенные документы'!B4/'Таможенные документы'!A4)</f>
@@ -2887,9 +2834,9 @@
         <f>'Экспортные грузы'!C4</f>
         <v>1</v>
       </c>
-      <c r="E10" s="140">
+      <c r="E10" s="109">
         <f>'Экспортные грузы'!D4</f>
-        <v>1012</v>
+        <v>532</v>
       </c>
       <c r="F10" s="35">
         <f>IF('Экспортные грузы'!A4=0,0,'Экспортные грузы'!B4/'Экспортные грузы'!A4)</f>
@@ -2914,9 +2861,9 @@
         <f>Терминал!C4</f>
         <v>2</v>
       </c>
-      <c r="E11" s="141">
+      <c r="E11" s="110">
         <f>Терминал!D4</f>
-        <v>1141</v>
+        <v>1231</v>
       </c>
       <c r="F11" s="38">
         <f>IF(Терминал!A4=0,0,Терминал!B4/Терминал!A4)</f>
@@ -2941,9 +2888,9 @@
         <f>'ЖД грузы'!C4</f>
         <v>1</v>
       </c>
-      <c r="E12" s="140">
+      <c r="E12" s="109">
         <f>'ЖД грузы'!D4</f>
-        <v>1279</v>
+        <v>175</v>
       </c>
       <c r="F12" s="35">
         <f>IF('ЖД грузы'!A4=0,0,'ЖД грузы'!B4/'ЖД грузы'!A4)</f>
@@ -2962,19 +2909,19 @@
       </c>
       <c r="C13" s="39">
         <f>SUM(C8:C12)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D13" s="39">
         <f>SUM(D8:D12)</f>
         <v>7</v>
       </c>
-      <c r="E13" s="142">
+      <c r="E13" s="111">
         <f>SUM(E8:E12)</f>
-        <v>6385</v>
+        <v>3231</v>
       </c>
       <c r="F13" s="40">
         <f>IF(B13=0,0,C13/B13)</f>
-        <v>0.34883720930232559</v>
+        <v>0.32558139534883723</v>
       </c>
       <c r="H13" s="23"/>
       <c r="I13" s="23"/>
@@ -2991,17 +2938,17 @@
       <c r="I14" s="23"/>
     </row>
     <row r="15" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="121" t="s">
+      <c r="A15" s="114" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="122"/>
-      <c r="C15" s="122"/>
+      <c r="B15" s="115"/>
+      <c r="C15" s="115"/>
       <c r="D15" s="23"/>
-      <c r="E15" s="121" t="s">
+      <c r="E15" s="114" t="s">
         <v>37</v>
       </c>
-      <c r="F15" s="122"/>
-      <c r="G15" s="122"/>
+      <c r="F15" s="115"/>
+      <c r="G15" s="115"/>
       <c r="H15" s="23"/>
       <c r="I15" s="23"/>
     </row>
@@ -3018,20 +2965,20 @@
         <v>0.27906976744186046</v>
       </c>
       <c r="D16" s="23"/>
-      <c r="E16" s="93" t="s">
+      <c r="E16" s="92" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="93" t="s">
-        <v>217</v>
-      </c>
-      <c r="G16" s="93" t="s">
+      <c r="F16" s="92" t="s">
+        <v>209</v>
+      </c>
+      <c r="G16" s="92" t="s">
         <v>10</v>
       </c>
       <c r="H16" s="23"/>
       <c r="I16" s="23"/>
     </row>
     <row r="17" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="46" t="s">
+      <c r="A17" s="45" t="s">
         <v>40</v>
       </c>
       <c r="B17" s="42">
@@ -3050,7 +2997,7 @@
         <f>COUNTIF('Судовые документы'!H6:H12,"7.4.4")+COUNTIF('Таможенные документы'!H6:H10,"7.4.4")+COUNTIF('Экспортные грузы'!H6:H10,"7.4.4")+COUNTIF(Терминал!H6:H21,"7.4.4")+COUNTIF('ЖД грузы'!H6:H15,"7.4.4")</f>
         <v>1</v>
       </c>
-      <c r="G17" s="104">
+      <c r="G17" s="103">
         <f>SUMIF('Судовые документы'!H6:H12,"7.4.4",'Судовые документы'!I6:I12)+SUMIF('Таможенные документы'!H6:H10,"7.4.4",'Таможенные документы'!I6:I10)+SUMIF('Экспортные грузы'!H6:H10,"7.4.4",'Экспортные грузы'!I6:I10)+SUMIF(Терминал!H6:H21,"7.4.4",Терминал!I6:I21)+SUMIF('ЖД грузы'!H6:H15,"7.4.4",'ЖД грузы'!I6:I15)</f>
         <v>780</v>
       </c>
@@ -3058,7 +3005,7 @@
       <c r="I17" s="23"/>
     </row>
     <row r="18" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="47" t="s">
+      <c r="A18" s="46" t="s">
         <v>42</v>
       </c>
       <c r="B18" s="42">
@@ -3077,15 +3024,15 @@
         <f>COUNTIF('Судовые документы'!H6:H12,"7.4.5")+COUNTIF('Таможенные документы'!H6:H10,"7.4.5")+COUNTIF('Экспортные грузы'!H6:H10,"7.4.5")+COUNTIF(Терминал!H6:H21,"7.4.5")+COUNTIF('ЖД грузы'!H6:H15,"7.4.5")</f>
         <v>2</v>
       </c>
-      <c r="G18" s="104">
+      <c r="G18" s="103">
         <f>SUMIF('Судовые документы'!H6:H12,"7.4.5",'Судовые документы'!I6:I12)+SUMIF('Таможенные документы'!H6:H10,"7.4.5",'Таможенные документы'!I6:I10)+SUMIF('Экспортные грузы'!H6:H10,"7.4.5",'Экспортные грузы'!I6:I10)+SUMIF(Терминал!H6:H21,"7.4.5",Терминал!I6:I21)+SUMIF('ЖД грузы'!H6:H15,"7.4.5",'ЖД грузы'!I6:I15)</f>
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="H18" s="23"/>
       <c r="I18" s="23"/>
     </row>
     <row r="19" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="48" t="s">
+      <c r="A19" s="47" t="s">
         <v>29</v>
       </c>
       <c r="B19" s="42">
@@ -3102,17 +3049,17 @@
       </c>
       <c r="F19" s="42">
         <f>COUNTIF('Судовые документы'!H6:H12,"7.4.7")+COUNTIF('Таможенные документы'!H6:H10,"7.4.7")+COUNTIF('Экспортные грузы'!H6:H10,"7.4.7")+COUNTIF(Терминал!H6:H21,"7.4.7")+COUNTIF('ЖД грузы'!H6:H15,"7.4.7")</f>
-        <v>2</v>
-      </c>
-      <c r="G19" s="104">
+        <v>3</v>
+      </c>
+      <c r="G19" s="103">
         <f>SUMIF('Судовые документы'!H6:H12,"7.4.7",'Судовые документы'!I6:I12)+SUMIF('Таможенные документы'!H6:H10,"7.4.7",'Таможенные документы'!I6:I10)+SUMIF('Экспортные грузы'!H6:H10,"7.4.7",'Экспортные грузы'!I6:I10)+SUMIF(Терминал!H6:H21,"7.4.7",Терминал!I6:I21)+SUMIF('ЖД грузы'!H6:H15,"7.4.7",'ЖД грузы'!I6:I15)</f>
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="H19" s="23"/>
       <c r="I19" s="23"/>
     </row>
     <row r="20" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="48" t="s">
+      <c r="A20" s="47" t="s">
         <v>45</v>
       </c>
       <c r="B20" s="42">
@@ -3131,15 +3078,15 @@
         <f>COUNTIF('Судовые документы'!H6:H12,"7.4.8")+COUNTIF('Таможенные документы'!H6:H10,"7.4.8")+COUNTIF('Экспортные грузы'!H6:H10,"7.4.8")+COUNTIF(Терминал!H6:H21,"7.4.8")+COUNTIF('ЖД грузы'!H6:H15,"7.4.8")</f>
         <v>4</v>
       </c>
-      <c r="G20" s="104">
+      <c r="G20" s="103">
         <f>SUMIF('Судовые документы'!H6:H12,"7.4.8",'Судовые документы'!I6:I12)+SUMIF('Таможенные документы'!H6:H10,"7.4.8",'Таможенные документы'!I6:I10)+SUMIF('Экспортные грузы'!H6:H10,"7.4.8",'Экспортные грузы'!I6:I10)+SUMIF(Терминал!H6:H21,"7.4.8",Терминал!I6:I21)+SUMIF('ЖД грузы'!H6:H15,"7.4.8",'ЖД грузы'!I6:I15)</f>
-        <v>144</v>
+        <v>214</v>
       </c>
       <c r="H20" s="23"/>
       <c r="I20" s="23"/>
     </row>
     <row r="21" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="49" t="s">
+      <c r="A21" s="48" t="s">
         <v>47</v>
       </c>
       <c r="B21" s="42">
@@ -3158,7 +3105,7 @@
         <f>COUNTIF('Судовые документы'!H6:H12,"7.4.9")+COUNTIF('Таможенные документы'!H6:H10,"7.4.9")+COUNTIF('Экспортные грузы'!H6:H10,"7.4.9")+COUNTIF(Терминал!H6:H21,"7.4.9")+COUNTIF('ЖД грузы'!H6:H15,"7.4.9")</f>
         <v>4</v>
       </c>
-      <c r="G21" s="104">
+      <c r="G21" s="103">
         <f>SUMIF('Судовые документы'!H6:H12,"7.4.9",'Судовые документы'!I6:I12)+SUMIF('Таможенные документы'!H6:H10,"7.4.9",'Таможенные документы'!I6:I10)+SUMIF('Экспортные грузы'!H6:H10,"7.4.9",'Экспортные грузы'!I6:I10)+SUMIF(Терминал!H6:H21,"7.4.9",Терминал!I6:I21)+SUMIF('ЖД грузы'!H6:H15,"7.4.9",'ЖД грузы'!I6:I15)</f>
         <v>441</v>
       </c>
@@ -3166,7 +3113,7 @@
       <c r="I21" s="23"/>
     </row>
     <row r="22" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="50" t="s">
+      <c r="A22" s="49" t="s">
         <v>49</v>
       </c>
       <c r="B22" s="42">
@@ -3185,15 +3132,15 @@
         <f>COUNTIF('Судовые документы'!H6:H12,"7.4.10")+COUNTIF('Таможенные документы'!H6:H10,"7.4.10")+COUNTIF('Экспортные грузы'!H6:H10,"7.4.10")+COUNTIF(Терминал!H6:H21,"7.4.10")+COUNTIF('ЖД грузы'!H6:H15,"7.4.10")</f>
         <v>8</v>
       </c>
-      <c r="G22" s="104">
+      <c r="G22" s="103">
         <f>SUMIF('Судовые документы'!H6:H12,"7.4.10",'Судовые документы'!I6:I12)+SUMIF('Таможенные документы'!H6:H10,"7.4.10",'Таможенные документы'!I6:I10)+SUMIF('Экспортные грузы'!H6:H10,"7.4.10",'Экспортные грузы'!I6:I10)+SUMIF(Терминал!H6:H21,"7.4.10",Терминал!I6:I21)+SUMIF('ЖД грузы'!H6:H15,"7.4.10",'ЖД грузы'!I6:I15)</f>
-        <v>1180</v>
+        <v>892</v>
       </c>
       <c r="H22" s="23"/>
       <c r="I22" s="23"/>
     </row>
     <row r="23" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="51" t="s">
+      <c r="A23" s="50" t="s">
         <v>51</v>
       </c>
       <c r="B23" s="42">
@@ -3210,17 +3157,17 @@
       </c>
       <c r="F23" s="42">
         <f>COUNTIF('Судовые документы'!H6:H12,"7.4.10/1")+COUNTIF('Таможенные документы'!H6:H10,"7.4.10/1")+COUNTIF('Экспортные грузы'!H6:H10,"7.4.10/1")+COUNTIF(Терминал!H6:H21,"7.4.10/1")+COUNTIF('ЖД грузы'!H6:H15,"7.4.10/1")</f>
-        <v>1</v>
-      </c>
-      <c r="G23" s="104">
+        <v>0</v>
+      </c>
+      <c r="G23" s="103">
         <f>SUMIF('Судовые документы'!H6:H12,"7.4.10/1",'Судовые документы'!I6:I12)+SUMIF('Таможенные документы'!H6:H10,"7.4.10/1",'Таможенные документы'!I6:I10)+SUMIF('Экспортные грузы'!H6:H10,"7.4.10/1",'Экспортные грузы'!I6:I10)+SUMIF(Терминал!H6:H21,"7.4.10/1",Терминал!I6:I21)+SUMIF('ЖД грузы'!H6:H15,"7.4.10/1",'ЖД грузы'!I6:I15)</f>
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H23" s="23"/>
       <c r="I23" s="23"/>
     </row>
     <row r="24" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="51" t="s">
+      <c r="A24" s="50" t="s">
         <v>53</v>
       </c>
       <c r="B24" s="42">
@@ -3239,15 +3186,15 @@
         <f>COUNTIF('Судовые документы'!H6:H12,"7.4.11")+COUNTIF('Таможенные документы'!H6:H10,"7.4.11")+COUNTIF('Экспортные грузы'!H6:H10,"7.4.11")+COUNTIF(Терминал!H6:H21,"7.4.11")+COUNTIF('ЖД грузы'!H6:H15,"7.4.11")</f>
         <v>16</v>
       </c>
-      <c r="G24" s="104">
+      <c r="G24" s="103">
         <f>SUMIF('Судовые документы'!H6:H12,"7.4.11",'Судовые документы'!I6:I12)+SUMIF('Таможенные документы'!H6:H10,"7.4.11",'Таможенные документы'!I6:I10)+SUMIF('Экспортные грузы'!H6:H10,"7.4.11",'Экспортные грузы'!I6:I10)+SUMIF(Терминал!H6:H21,"7.4.11",Терминал!I6:I21)+SUMIF('ЖД грузы'!H6:H15,"7.4.11",'ЖД грузы'!I6:I15)</f>
-        <v>2954</v>
+        <v>574</v>
       </c>
       <c r="H24" s="23"/>
       <c r="I24" s="23"/>
     </row>
     <row r="25" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="46" t="s">
+      <c r="A25" s="45" t="s">
         <v>55</v>
       </c>
       <c r="B25" s="42">
@@ -3264,83 +3211,110 @@
       </c>
       <c r="F25" s="42">
         <f>COUNTIF('Судовые документы'!H6:H12,"7.4.12")+COUNTIF('Таможенные документы'!H6:H10,"7.4.12")+COUNTIF('Экспортные грузы'!H6:H10,"7.4.12")+COUNTIF(Терминал!H6:H21,"7.4.12")+COUNTIF('ЖД грузы'!H6:H15,"7.4.12")</f>
-        <v>2</v>
-      </c>
-      <c r="G25" s="104">
+        <v>0</v>
+      </c>
+      <c r="G25" s="103">
         <f>SUMIF('Судовые документы'!H6:H12,"7.4.12",'Судовые документы'!I6:I12)+SUMIF('Таможенные документы'!H6:H10,"7.4.12",'Таможенные документы'!I6:I10)+SUMIF('Экспортные грузы'!H6:H10,"7.4.12",'Экспортные грузы'!I6:I10)+SUMIF(Терминал!H6:H21,"7.4.12",Терминал!I6:I21)+SUMIF('ЖД грузы'!H6:H15,"7.4.12",'ЖД грузы'!I6:I15)</f>
-        <v>860</v>
+        <v>0</v>
       </c>
       <c r="H25" s="23"/>
       <c r="I25" s="23"/>
     </row>
     <row r="26" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="76" t="s">
+      <c r="A26" s="75" t="s">
         <v>56</v>
       </c>
-      <c r="B26" s="77">
+      <c r="B26" s="76">
         <f>COUNTIF('Судовые документы'!G6:G12,"Не СОЛВО")+COUNTIF('Таможенные документы'!G6:G10,"Не СОЛВО")+COUNTIF('Экспортные грузы'!G6:G10,"Не СОЛВО")+COUNTIF(Терминал!G6:G21,"Не СОЛВО")+COUNTIF('ЖД грузы'!G6:G15,"Не СОЛВО")</f>
-        <v>3</v>
-      </c>
-      <c r="C26" s="78">
+        <v>2</v>
+      </c>
+      <c r="C26" s="77">
         <f>IF(('Судовые документы'!A4+'Таможенные документы'!A4+'Экспортные грузы'!A4+Терминал!A4+'ЖД грузы'!A4)=0,0,B26/('Судовые документы'!A4+'Таможенные документы'!A4+'Экспортные грузы'!A4+Терминал!A4+'ЖД грузы'!A4))</f>
-        <v>6.9767441860465115E-2</v>
+        <v>4.6511627906976744E-2</v>
       </c>
       <c r="D26" s="23"/>
       <c r="E26" s="44" t="s">
         <v>56</v>
       </c>
       <c r="F26" s="42">
-        <f>COUNTIF('Судовые документы'!G6:G12,"Не СОЛВО")+COUNTIF('Таможенные документы'!G6:G10,"Не СОЛВО")+COUNTIF('Экспортные грузы'!G6:G10,"Не СОЛВО")+COUNTIF(Терминал!G6:G21,"Не СОЛВО")+COUNTIF('ЖД грузы'!G6:G15,"Не СОЛВО")</f>
-        <v>3</v>
-      </c>
-      <c r="G26" s="45"/>
+        <f>COUNTIF('Судовые документы'!H6:H12,"Не СОЛВО")+COUNTIF('Таможенные документы'!H6:H10,"Не СОЛВО")+COUNTIF('Экспортные грузы'!H6:H10,"Не СОЛВО")+COUNTIF(Терминал!H6:H21,"Не СОЛВО")+COUNTIF('ЖД грузы'!H6:H15,"Не СОЛВО")</f>
+        <v>2</v>
+      </c>
+      <c r="G26" s="103">
+        <f>SUMIF('Судовые документы'!H7:H13,"Не СОЛВО",'Судовые документы'!I7:I13)+SUMIF('Таможенные документы'!H7:H11,"Не СОЛВО",'Таможенные документы'!I7:I11)+SUMIF('Экспортные грузы'!H7:H11,"Не СОЛВО",'Экспортные грузы'!I7:I11)+SUMIF(Терминал!H7:H22,"Не СОЛВО",Терминал!I7:I22)+SUMIF('ЖД грузы'!H7:H16,"Не СОЛВО",'ЖД грузы'!I7:I16)</f>
+        <v>0</v>
+      </c>
       <c r="H26" s="23"/>
       <c r="I26" s="23"/>
     </row>
     <row r="27" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="79" t="s">
-        <v>57</v>
-      </c>
-      <c r="B27" s="80">
-        <f>IFERROR(SUM(B16:B26),"0")</f>
-        <v>42</v>
-      </c>
-      <c r="C27" s="81">
-        <f>SUM(C16:C26)</f>
-        <v>0.9767441860465117</v>
+      <c r="A27" s="75" t="s">
+        <v>214</v>
+      </c>
+      <c r="B27" s="76">
+        <f>COUNTIF('Судовые документы'!H6:H12,"Н/Д")+COUNTIF('Таможенные документы'!H6:H10,"Н/Д")+COUNTIF('Экспортные грузы'!H6:H10,"Н/Д")+COUNTIF(Терминал!H6:H21,"Н/Д")+COUNTIF('ЖД грузы'!H6:H15,"Н/Д")</f>
+        <v>3</v>
+      </c>
+      <c r="C27" s="77">
+        <f>IF(('Судовые документы'!A4+'Таможенные документы'!A4+'Экспортные грузы'!A4+Терминал!A4+'ЖД грузы'!A4)=0,0,B27/('Судовые документы'!A4+'Таможенные документы'!A4+'Экспортные грузы'!A4+Терминал!A4+'ЖД грузы'!A4))</f>
+        <v>6.9767441860465115E-2</v>
       </c>
       <c r="D27" s="23"/>
-      <c r="E27" s="79" t="s">
-        <v>57</v>
-      </c>
-      <c r="F27" s="80">
-        <f>IFERROR(SUM(F17:F26),"0")</f>
-        <v>43</v>
-      </c>
-      <c r="G27" s="102">
-        <f>IFERROR(SUM(G17:G26),"0")</f>
-        <v>6385</v>
+      <c r="E27" s="142" t="s">
+        <v>214</v>
+      </c>
+      <c r="F27" s="42">
+        <f>COUNTIF('Судовые документы'!H6:H12,"Н/Д")+COUNTIF('Таможенные документы'!H6:H10,"Н/Д")+COUNTIF('Экспортные грузы'!H6:H10,"Н/Д")+COUNTIF(Терминал!H6:H21,"Н/Д")+COUNTIF('ЖД грузы'!H6:H15,"Н/Д")</f>
+        <v>3</v>
+      </c>
+      <c r="G27" s="103">
+        <f>SUMIF('Судовые документы'!H8:H14,"7.4.12",'Судовые документы'!I8:I14)+SUMIF('Таможенные документы'!H8:H12,"7.4.12",'Таможенные документы'!I8:I12)+SUMIF('Экспортные грузы'!H8:H12,"7.4.12",'Экспортные грузы'!I8:I12)+SUMIF(Терминал!H8:H23,"7.4.12",Терминал!I8:I23)+SUMIF('ЖД грузы'!H8:H17,"7.4.12",'ЖД грузы'!I8:I17)</f>
+        <v>0</v>
       </c>
       <c r="H27" s="23"/>
       <c r="I27" s="23"/>
     </row>
     <row r="28" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="52" t="s">
-        <v>58</v>
-      </c>
-      <c r="B28" s="23"/>
-      <c r="C28" s="23"/>
+      <c r="A28" s="78" t="s">
+        <v>57</v>
+      </c>
+      <c r="B28" s="79">
+        <f>IFERROR(SUM(B16:B27),"0")</f>
+        <v>44</v>
+      </c>
+      <c r="C28" s="80">
+        <f>SUM(C16:C27)</f>
+        <v>1.0232558139534884</v>
+      </c>
       <c r="D28" s="23"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="23"/>
+      <c r="E28" s="78" t="s">
+        <v>57</v>
+      </c>
+      <c r="F28" s="79">
+        <f>IFERROR(SUM(F17:F27),"0")</f>
+        <v>43</v>
+      </c>
+      <c r="G28" s="101">
+        <f>IFERROR(SUM(G17:G26),"0")</f>
+        <v>3231</v>
+      </c>
       <c r="H28" s="23"/>
       <c r="I28" s="23"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A29" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="B29" s="23"/>
+      <c r="C29" s="23"/>
       <c r="E29" s="23"/>
       <c r="F29" s="23"/>
       <c r="G29" s="23"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E30" s="23"/>
+      <c r="F30" s="23"/>
+      <c r="G30" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3349,11 +3323,11 @@
     <mergeCell ref="E15:G15"/>
   </mergeCells>
   <conditionalFormatting sqref="D6">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="81" priority="1" operator="equal">
+      <formula>FALSE</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="80" priority="2" operator="equal">
       <formula>TRUE</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
-      <formula>FALSE</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3431,7 +3405,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
@@ -3441,7 +3415,7 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -3460,13 +3434,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="B1" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="C1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -3482,18 +3456,18 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="B3" t="s">
         <v>42</v>
       </c>
       <c r="C3" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="B4" t="s">
         <v>55</v>
@@ -3501,7 +3475,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="B5" t="s">
         <v>40</v>
@@ -3509,7 +3483,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="B6" t="s">
         <v>38</v>
@@ -3517,15 +3491,15 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="B7" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -3557,38 +3531,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="126" t="s">
+      <c r="A1" s="119" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="126"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="126"/>
-      <c r="E1" s="126"/>
-      <c r="F1" s="126"/>
-      <c r="G1" s="126"/>
-      <c r="H1" s="126"/>
-      <c r="I1" s="126"/>
-      <c r="J1" s="126"/>
-      <c r="K1" s="126"/>
-      <c r="L1" s="126"/>
-      <c r="M1" s="126"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
     </row>
     <row r="2" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="123" t="s">
+      <c r="A2" s="116" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="120"/>
-      <c r="C2" s="120"/>
-      <c r="D2" s="120"/>
-      <c r="E2" s="120"/>
-      <c r="F2" s="120"/>
-      <c r="G2" s="120"/>
-      <c r="H2" s="120"/>
-      <c r="I2" s="120"/>
-      <c r="J2" s="120"/>
-      <c r="K2" s="120"/>
-      <c r="L2" s="120"/>
-      <c r="M2" s="120"/>
+      <c r="B2" s="113"/>
+      <c r="C2" s="113"/>
+      <c r="D2" s="113"/>
+      <c r="E2" s="113"/>
+      <c r="F2" s="113"/>
+      <c r="G2" s="113"/>
+      <c r="H2" s="113"/>
+      <c r="I2" s="113"/>
+      <c r="J2" s="113"/>
+      <c r="K2" s="113"/>
+      <c r="L2" s="113"/>
+      <c r="M2" s="113"/>
     </row>
     <row r="3" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -3632,21 +3606,21 @@
       </c>
     </row>
     <row r="4" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="124" t="s">
+      <c r="A4" s="117" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="125"/>
-      <c r="C4" s="125"/>
-      <c r="D4" s="125"/>
-      <c r="E4" s="125"/>
-      <c r="F4" s="125"/>
-      <c r="G4" s="125"/>
-      <c r="H4" s="125"/>
-      <c r="I4" s="125"/>
-      <c r="J4" s="125"/>
-      <c r="K4" s="125"/>
-      <c r="L4" s="125"/>
-      <c r="M4" s="125"/>
+      <c r="B4" s="118"/>
+      <c r="C4" s="118"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="118"/>
+      <c r="L4" s="118"/>
+      <c r="M4" s="118"/>
     </row>
     <row r="5" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
@@ -3706,7 +3680,7 @@
         <f>'Судовые документы'!A7</f>
         <v>2</v>
       </c>
-      <c r="B6" s="13" t="str">
+      <c r="B6" s="13">
         <f>'Судовые документы'!B7</f>
         <v>3323631</v>
       </c>
@@ -3834,15 +3808,15 @@
       </c>
       <c r="G8" s="15" t="str">
         <f>IFERROR(IF(K8="Обработка судовых документов",INDEX('Судовые документы'!G:G,MATCH(A8,'Судовые документы'!A:A,0)),IF(K8="Оформление таможенных документов",INDEX('Таможенные документы'!G:G,MATCH(A8,'Таможенные документы'!A:A,0)),IF(K8="Оформление экспортных грузов",INDEX('Экспортные грузы'!G:G,MATCH(A8,'Экспортные грузы'!A:A,0)),IF(K8="Терминальные операции",INDEX(Терминал!G:G,MATCH(A8,Терминал!A:A,0)),IF(K8="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!G:G,MATCH(A8,'ЖД грузы'!A:A,0)),""))))),"")</f>
-        <v>Не СОЛВО</v>
-      </c>
-      <c r="H8" s="17">
+        <v>Выставлено</v>
+      </c>
+      <c r="H8" s="17" t="str">
         <f>IFERROR(IF(K8="Обработка судовых документов",INDEX('Судовые документы'!H:H,MATCH(A8,'Судовые документы'!A:A,0)),IF(K8="Оформление таможенных документов",INDEX('Таможенные документы'!H:H,MATCH(A8,'Таможенные документы'!A:A,0)),IF(K8="Оформление экспортных грузов",INDEX('Экспортные грузы'!H:H,MATCH(A8,'Экспортные грузы'!A:A,0)),IF(K8="Терминальные операции",INDEX(Терминал!H:H,MATCH(A8,Терминал!A:A,0)),IF(K8="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!H:H,MATCH(A8,'ЖД грузы'!A:A,0)),""))))),"")</f>
-        <v>0</v>
+        <v>7.4.5</v>
       </c>
       <c r="I8" s="18">
         <f>IFERROR(IF(K8="Обработка судовых документов",INDEX('Судовые документы'!I:I,MATCH(A8,'Судовые документы'!A:A,0)),IF(K8="Оформление таможенных документов",INDEX('Таможенные документы'!I:I,MATCH(A8,'Таможенные документы'!A:A,0)),IF(K8="Оформление экспортных грузов",INDEX('Экспортные грузы'!I:I,MATCH(A8,'Экспортные грузы'!A:A,0)),IF(K8="Терминальные операции",INDEX(Терминал!I:I,MATCH(A8,Терминал!A:A,0)),IF(K8="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!I:I,MATCH(A8,'ЖД грузы'!A:A,0)),""))))),"")</f>
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J8" s="16" t="str">
         <f>IFERROR(IF(K8="Обработка судовых документов",INDEX('Судовые документы'!J:J,MATCH(A8,'Судовые документы'!A:A,0)),IF(K8="Оформление таможенных документов",INDEX('Таможенные документы'!J:J,MATCH(A8,'Таможенные документы'!A:A,0)),IF(K8="Оформление экспортных грузов",INDEX('Экспортные грузы'!J:J,MATCH(A8,'Экспортные грузы'!A:A,0)),IF(K8="Терминальные операции",INDEX(Терминал!J:J,MATCH(A8,Терминал!A:A,0)),IF(K8="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!J:J,MATCH(A8,'ЖД грузы'!A:A,0)),""))))),"")</f>
@@ -3889,9 +3863,9 @@
         <f>IFERROR(IF(K9="Обработка судовых документов",INDEX('Судовые документы'!G:G,MATCH(A9,'Судовые документы'!A:A,0)),IF(K9="Оформление таможенных документов",INDEX('Таможенные документы'!G:G,MATCH(A9,'Таможенные документы'!A:A,0)),IF(K9="Оформление экспортных грузов",INDEX('Экспортные грузы'!G:G,MATCH(A9,'Экспортные грузы'!A:A,0)),IF(K9="Терминальные операции",INDEX(Терминал!G:G,MATCH(A9,Терминал!A:A,0)),IF(K9="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!G:G,MATCH(A9,'ЖД грузы'!A:A,0)),""))))),"")</f>
         <v>Не СОЛВО</v>
       </c>
-      <c r="H9" s="8">
+      <c r="H9" s="8" t="str">
         <f>IFERROR(IF(K9="Обработка судовых документов",INDEX('Судовые документы'!H:H,MATCH(A9,'Судовые документы'!A:A,0)),IF(K9="Оформление таможенных документов",INDEX('Таможенные документы'!H:H,MATCH(A9,'Таможенные документы'!A:A,0)),IF(K9="Оформление экспортных грузов",INDEX('Экспортные грузы'!H:H,MATCH(A9,'Экспортные грузы'!A:A,0)),IF(K9="Терминальные операции",INDEX(Терминал!H:H,MATCH(A9,Терминал!A:A,0)),IF(K9="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!H:H,MATCH(A9,'ЖД грузы'!A:A,0)),""))))),"")</f>
-        <v>0</v>
+        <v>Не СОЛВО</v>
       </c>
       <c r="I9" s="9">
         <f>IFERROR(IF(K9="Обработка судовых документов",INDEX('Судовые документы'!I:I,MATCH(A9,'Судовые документы'!A:A,0)),IF(K9="Оформление таможенных документов",INDEX('Таможенные документы'!I:I,MATCH(A9,'Таможенные документы'!A:A,0)),IF(K9="Оформление экспортных грузов",INDEX('Экспортные грузы'!I:I,MATCH(A9,'Экспортные грузы'!A:A,0)),IF(K9="Терминальные операции",INDEX(Терминал!I:I,MATCH(A9,Терминал!A:A,0)),IF(K9="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!I:I,MATCH(A9,'ЖД грузы'!A:A,0)),""))))),"")</f>
@@ -3948,7 +3922,7 @@
       </c>
       <c r="I10" s="18">
         <f>IFERROR(IF(K10="Обработка судовых документов",INDEX('Судовые документы'!I:I,MATCH(A10,'Судовые документы'!A:A,0)),IF(K10="Оформление таможенных документов",INDEX('Таможенные документы'!I:I,MATCH(A10,'Таможенные документы'!A:A,0)),IF(K10="Оформление экспортных грузов",INDEX('Экспортные грузы'!I:I,MATCH(A10,'Экспортные грузы'!A:A,0)),IF(K10="Терминальные операции",INDEX(Терминал!I:I,MATCH(A10,Терминал!A:A,0)),IF(K10="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!I:I,MATCH(A10,'ЖД грузы'!A:A,0)),""))))),"")</f>
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="J10" s="16" t="str">
         <f>IFERROR(IF(K10="Обработка судовых документов",INDEX('Судовые документы'!J:J,MATCH(A10,'Судовые документы'!A:A,0)),IF(K10="Оформление таможенных документов",INDEX('Таможенные документы'!J:J,MATCH(A10,'Таможенные документы'!A:A,0)),IF(K10="Оформление экспортных грузов",INDEX('Экспортные грузы'!J:J,MATCH(A10,'Экспортные грузы'!A:A,0)),IF(K10="Терминальные операции",INDEX(Терминал!J:J,MATCH(A10,Терминал!A:A,0)),IF(K10="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!J:J,MATCH(A10,'ЖД грузы'!A:A,0)),""))))),"")</f>
@@ -3967,74 +3941,66 @@
       </c>
     </row>
     <row r="11" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="105">
+      <c r="A11" s="133">
         <f>'Судовые документы'!A12</f>
         <v>7</v>
       </c>
-      <c r="B11" s="106" t="str">
+      <c r="B11" s="134" t="str">
         <f>'Судовые документы'!B12</f>
         <v>4SC-RQ-CR-988 #4032163</v>
       </c>
-      <c r="C11" s="107" t="str">
+      <c r="C11" s="135" t="str">
         <f>'Судовые документы'!C12</f>
         <v>Обработка на т/х порожних контейнеров (каботаж)</v>
       </c>
-      <c r="D11" s="108">
-        <f>IFERROR(IF(K11="Обработка судовых документов",INDEX('Судовые документы'!D:D,MATCH(A11,'Судовые документы'!A:A,0)),IF(K11="Оформление таможенных документов",INDEX('Таможенные документы'!D:D,MATCH(A11,'Таможенные документы'!A:A,0)),IF(K11="Оформление экспортных грузов",INDEX('Экспортные грузы'!D:D,MATCH(A11,'Экспортные грузы'!A:A,0)),IF(K11="Терминальные операции",INDEX(Терминал!D:D,MATCH(A11,Терминал!A:A,0)),IF(K11="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!D:D,MATCH(A11,'ЖД грузы'!A:A,0)),""))))),"")</f>
-        <v>553</v>
-      </c>
-      <c r="E11" s="109">
-        <f>IFERROR(IF(K11="Обработка судовых документов",INDEX('Судовые документы'!E:E,MATCH(A11,'Судовые документы'!A:A,0)),IF(K11="Оформление таможенных документов",INDEX('Таможенные документы'!E:E,MATCH(A11,'Таможенные документы'!A:A,0)),IF(K11="Оформление экспортных грузов",INDEX('Экспортные грузы'!E:E,MATCH(A11,'Экспортные грузы'!A:A,0)),IF(K11="Терминальные операции",INDEX(Терминал!E:E,MATCH(A11,Терминал!A:A,0)),IF(K11="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!E:E,MATCH(A11,'ЖД грузы'!A:A,0)),""))))),"")</f>
-        <v>0.42857142857142855</v>
-      </c>
-      <c r="F11" s="108">
-        <f>IFERROR(IF(K11="Обработка судовых документов",INDEX('Судовые документы'!F:F,MATCH(A11,'Судовые документы'!A:A,0)),IF(K11="Оформление таможенных документов",INDEX('Таможенные документы'!F:F,MATCH(A11,'Таможенные документы'!A:A,0)),IF(K11="Оформление экспортных грузов",INDEX('Экспортные грузы'!F:F,MATCH(A11,'Экспортные грузы'!A:A,0)),IF(K11="Терминальные операции",INDEX(Терминал!F:F,MATCH(A11,Терминал!A:A,0)),IF(K11="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!F:F,MATCH(A11,'ЖД грузы'!A:A,0)),""))))),"")</f>
+      <c r="D11" s="136" t="s">
+        <v>83</v>
+      </c>
+      <c r="E11" s="137">
+        <v>2026</v>
+      </c>
+      <c r="F11" s="136" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" s="136" t="s">
+        <v>47</v>
+      </c>
+      <c r="H11" s="138" t="s">
+        <v>52</v>
+      </c>
+      <c r="I11" s="139">
         <v>0</v>
       </c>
-      <c r="G11" s="108">
-        <f>IFERROR(IF(K11="Обработка судовых документов",INDEX('Судовые документы'!G:G,MATCH(A11,'Судовые документы'!A:A,0)),IF(K11="Оформление таможенных документов",INDEX('Таможенные документы'!G:G,MATCH(A11,'Таможенные документы'!A:A,0)),IF(K11="Оформление экспортных грузов",INDEX('Экспортные грузы'!G:G,MATCH(A11,'Экспортные грузы'!A:A,0)),IF(K11="Терминальные операции",INDEX(Терминал!G:G,MATCH(A11,Терминал!A:A,0)),IF(K11="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!G:G,MATCH(A11,'ЖД грузы'!A:A,0)),""))))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="H11" s="110">
-        <f>IFERROR(IF(K11="Обработка судовых документов",INDEX('Судовые документы'!H:H,MATCH(A11,'Судовые документы'!A:A,0)),IF(K11="Оформление таможенных документов",INDEX('Таможенные документы'!H:H,MATCH(A11,'Таможенные документы'!A:A,0)),IF(K11="Оформление экспортных грузов",INDEX('Экспортные грузы'!H:H,MATCH(A11,'Экспортные грузы'!A:A,0)),IF(K11="Терминальные операции",INDEX(Терминал!H:H,MATCH(A11,Терминал!A:A,0)),IF(K11="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!H:H,MATCH(A11,'ЖД грузы'!A:A,0)),""))))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="I11" s="111">
-        <f>IFERROR(IF(K11="Обработка судовых документов",INDEX('Судовые документы'!I:I,MATCH(A11,'Судовые документы'!A:A,0)),IF(K11="Оформление таможенных документов",INDEX('Таможенные документы'!I:I,MATCH(A11,'Таможенные документы'!A:A,0)),IF(K11="Оформление экспортных грузов",INDEX('Экспортные грузы'!I:I,MATCH(A11,'Экспортные грузы'!A:A,0)),IF(K11="Терминальные операции",INDEX(Терминал!I:I,MATCH(A11,Терминал!A:A,0)),IF(K11="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!I:I,MATCH(A11,'ЖД грузы'!A:A,0)),""))))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="J11" s="109">
-        <f>IFERROR(IF(K11="Обработка судовых документов",INDEX('Судовые документы'!J:J,MATCH(A11,'Судовые документы'!A:A,0)),IF(K11="Оформление таможенных документов",INDEX('Таможенные документы'!J:J,MATCH(A11,'Таможенные документы'!A:A,0)),IF(K11="Оформление экспортных грузов",INDEX('Экспортные грузы'!J:J,MATCH(A11,'Экспортные грузы'!A:A,0)),IF(K11="Терминальные операции",INDEX(Терминал!J:J,MATCH(A11,Терминал!A:A,0)),IF(K11="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!J:J,MATCH(A11,'ЖД грузы'!A:A,0)),""))))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="K11" s="112" t="s">
+      <c r="J11" s="137" t="s">
+        <v>65</v>
+      </c>
+      <c r="K11" s="140" t="s">
         <v>16</v>
       </c>
-      <c r="L11" s="113">
-        <f>IFERROR(IF(K11="Обработка судовых документов",INDEX('Судовые документы'!L:L,MATCH(A11,'Судовые документы'!A:A,0)),IF(K11="Оформление таможенных документов",INDEX('Таможенные документы'!L:L,MATCH(A11,'Таможенные документы'!A:A,0)),IF(K11="Оформление экспортных грузов",INDEX('Экспортные грузы'!L:L,MATCH(A11,'Экспортные грузы'!A:A,0)),IF(K11="Терминальные операции",INDEX(Терминал!L:L,MATCH(A11,Терминал!A:A,0)),IF(K11="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!L:L,MATCH(A11,'ЖД грузы'!A:A,0)),""))))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="M11" s="109">
+      <c r="L11" s="141" t="s">
+        <v>66</v>
+      </c>
+      <c r="M11" s="137">
         <f>IFERROR(IF(K11="Обработка судовых документов",INDEX('Судовые документы'!K:K,MATCH(A11,'Судовые документы'!A:A,0)),IF(K11="Оформление таможенных документов",INDEX('Таможенные документы'!K:K,MATCH(A11,'Таможенные документы'!A:A,0)),IF(K11="Оформление экспортных грузов",INDEX('Экспортные грузы'!K:K,MATCH(A11,'Экспортные грузы'!A:A,0)),IF(K11="Терминальные операции",INDEX(Терминал!K:K,MATCH(A11,Терминал!A:A,0)),IF(K11="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!K:K,MATCH(A11,'ЖД грузы'!A:A,0)),""))))),"")</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="129" t="s">
+      <c r="A12" s="122" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="122"/>
-      <c r="C12" s="122"/>
-      <c r="D12" s="122"/>
-      <c r="E12" s="122"/>
-      <c r="F12" s="122"/>
-      <c r="G12" s="122"/>
-      <c r="H12" s="122"/>
-      <c r="I12" s="122"/>
-      <c r="J12" s="122"/>
-      <c r="K12" s="122"/>
-      <c r="L12" s="122"/>
-      <c r="M12" s="122"/>
+      <c r="B12" s="115"/>
+      <c r="C12" s="115"/>
+      <c r="D12" s="115"/>
+      <c r="E12" s="115"/>
+      <c r="F12" s="115"/>
+      <c r="G12" s="115"/>
+      <c r="H12" s="115"/>
+      <c r="I12" s="115"/>
+      <c r="J12" s="115"/>
+      <c r="K12" s="115"/>
+      <c r="L12" s="115"/>
+      <c r="M12" s="115"/>
     </row>
     <row r="13" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
@@ -4124,7 +4090,7 @@
       </c>
       <c r="I14" s="18">
         <f>IFERROR(IF(K14="Обработка судовых документов",INDEX('Судовые документы'!I:I,MATCH(A14,'Судовые документы'!A:A,0)),IF(K14="Оформление таможенных документов",INDEX('Таможенные документы'!I:I,MATCH(A14,'Таможенные документы'!A:A,0)),IF(K14="Оформление экспортных грузов",INDEX('Экспортные грузы'!I:I,MATCH(A14,'Экспортные грузы'!A:A,0)),IF(K14="Терминальные операции",INDEX(Терминал!I:I,MATCH(A14,Терминал!A:A,0)),IF(K14="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!I:I,MATCH(A14,'ЖД грузы'!A:A,0)),""))))),"")</f>
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="J14" s="16" t="str">
         <f>IFERROR(IF(K14="Обработка судовых документов",INDEX('Судовые документы'!J:J,MATCH(A14,'Судовые документы'!A:A,0)),IF(K14="Оформление таможенных документов",INDEX('Таможенные документы'!J:J,MATCH(A14,'Таможенные документы'!A:A,0)),IF(K14="Оформление экспортных грузов",INDEX('Экспортные грузы'!J:J,MATCH(A14,'Экспортные грузы'!A:A,0)),IF(K14="Терминальные операции",INDEX(Терминал!J:J,MATCH(A14,Терминал!A:A,0)),IF(K14="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!J:J,MATCH(A14,'ЖД грузы'!A:A,0)),""))))),"")</f>
@@ -4177,7 +4143,7 @@
       </c>
       <c r="I15" s="9">
         <f>IFERROR(IF(K15="Обработка судовых документов",INDEX('Судовые документы'!I:I,MATCH(A15,'Судовые документы'!A:A,0)),IF(K15="Оформление таможенных документов",INDEX('Таможенные документы'!I:I,MATCH(A15,'Таможенные документы'!A:A,0)),IF(K15="Оформление экспортных грузов",INDEX('Экспортные грузы'!I:I,MATCH(A15,'Экспортные грузы'!A:A,0)),IF(K15="Терминальные операции",INDEX(Терминал!I:I,MATCH(A15,Терминал!A:A,0)),IF(K15="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!I:I,MATCH(A15,'ЖД грузы'!A:A,0)),""))))),"")</f>
-        <v>680</v>
+        <v>0</v>
       </c>
       <c r="J15" s="7" t="str">
         <f>IFERROR(IF(K15="Обработка судовых документов",INDEX('Судовые документы'!J:J,MATCH(A15,'Судовые документы'!A:A,0)),IF(K15="Оформление таможенных документов",INDEX('Таможенные документы'!J:J,MATCH(A15,'Таможенные документы'!A:A,0)),IF(K15="Оформление экспортных грузов",INDEX('Экспортные грузы'!J:J,MATCH(A15,'Экспортные грузы'!A:A,0)),IF(K15="Терминальные операции",INDEX(Терминал!J:J,MATCH(A15,Терминал!A:A,0)),IF(K15="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!J:J,MATCH(A15,'ЖД грузы'!A:A,0)),""))))),"")</f>
@@ -4230,7 +4196,7 @@
       </c>
       <c r="I16" s="18">
         <f>IFERROR(IF(K16="Обработка судовых документов",INDEX('Судовые документы'!I:I,MATCH(A16,'Судовые документы'!A:A,0)),IF(K16="Оформление таможенных документов",INDEX('Таможенные документы'!I:I,MATCH(A16,'Таможенные документы'!A:A,0)),IF(K16="Оформление экспортных грузов",INDEX('Экспортные грузы'!I:I,MATCH(A16,'Экспортные грузы'!A:A,0)),IF(K16="Терминальные операции",INDEX(Терминал!I:I,MATCH(A16,Терминал!A:A,0)),IF(K16="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!I:I,MATCH(A16,'ЖД грузы'!A:A,0)),""))))),"")</f>
-        <v>460</v>
+        <v>0</v>
       </c>
       <c r="J16" s="16" t="str">
         <f>IFERROR(IF(K16="Обработка судовых документов",INDEX('Судовые документы'!J:J,MATCH(A16,'Судовые документы'!A:A,0)),IF(K16="Оформление таможенных документов",INDEX('Таможенные документы'!J:J,MATCH(A16,'Таможенные документы'!A:A,0)),IF(K16="Оформление экспортных грузов",INDEX('Экспортные грузы'!J:J,MATCH(A16,'Экспортные грузы'!A:A,0)),IF(K16="Терминальные операции",INDEX(Терминал!J:J,MATCH(A16,Терминал!A:A,0)),IF(K16="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!J:J,MATCH(A16,'ЖД грузы'!A:A,0)),""))))),"")</f>
@@ -4253,9 +4219,9 @@
         <f>'Таможенные документы'!A10</f>
         <v>12</v>
       </c>
-      <c r="B17" s="4" t="str">
+      <c r="B17" s="4">
         <f>'Таможенные документы'!B10</f>
-        <v>4SC-RQ-CR-987 #4073944</v>
+        <v>0</v>
       </c>
       <c r="C17" s="5" t="str">
         <f>'Таможенные документы'!C10</f>
@@ -4283,7 +4249,7 @@
       </c>
       <c r="I17" s="9">
         <f>IFERROR(IF(K17="Обработка судовых документов",INDEX('Судовые документы'!I:I,MATCH(A17,'Судовые документы'!A:A,0)),IF(K17="Оформление таможенных документов",INDEX('Таможенные документы'!I:I,MATCH(A17,'Таможенные документы'!A:A,0)),IF(K17="Оформление экспортных грузов",INDEX('Экспортные грузы'!I:I,MATCH(A17,'Экспортные грузы'!A:A,0)),IF(K17="Терминальные операции",INDEX(Терминал!I:I,MATCH(A17,Терминал!A:A,0)),IF(K17="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!I:I,MATCH(A17,'ЖД грузы'!A:A,0)),""))))),"")</f>
-        <v>410</v>
+        <v>0</v>
       </c>
       <c r="J17" s="7" t="str">
         <f>IFERROR(IF(K17="Обработка судовых документов",INDEX('Судовые документы'!J:J,MATCH(A17,'Судовые документы'!A:A,0)),IF(K17="Оформление таможенных документов",INDEX('Таможенные документы'!J:J,MATCH(A17,'Таможенные документы'!A:A,0)),IF(K17="Оформление экспортных грузов",INDEX('Экспортные грузы'!J:J,MATCH(A17,'Экспортные грузы'!A:A,0)),IF(K17="Терминальные операции",INDEX(Терминал!J:J,MATCH(A17,Терминал!A:A,0)),IF(K17="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!J:J,MATCH(A17,'ЖД грузы'!A:A,0)),""))))),"")</f>
@@ -4302,21 +4268,21 @@
       </c>
     </row>
     <row r="18" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="129" t="s">
+      <c r="A18" s="122" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="122"/>
-      <c r="C18" s="122"/>
-      <c r="D18" s="122"/>
-      <c r="E18" s="122"/>
-      <c r="F18" s="122"/>
-      <c r="G18" s="122"/>
-      <c r="H18" s="122"/>
-      <c r="I18" s="122"/>
-      <c r="J18" s="122"/>
-      <c r="K18" s="122"/>
-      <c r="L18" s="122"/>
-      <c r="M18" s="122"/>
+      <c r="B18" s="115"/>
+      <c r="C18" s="115"/>
+      <c r="D18" s="115"/>
+      <c r="E18" s="115"/>
+      <c r="F18" s="115"/>
+      <c r="G18" s="115"/>
+      <c r="H18" s="115"/>
+      <c r="I18" s="115"/>
+      <c r="J18" s="115"/>
+      <c r="K18" s="115"/>
+      <c r="L18" s="115"/>
+      <c r="M18" s="115"/>
     </row>
     <row r="19" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
@@ -4325,7 +4291,7 @@
       </c>
       <c r="B19" s="4" t="str">
         <f>'Экспортные грузы'!B6</f>
-        <v>4SC-1-RQ-CR-409 #2489904</v>
+        <v>4SC-RQ-CR-859 #3985850</v>
       </c>
       <c r="C19" s="5" t="str">
         <f>'Экспортные грузы'!C6</f>
@@ -4353,7 +4319,7 @@
       </c>
       <c r="I19" s="9">
         <f>IFERROR(IF(K19="Обработка судовых документов",INDEX('Судовые документы'!I:I,MATCH(A19,'Судовые документы'!A:A,0)),IF(K19="Оформление таможенных документов",INDEX('Таможенные документы'!I:I,MATCH(A19,'Таможенные документы'!A:A,0)),IF(K19="Оформление экспортных грузов",INDEX('Экспортные грузы'!I:I,MATCH(A19,'Экспортные грузы'!A:A,0)),IF(K19="Терминальные операции",INDEX(Терминал!I:I,MATCH(A19,Терминал!A:A,0)),IF(K19="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!I:I,MATCH(A19,'ЖД грузы'!A:A,0)),""))))),"")</f>
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="J19" s="7" t="str">
         <f>IFERROR(IF(K19="Обработка судовых документов",INDEX('Судовые документы'!J:J,MATCH(A19,'Судовые документы'!A:A,0)),IF(K19="Оформление таможенных документов",INDEX('Таможенные документы'!J:J,MATCH(A19,'Таможенные документы'!A:A,0)),IF(K19="Оформление экспортных грузов",INDEX('Экспортные грузы'!J:J,MATCH(A19,'Экспортные грузы'!A:A,0)),IF(K19="Терминальные операции",INDEX(Терминал!J:J,MATCH(A19,Терминал!A:A,0)),IF(K19="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!J:J,MATCH(A19,'ЖД грузы'!A:A,0)),""))))),"")</f>
@@ -4463,7 +4429,7 @@
       </c>
       <c r="J21" s="7" t="str">
         <f>IFERROR(IF(K21="Обработка судовых документов",INDEX('Судовые документы'!J:J,MATCH(A21,'Судовые документы'!A:A,0)),IF(K21="Оформление таможенных документов",INDEX('Таможенные документы'!J:J,MATCH(A21,'Таможенные документы'!A:A,0)),IF(K21="Оформление экспортных грузов",INDEX('Экспортные грузы'!J:J,MATCH(A21,'Экспортные грузы'!A:A,0)),IF(K21="Терминальные операции",INDEX(Терминал!J:J,MATCH(A21,Терминал!A:A,0)),IF(K21="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!J:J,MATCH(A21,'ЖД грузы'!A:A,0)),""))))),"")</f>
-        <v>Да</v>
+        <v>Нет</v>
       </c>
       <c r="K21" s="10" t="s">
         <v>20</v>
@@ -4537,7 +4503,7 @@
       </c>
       <c r="B23" s="4" t="str">
         <f>'Экспортные грузы'!B10</f>
-        <v>4SC-1-RQ-CR-794 #3307597</v>
+        <v>4SC-1-RQ-CR-794 #3307598</v>
       </c>
       <c r="C23" s="5" t="str">
         <f>'Экспортные грузы'!C10</f>
@@ -4565,7 +4531,7 @@
       </c>
       <c r="I23" s="9">
         <f>IFERROR(IF(K23="Обработка судовых документов",INDEX('Судовые документы'!I:I,MATCH(A23,'Судовые документы'!A:A,0)),IF(K23="Оформление таможенных документов",INDEX('Таможенные документы'!I:I,MATCH(A23,'Таможенные документы'!A:A,0)),IF(K23="Оформление экспортных грузов",INDEX('Экспортные грузы'!I:I,MATCH(A23,'Экспортные грузы'!A:A,0)),IF(K23="Терминальные операции",INDEX(Терминал!I:I,MATCH(A23,Терминал!A:A,0)),IF(K23="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!I:I,MATCH(A23,'ЖД грузы'!A:A,0)),""))))),"")</f>
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="J23" s="7" t="str">
         <f>IFERROR(IF(K23="Обработка судовых документов",INDEX('Судовые документы'!J:J,MATCH(A23,'Судовые документы'!A:A,0)),IF(K23="Оформление таможенных документов",INDEX('Таможенные документы'!J:J,MATCH(A23,'Таможенные документы'!A:A,0)),IF(K23="Оформление экспортных грузов",INDEX('Экспортные грузы'!J:J,MATCH(A23,'Экспортные грузы'!A:A,0)),IF(K23="Терминальные операции",INDEX(Терминал!J:J,MATCH(A23,Терминал!A:A,0)),IF(K23="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!J:J,MATCH(A23,'ЖД грузы'!A:A,0)),""))))),"")</f>
@@ -4584,21 +4550,21 @@
       </c>
     </row>
     <row r="24" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="129" t="s">
+      <c r="A24" s="122" t="s">
         <v>21</v>
       </c>
-      <c r="B24" s="122"/>
-      <c r="C24" s="122"/>
-      <c r="D24" s="122"/>
-      <c r="E24" s="122"/>
-      <c r="F24" s="122"/>
-      <c r="G24" s="122"/>
-      <c r="H24" s="122"/>
-      <c r="I24" s="122"/>
-      <c r="J24" s="122"/>
-      <c r="K24" s="122"/>
-      <c r="L24" s="122"/>
-      <c r="M24" s="122"/>
+      <c r="B24" s="115"/>
+      <c r="C24" s="115"/>
+      <c r="D24" s="115"/>
+      <c r="E24" s="115"/>
+      <c r="F24" s="115"/>
+      <c r="G24" s="115"/>
+      <c r="H24" s="115"/>
+      <c r="I24" s="115"/>
+      <c r="J24" s="115"/>
+      <c r="K24" s="115"/>
+      <c r="L24" s="115"/>
+      <c r="M24" s="115"/>
     </row>
     <row r="25" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
@@ -4631,11 +4597,11 @@
       </c>
       <c r="H25" s="8" t="str">
         <f>IFERROR(IF(K25="Обработка судовых документов",INDEX('Судовые документы'!H:H,MATCH(A25,'Судовые документы'!A:A,0)),IF(K25="Оформление таможенных документов",INDEX('Таможенные документы'!H:H,MATCH(A25,'Таможенные документы'!A:A,0)),IF(K25="Оформление экспортных грузов",INDEX('Экспортные грузы'!H:H,MATCH(A25,'Экспортные грузы'!A:A,0)),IF(K25="Терминальные операции",INDEX(Терминал!H:H,MATCH(A25,Терминал!A:A,0)),IF(K25="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!H:H,MATCH(A25,'ЖД грузы'!A:A,0)),""))))),"")</f>
-        <v>7.4.11</v>
+        <v>Н/Д</v>
       </c>
       <c r="I25" s="9">
         <f>IFERROR(IF(K25="Обработка судовых документов",INDEX('Судовые документы'!I:I,MATCH(A25,'Судовые документы'!A:A,0)),IF(K25="Оформление таможенных документов",INDEX('Таможенные документы'!I:I,MATCH(A25,'Таможенные документы'!A:A,0)),IF(K25="Оформление экспортных грузов",INDEX('Экспортные грузы'!I:I,MATCH(A25,'Экспортные грузы'!A:A,0)),IF(K25="Терминальные операции",INDEX(Терминал!I:I,MATCH(A25,Терминал!A:A,0)),IF(K25="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!I:I,MATCH(A25,'ЖД грузы'!A:A,0)),""))))),"")</f>
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="J25" s="7" t="str">
         <f>IFERROR(IF(K25="Обработка судовых документов",INDEX('Судовые документы'!J:J,MATCH(A25,'Судовые документы'!A:A,0)),IF(K25="Оформление таможенных документов",INDEX('Таможенные документы'!J:J,MATCH(A25,'Таможенные документы'!A:A,0)),IF(K25="Оформление экспортных грузов",INDEX('Экспортные грузы'!J:J,MATCH(A25,'Экспортные грузы'!A:A,0)),IF(K25="Терминальные операции",INDEX(Терминал!J:J,MATCH(A25,Терминал!A:A,0)),IF(K25="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!J:J,MATCH(A25,'ЖД грузы'!A:A,0)),""))))),"")</f>
@@ -4688,7 +4654,7 @@
       </c>
       <c r="I26" s="18">
         <f>IFERROR(IF(K26="Обработка судовых документов",INDEX('Судовые документы'!I:I,MATCH(A26,'Судовые документы'!A:A,0)),IF(K26="Оформление таможенных документов",INDEX('Таможенные документы'!I:I,MATCH(A26,'Таможенные документы'!A:A,0)),IF(K26="Оформление экспортных грузов",INDEX('Экспортные грузы'!I:I,MATCH(A26,'Экспортные грузы'!A:A,0)),IF(K26="Терминальные операции",INDEX(Терминал!I:I,MATCH(A26,Терминал!A:A,0)),IF(K26="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!I:I,MATCH(A26,'ЖД грузы'!A:A,0)),""))))),"")</f>
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="J26" s="16" t="str">
         <f>IFERROR(IF(K26="Обработка судовых документов",INDEX('Судовые документы'!J:J,MATCH(A26,'Судовые документы'!A:A,0)),IF(K26="Оформление таможенных документов",INDEX('Таможенные документы'!J:J,MATCH(A26,'Таможенные документы'!A:A,0)),IF(K26="Оформление экспортных грузов",INDEX('Экспортные грузы'!J:J,MATCH(A26,'Экспортные грузы'!A:A,0)),IF(K26="Терминальные операции",INDEX(Терминал!J:J,MATCH(A26,Терминал!A:A,0)),IF(K26="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!J:J,MATCH(A26,'ЖД грузы'!A:A,0)),""))))),"")</f>
@@ -4794,11 +4760,11 @@
       </c>
       <c r="I28" s="18">
         <f>IFERROR(IF(K28="Обработка судовых документов",INDEX('Судовые документы'!I:I,MATCH(A28,'Судовые документы'!A:A,0)),IF(K28="Оформление таможенных документов",INDEX('Таможенные документы'!I:I,MATCH(A28,'Таможенные документы'!A:A,0)),IF(K28="Оформление экспортных грузов",INDEX('Экспортные грузы'!I:I,MATCH(A28,'Экспортные грузы'!A:A,0)),IF(K28="Терминальные операции",INDEX(Терминал!I:I,MATCH(A28,Терминал!A:A,0)),IF(K28="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!I:I,MATCH(A28,'ЖД грузы'!A:A,0)),""))))),"")</f>
-        <v>350</v>
+        <v>320</v>
       </c>
       <c r="J28" s="16" t="str">
         <f>IFERROR(IF(K28="Обработка судовых документов",INDEX('Судовые документы'!J:J,MATCH(A28,'Судовые документы'!A:A,0)),IF(K28="Оформление таможенных документов",INDEX('Таможенные документы'!J:J,MATCH(A28,'Таможенные документы'!A:A,0)),IF(K28="Оформление экспортных грузов",INDEX('Экспортные грузы'!J:J,MATCH(A28,'Экспортные грузы'!A:A,0)),IF(K28="Терминальные операции",INDEX(Терминал!J:J,MATCH(A28,Терминал!A:A,0)),IF(K28="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!J:J,MATCH(A28,'ЖД грузы'!A:A,0)),""))))),"")</f>
-        <v>Нет</v>
+        <v>Да</v>
       </c>
       <c r="K28" s="19" t="s">
         <v>22</v>
@@ -4900,7 +4866,7 @@
       </c>
       <c r="I30" s="18">
         <f>IFERROR(IF(K30="Обработка судовых документов",INDEX('Судовые документы'!I:I,MATCH(A30,'Судовые документы'!A:A,0)),IF(K30="Оформление таможенных документов",INDEX('Таможенные документы'!I:I,MATCH(A30,'Таможенные документы'!A:A,0)),IF(K30="Оформление экспортных грузов",INDEX('Экспортные грузы'!I:I,MATCH(A30,'Экспортные грузы'!A:A,0)),IF(K30="Терминальные операции",INDEX(Терминал!I:I,MATCH(A30,Терминал!A:A,0)),IF(K30="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!I:I,MATCH(A30,'ЖД грузы'!A:A,0)),""))))),"")</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="J30" s="16" t="str">
         <f>IFERROR(IF(K30="Обработка судовых документов",INDEX('Судовые документы'!J:J,MATCH(A30,'Судовые документы'!A:A,0)),IF(K30="Оформление таможенных документов",INDEX('Таможенные документы'!J:J,MATCH(A30,'Таможенные документы'!A:A,0)),IF(K30="Оформление экспортных грузов",INDEX('Экспортные грузы'!J:J,MATCH(A30,'Экспортные грузы'!A:A,0)),IF(K30="Терминальные операции",INDEX(Терминал!J:J,MATCH(A30,Терминал!A:A,0)),IF(K30="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!J:J,MATCH(A30,'ЖД грузы'!A:A,0)),""))))),"")</f>
@@ -4953,7 +4919,7 @@
       </c>
       <c r="I31" s="9">
         <f>IFERROR(IF(K31="Обработка судовых документов",INDEX('Судовые документы'!I:I,MATCH(A31,'Судовые документы'!A:A,0)),IF(K31="Оформление таможенных документов",INDEX('Таможенные документы'!I:I,MATCH(A31,'Таможенные документы'!A:A,0)),IF(K31="Оформление экспортных грузов",INDEX('Экспортные грузы'!I:I,MATCH(A31,'Экспортные грузы'!A:A,0)),IF(K31="Терминальные операции",INDEX(Терминал!I:I,MATCH(A31,Терминал!A:A,0)),IF(K31="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!I:I,MATCH(A31,'ЖД грузы'!A:A,0)),""))))),"")</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J31" s="7" t="str">
         <f>IFERROR(IF(K31="Обработка судовых документов",INDEX('Судовые документы'!J:J,MATCH(A31,'Судовые документы'!A:A,0)),IF(K31="Оформление таможенных документов",INDEX('Таможенные документы'!J:J,MATCH(A31,'Таможенные документы'!A:A,0)),IF(K31="Оформление экспортных грузов",INDEX('Экспортные грузы'!J:J,MATCH(A31,'Экспортные грузы'!A:A,0)),IF(K31="Терминальные операции",INDEX(Терминал!J:J,MATCH(A31,Терминал!A:A,0)),IF(K31="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!J:J,MATCH(A31,'ЖД грузы'!A:A,0)),""))))),"")</f>
@@ -5002,11 +4968,11 @@
       </c>
       <c r="H32" s="17" t="str">
         <f>IFERROR(IF(K32="Обработка судовых документов",INDEX('Судовые документы'!H:H,MATCH(A32,'Судовые документы'!A:A,0)),IF(K32="Оформление таможенных документов",INDEX('Таможенные документы'!H:H,MATCH(A32,'Таможенные документы'!A:A,0)),IF(K32="Оформление экспортных грузов",INDEX('Экспортные грузы'!H:H,MATCH(A32,'Экспортные грузы'!A:A,0)),IF(K32="Терминальные операции",INDEX(Терминал!H:H,MATCH(A32,Терминал!A:A,0)),IF(K32="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!H:H,MATCH(A32,'ЖД грузы'!A:A,0)),""))))),"")</f>
-        <v>7.4.10/1</v>
+        <v>Н/Д</v>
       </c>
       <c r="I32" s="18">
         <f>IFERROR(IF(K32="Обработка судовых документов",INDEX('Судовые документы'!I:I,MATCH(A32,'Судовые документы'!A:A,0)),IF(K32="Оформление таможенных документов",INDEX('Таможенные документы'!I:I,MATCH(A32,'Таможенные документы'!A:A,0)),IF(K32="Оформление экспортных грузов",INDEX('Экспортные грузы'!I:I,MATCH(A32,'Экспортные грузы'!A:A,0)),IF(K32="Терминальные операции",INDEX(Терминал!I:I,MATCH(A32,Терминал!A:A,0)),IF(K32="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!I:I,MATCH(A32,'ЖД грузы'!A:A,0)),""))))),"")</f>
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J32" s="16" t="str">
         <f>IFERROR(IF(K32="Обработка судовых документов",INDEX('Судовые документы'!J:J,MATCH(A32,'Судовые документы'!A:A,0)),IF(K32="Оформление таможенных документов",INDEX('Таможенные документы'!J:J,MATCH(A32,'Таможенные документы'!A:A,0)),IF(K32="Оформление экспортных грузов",INDEX('Экспортные грузы'!J:J,MATCH(A32,'Экспортные грузы'!A:A,0)),IF(K32="Терминальные операции",INDEX(Терминал!J:J,MATCH(A32,Терминал!A:A,0)),IF(K32="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!J:J,MATCH(A32,'ЖД грузы'!A:A,0)),""))))),"")</f>
@@ -5053,9 +5019,9 @@
         <f>IFERROR(IF(K33="Обработка судовых документов",INDEX('Судовые документы'!G:G,MATCH(A33,'Судовые документы'!A:A,0)),IF(K33="Оформление таможенных документов",INDEX('Таможенные документы'!G:G,MATCH(A33,'Таможенные документы'!A:A,0)),IF(K33="Оформление экспортных грузов",INDEX('Экспортные грузы'!G:G,MATCH(A33,'Экспортные грузы'!A:A,0)),IF(K33="Терминальные операции",INDEX(Терминал!G:G,MATCH(A33,Терминал!A:A,0)),IF(K33="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!G:G,MATCH(A33,'ЖД грузы'!A:A,0)),""))))),"")</f>
         <v>Не СОЛВО</v>
       </c>
-      <c r="H33" s="8">
+      <c r="H33" s="8" t="str">
         <f>IFERROR(IF(K33="Обработка судовых документов",INDEX('Судовые документы'!H:H,MATCH(A33,'Судовые документы'!A:A,0)),IF(K33="Оформление таможенных документов",INDEX('Таможенные документы'!H:H,MATCH(A33,'Таможенные документы'!A:A,0)),IF(K33="Оформление экспортных грузов",INDEX('Экспортные грузы'!H:H,MATCH(A33,'Экспортные грузы'!A:A,0)),IF(K33="Терминальные операции",INDEX(Терминал!H:H,MATCH(A33,Терминал!A:A,0)),IF(K33="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!H:H,MATCH(A33,'ЖД грузы'!A:A,0)),""))))),"")</f>
-        <v>0</v>
+        <v>Не СОЛВО</v>
       </c>
       <c r="I33" s="9">
         <f>IFERROR(IF(K33="Обработка судовых документов",INDEX('Судовые документы'!I:I,MATCH(A33,'Судовые документы'!A:A,0)),IF(K33="Оформление таможенных документов",INDEX('Таможенные документы'!I:I,MATCH(A33,'Таможенные документы'!A:A,0)),IF(K33="Оформление экспортных грузов",INDEX('Экспортные грузы'!I:I,MATCH(A33,'Экспортные грузы'!A:A,0)),IF(K33="Терминальные операции",INDEX(Терминал!I:I,MATCH(A33,Терминал!A:A,0)),IF(K33="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!I:I,MATCH(A33,'ЖД грузы'!A:A,0)),""))))),"")</f>
@@ -5108,11 +5074,11 @@
       </c>
       <c r="H34" s="17" t="str">
         <f>IFERROR(IF(K34="Обработка судовых документов",INDEX('Судовые документы'!H:H,MATCH(A34,'Судовые документы'!A:A,0)),IF(K34="Оформление таможенных документов",INDEX('Таможенные документы'!H:H,MATCH(A34,'Таможенные документы'!A:A,0)),IF(K34="Оформление экспортных грузов",INDEX('Экспортные грузы'!H:H,MATCH(A34,'Экспортные грузы'!A:A,0)),IF(K34="Терминальные операции",INDEX(Терминал!H:H,MATCH(A34,Терминал!A:A,0)),IF(K34="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!H:H,MATCH(A34,'ЖД грузы'!A:A,0)),""))))),"")</f>
-        <v>7.4.5</v>
+        <v>7.4.7</v>
       </c>
       <c r="I34" s="18">
         <f>IFERROR(IF(K34="Обработка судовых документов",INDEX('Судовые документы'!I:I,MATCH(A34,'Судовые документы'!A:A,0)),IF(K34="Оформление таможенных документов",INDEX('Таможенные документы'!I:I,MATCH(A34,'Таможенные документы'!A:A,0)),IF(K34="Оформление экспортных грузов",INDEX('Экспортные грузы'!I:I,MATCH(A34,'Экспортные грузы'!A:A,0)),IF(K34="Терминальные операции",INDEX(Терминал!I:I,MATCH(A34,Терминал!A:A,0)),IF(K34="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!I:I,MATCH(A34,'ЖД грузы'!A:A,0)),""))))),"")</f>
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="J34" s="16" t="str">
         <f>IFERROR(IF(K34="Обработка судовых документов",INDEX('Судовые документы'!J:J,MATCH(A34,'Судовые документы'!A:A,0)),IF(K34="Оформление таможенных документов",INDEX('Таможенные документы'!J:J,MATCH(A34,'Таможенные документы'!A:A,0)),IF(K34="Оформление экспортных грузов",INDEX('Экспортные грузы'!J:J,MATCH(A34,'Экспортные грузы'!A:A,0)),IF(K34="Терминальные операции",INDEX(Терминал!J:J,MATCH(A34,Терминал!A:A,0)),IF(K34="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!J:J,MATCH(A34,'ЖД грузы'!A:A,0)),""))))),"")</f>
@@ -5169,7 +5135,7 @@
       </c>
       <c r="J35" s="7" t="str">
         <f>IFERROR(IF(K35="Обработка судовых документов",INDEX('Судовые документы'!J:J,MATCH(A35,'Судовые документы'!A:A,0)),IF(K35="Оформление таможенных документов",INDEX('Таможенные документы'!J:J,MATCH(A35,'Таможенные документы'!A:A,0)),IF(K35="Оформление экспортных грузов",INDEX('Экспортные грузы'!J:J,MATCH(A35,'Экспортные грузы'!A:A,0)),IF(K35="Терминальные операции",INDEX(Терминал!J:J,MATCH(A35,Терминал!A:A,0)),IF(K35="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!J:J,MATCH(A35,'ЖД грузы'!A:A,0)),""))))),"")</f>
-        <v>Да</v>
+        <v>Нет</v>
       </c>
       <c r="K35" s="10" t="s">
         <v>22</v>
@@ -5190,7 +5156,7 @@
       </c>
       <c r="B36" s="13" t="str">
         <f>Терминал!B17</f>
-        <v>4SC-RQ-CR-902 #3782828</v>
+        <v>4SC-RQ-CR-902 #3782827</v>
       </c>
       <c r="C36" s="14" t="str">
         <f>Терминал!C17</f>
@@ -5308,7 +5274,7 @@
       </c>
       <c r="E38" s="16" t="str">
         <f>IFERROR(IF(K38="Обработка судовых документов",INDEX('Судовые документы'!E:E,MATCH(A38,'Судовые документы'!A:A,0)),IF(K38="Оформление таможенных документов",INDEX('Таможенные документы'!E:E,MATCH(A38,'Таможенные документы'!A:A,0)),IF(K38="Оформление экспортных грузов",INDEX('Экспортные грузы'!E:E,MATCH(A38,'Экспортные грузы'!A:A,0)),IF(K38="Терминальные операции",INDEX(Терминал!E:E,MATCH(A38,Терминал!A:A,0)),IF(K38="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!E:E,MATCH(A38,'ЖД грузы'!A:A,0)),""))))),"")</f>
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="F38" s="15" t="str">
         <f>IFERROR(IF(K38="Обработка судовых документов",INDEX('Судовые документы'!F:F,MATCH(A38,'Судовые документы'!A:A,0)),IF(K38="Оформление таможенных документов",INDEX('Таможенные документы'!F:F,MATCH(A38,'Таможенные документы'!A:A,0)),IF(K38="Оформление экспортных грузов",INDEX('Экспортные грузы'!F:F,MATCH(A38,'Экспортные грузы'!A:A,0)),IF(K38="Терминальные операции",INDEX(Терминал!F:F,MATCH(A38,Терминал!A:A,0)),IF(K38="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!F:F,MATCH(A38,'ЖД грузы'!A:A,0)),""))))),"")</f>
@@ -5320,7 +5286,7 @@
       </c>
       <c r="H38" s="17" t="str">
         <f>IFERROR(IF(K38="Обработка судовых документов",INDEX('Судовые документы'!H:H,MATCH(A38,'Судовые документы'!A:A,0)),IF(K38="Оформление таможенных документов",INDEX('Таможенные документы'!H:H,MATCH(A38,'Таможенные документы'!A:A,0)),IF(K38="Оформление экспортных грузов",INDEX('Экспортные грузы'!H:H,MATCH(A38,'Экспортные грузы'!A:A,0)),IF(K38="Терминальные операции",INDEX(Терминал!H:H,MATCH(A38,Терминал!A:A,0)),IF(K38="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!H:H,MATCH(A38,'ЖД грузы'!A:A,0)),""))))),"")</f>
-        <v>7.4.12</v>
+        <v>7.4.11</v>
       </c>
       <c r="I38" s="18">
         <f>IFERROR(IF(K38="Обработка судовых документов",INDEX('Судовые документы'!I:I,MATCH(A38,'Судовые документы'!A:A,0)),IF(K38="Оформление таможенных документов",INDEX('Таможенные документы'!I:I,MATCH(A38,'Таможенные документы'!A:A,0)),IF(K38="Оформление экспортных грузов",INDEX('Экспортные грузы'!I:I,MATCH(A38,'Экспортные грузы'!A:A,0)),IF(K38="Терминальные операции",INDEX(Терминал!I:I,MATCH(A38,Терминал!A:A,0)),IF(K38="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!I:I,MATCH(A38,'ЖД грузы'!A:A,0)),""))))),"")</f>
@@ -5349,7 +5315,7 @@
       </c>
       <c r="B39" s="4" t="str">
         <f>Терминал!B20</f>
-        <v>4SC-RQ-CR-812 №3333318</v>
+        <v>4SC-RQ-CR-812 #3333318</v>
       </c>
       <c r="C39" s="5" t="str">
         <f>Терминал!C20</f>
@@ -5377,7 +5343,7 @@
       </c>
       <c r="I39" s="9">
         <f>IFERROR(IF(K39="Обработка судовых документов",INDEX('Судовые документы'!I:I,MATCH(A39,'Судовые документы'!A:A,0)),IF(K39="Оформление таможенных документов",INDEX('Таможенные документы'!I:I,MATCH(A39,'Таможенные документы'!A:A,0)),IF(K39="Оформление экспортных грузов",INDEX('Экспортные грузы'!I:I,MATCH(A39,'Экспортные грузы'!A:A,0)),IF(K39="Терминальные операции",INDEX(Терминал!I:I,MATCH(A39,Терминал!A:A,0)),IF(K39="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!I:I,MATCH(A39,'ЖД грузы'!A:A,0)),""))))),"")</f>
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="J39" s="7" t="str">
         <f>IFERROR(IF(K39="Обработка судовых документов",INDEX('Судовые документы'!J:J,MATCH(A39,'Судовые документы'!A:A,0)),IF(K39="Оформление таможенных документов",INDEX('Таможенные документы'!J:J,MATCH(A39,'Таможенные документы'!A:A,0)),IF(K39="Оформление экспортных грузов",INDEX('Экспортные грузы'!J:J,MATCH(A39,'Экспортные грузы'!A:A,0)),IF(K39="Терминальные операции",INDEX(Терминал!J:J,MATCH(A39,Терминал!A:A,0)),IF(K39="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!J:J,MATCH(A39,'ЖД грузы'!A:A,0)),""))))),"")</f>
@@ -5430,11 +5396,11 @@
       </c>
       <c r="I40" s="18">
         <f>IFERROR(IF(K40="Обработка судовых документов",INDEX('Судовые документы'!I:I,MATCH(A40,'Судовые документы'!A:A,0)),IF(K40="Оформление таможенных документов",INDEX('Таможенные документы'!I:I,MATCH(A40,'Таможенные документы'!A:A,0)),IF(K40="Оформление экспортных грузов",INDEX('Экспортные грузы'!I:I,MATCH(A40,'Экспортные грузы'!A:A,0)),IF(K40="Терминальные операции",INDEX(Терминал!I:I,MATCH(A40,Терминал!A:A,0)),IF(K40="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!I:I,MATCH(A40,'ЖД грузы'!A:A,0)),""))))),"")</f>
-        <v>140</v>
+        <v>254</v>
       </c>
       <c r="J40" s="16" t="str">
         <f>IFERROR(IF(K40="Обработка судовых документов",INDEX('Судовые документы'!J:J,MATCH(A40,'Судовые документы'!A:A,0)),IF(K40="Оформление таможенных документов",INDEX('Таможенные документы'!J:J,MATCH(A40,'Таможенные документы'!A:A,0)),IF(K40="Оформление экспортных грузов",INDEX('Экспортные грузы'!J:J,MATCH(A40,'Экспортные грузы'!A:A,0)),IF(K40="Терминальные операции",INDEX(Терминал!J:J,MATCH(A40,Терминал!A:A,0)),IF(K40="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!J:J,MATCH(A40,'ЖД грузы'!A:A,0)),""))))),"")</f>
-        <v>Нет</v>
+        <v>Да</v>
       </c>
       <c r="K40" s="19" t="s">
         <v>22</v>
@@ -5449,21 +5415,21 @@
       </c>
     </row>
     <row r="41" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="129" t="s">
+      <c r="A41" s="122" t="s">
         <v>23</v>
       </c>
-      <c r="B41" s="122"/>
-      <c r="C41" s="122"/>
-      <c r="D41" s="122"/>
-      <c r="E41" s="122"/>
-      <c r="F41" s="122"/>
-      <c r="G41" s="122"/>
-      <c r="H41" s="122"/>
-      <c r="I41" s="122"/>
-      <c r="J41" s="122"/>
-      <c r="K41" s="122"/>
-      <c r="L41" s="122"/>
-      <c r="M41" s="122"/>
+      <c r="B41" s="115"/>
+      <c r="C41" s="115"/>
+      <c r="D41" s="115"/>
+      <c r="E41" s="115"/>
+      <c r="F41" s="115"/>
+      <c r="G41" s="115"/>
+      <c r="H41" s="115"/>
+      <c r="I41" s="115"/>
+      <c r="J41" s="115"/>
+      <c r="K41" s="115"/>
+      <c r="L41" s="115"/>
+      <c r="M41" s="115"/>
     </row>
     <row r="42" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
@@ -5576,9 +5542,9 @@
         <f>'ЖД грузы'!A8</f>
         <v>36</v>
       </c>
-      <c r="B44" s="4" t="str">
+      <c r="B44" s="4">
         <f>'ЖД грузы'!B8</f>
-        <v>4SC-RQ-CR-951 #3940390</v>
+        <v>0</v>
       </c>
       <c r="C44" s="5" t="str">
         <f>'ЖД грузы'!C8</f>
@@ -5602,11 +5568,11 @@
       </c>
       <c r="H44" s="8" t="str">
         <f>IFERROR(IF(K44="Обработка судовых документов",INDEX('Судовые документы'!H:H,MATCH(A44,'Судовые документы'!A:A,0)),IF(K44="Оформление таможенных документов",INDEX('Таможенные документы'!H:H,MATCH(A44,'Таможенные документы'!A:A,0)),IF(K44="Оформление экспортных грузов",INDEX('Экспортные грузы'!H:H,MATCH(A44,'Экспортные грузы'!A:A,0)),IF(K44="Терминальные операции",INDEX(Терминал!H:H,MATCH(A44,Терминал!A:A,0)),IF(K44="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!H:H,MATCH(A44,'ЖД грузы'!A:A,0)),""))))),"")</f>
-        <v>7.4.12</v>
+        <v>Н/Д</v>
       </c>
       <c r="I44" s="9">
         <f>IFERROR(IF(K44="Обработка судовых документов",INDEX('Судовые документы'!I:I,MATCH(A44,'Судовые документы'!A:A,0)),IF(K44="Оформление таможенных документов",INDEX('Таможенные документы'!I:I,MATCH(A44,'Таможенные документы'!A:A,0)),IF(K44="Оформление экспортных грузов",INDEX('Экспортные грузы'!I:I,MATCH(A44,'Экспортные грузы'!A:A,0)),IF(K44="Терминальные операции",INDEX(Терминал!I:I,MATCH(A44,Терминал!A:A,0)),IF(K44="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!I:I,MATCH(A44,'ЖД грузы'!A:A,0)),""))))),"")</f>
-        <v>860</v>
+        <v>0</v>
       </c>
       <c r="J44" s="7" t="str">
         <f>IFERROR(IF(K44="Обработка судовых документов",INDEX('Судовые документы'!J:J,MATCH(A44,'Судовые документы'!A:A,0)),IF(K44="Оформление таможенных документов",INDEX('Таможенные документы'!J:J,MATCH(A44,'Таможенные документы'!A:A,0)),IF(K44="Оформление экспортных грузов",INDEX('Экспортные грузы'!J:J,MATCH(A44,'Экспортные грузы'!A:A,0)),IF(K44="Терминальные операции",INDEX(Терминал!J:J,MATCH(A44,Терминал!A:A,0)),IF(K44="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!J:J,MATCH(A44,'ЖД грузы'!A:A,0)),""))))),"")</f>
@@ -5659,7 +5625,7 @@
       </c>
       <c r="I45" s="18">
         <f>IFERROR(IF(K45="Обработка судовых документов",INDEX('Судовые документы'!I:I,MATCH(A45,'Судовые документы'!A:A,0)),IF(K45="Оформление таможенных документов",INDEX('Таможенные документы'!I:I,MATCH(A45,'Таможенные документы'!A:A,0)),IF(K45="Оформление экспортных грузов",INDEX('Экспортные грузы'!I:I,MATCH(A45,'Экспортные грузы'!A:A,0)),IF(K45="Терминальные операции",INDEX(Терминал!I:I,MATCH(A45,Терминал!A:A,0)),IF(K45="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!I:I,MATCH(A45,'ЖД грузы'!A:A,0)),""))))),"")</f>
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="J45" s="16" t="str">
         <f>IFERROR(IF(K45="Обработка судовых документов",INDEX('Судовые документы'!J:J,MATCH(A45,'Судовые документы'!A:A,0)),IF(K45="Оформление таможенных документов",INDEX('Таможенные документы'!J:J,MATCH(A45,'Таможенные документы'!A:A,0)),IF(K45="Оформление экспортных грузов",INDEX('Экспортные грузы'!J:J,MATCH(A45,'Экспортные грузы'!A:A,0)),IF(K45="Терминальные операции",INDEX(Терминал!J:J,MATCH(A45,Терминал!A:A,0)),IF(K45="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!J:J,MATCH(A45,'ЖД грузы'!A:A,0)),""))))),"")</f>
@@ -5684,7 +5650,7 @@
       </c>
       <c r="B46" s="4" t="str">
         <f>'ЖД грузы'!B10</f>
-        <v>4SC-RQ-CR-933 #3895614</v>
+        <v>#3895614</v>
       </c>
       <c r="C46" s="5" t="str">
         <f>'ЖД грузы'!C10</f>
@@ -5765,7 +5731,7 @@
       </c>
       <c r="I47" s="18">
         <f>IFERROR(IF(K47="Обработка судовых документов",INDEX('Судовые документы'!I:I,MATCH(A47,'Судовые документы'!A:A,0)),IF(K47="Оформление таможенных документов",INDEX('Таможенные документы'!I:I,MATCH(A47,'Таможенные документы'!A:A,0)),IF(K47="Оформление экспортных грузов",INDEX('Экспортные грузы'!I:I,MATCH(A47,'Экспортные грузы'!A:A,0)),IF(K47="Терминальные операции",INDEX(Терминал!I:I,MATCH(A47,Терминал!A:A,0)),IF(K47="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!I:I,MATCH(A47,'ЖД грузы'!A:A,0)),""))))),"")</f>
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J47" s="16" t="str">
         <f>IFERROR(IF(K47="Обработка судовых документов",INDEX('Судовые документы'!J:J,MATCH(A47,'Судовые документы'!A:A,0)),IF(K47="Оформление таможенных документов",INDEX('Таможенные документы'!J:J,MATCH(A47,'Таможенные документы'!A:A,0)),IF(K47="Оформление экспортных грузов",INDEX('Экспортные грузы'!J:J,MATCH(A47,'Экспортные грузы'!A:A,0)),IF(K47="Терминальные операции",INDEX(Терминал!J:J,MATCH(A47,Терминал!A:A,0)),IF(K47="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!J:J,MATCH(A47,'ЖД грузы'!A:A,0)),""))))),"")</f>
@@ -5818,7 +5784,7 @@
       </c>
       <c r="I48" s="9">
         <f>IFERROR(IF(K48="Обработка судовых документов",INDEX('Судовые документы'!I:I,MATCH(A48,'Судовые документы'!A:A,0)),IF(K48="Оформление таможенных документов",INDEX('Таможенные документы'!I:I,MATCH(A48,'Таможенные документы'!A:A,0)),IF(K48="Оформление экспортных грузов",INDEX('Экспортные грузы'!I:I,MATCH(A48,'Экспортные грузы'!A:A,0)),IF(K48="Терминальные операции",INDEX(Терминал!I:I,MATCH(A48,Терминал!A:A,0)),IF(K48="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!I:I,MATCH(A48,'ЖД грузы'!A:A,0)),""))))),"")</f>
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="J48" s="7" t="str">
         <f>IFERROR(IF(K48="Обработка судовых документов",INDEX('Судовые документы'!J:J,MATCH(A48,'Судовые документы'!A:A,0)),IF(K48="Оформление таможенных документов",INDEX('Таможенные документы'!J:J,MATCH(A48,'Таможенные документы'!A:A,0)),IF(K48="Оформление экспортных грузов",INDEX('Экспортные грузы'!J:J,MATCH(A48,'Экспортные грузы'!A:A,0)),IF(K48="Терминальные операции",INDEX(Терминал!J:J,MATCH(A48,Терминал!A:A,0)),IF(K48="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!J:J,MATCH(A48,'ЖД грузы'!A:A,0)),""))))),"")</f>
@@ -5871,7 +5837,7 @@
       </c>
       <c r="I49" s="18">
         <f>IFERROR(IF(K49="Обработка судовых документов",INDEX('Судовые документы'!I:I,MATCH(A49,'Судовые документы'!A:A,0)),IF(K49="Оформление таможенных документов",INDEX('Таможенные документы'!I:I,MATCH(A49,'Таможенные документы'!A:A,0)),IF(K49="Оформление экспортных грузов",INDEX('Экспортные грузы'!I:I,MATCH(A49,'Экспортные грузы'!A:A,0)),IF(K49="Терминальные операции",INDEX(Терминал!I:I,MATCH(A49,Терминал!A:A,0)),IF(K49="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!I:I,MATCH(A49,'ЖД грузы'!A:A,0)),""))))),"")</f>
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J49" s="16" t="str">
         <f>IFERROR(IF(K49="Обработка судовых документов",INDEX('Судовые документы'!J:J,MATCH(A49,'Судовые документы'!A:A,0)),IF(K49="Оформление таможенных документов",INDEX('Таможенные документы'!J:J,MATCH(A49,'Таможенные документы'!A:A,0)),IF(K49="Оформление экспортных грузов",INDEX('Экспортные грузы'!J:J,MATCH(A49,'Экспортные грузы'!A:A,0)),IF(K49="Терминальные операции",INDEX(Терминал!J:J,MATCH(A49,Терминал!A:A,0)),IF(K49="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!J:J,MATCH(A49,'ЖД грузы'!A:A,0)),""))))),"")</f>
@@ -5924,7 +5890,7 @@
       </c>
       <c r="I50" s="9">
         <f>IFERROR(IF(K50="Обработка судовых документов",INDEX('Судовые документы'!I:I,MATCH(A50,'Судовые документы'!A:A,0)),IF(K50="Оформление таможенных документов",INDEX('Таможенные документы'!I:I,MATCH(A50,'Таможенные документы'!A:A,0)),IF(K50="Оформление экспортных грузов",INDEX('Экспортные грузы'!I:I,MATCH(A50,'Экспортные грузы'!A:A,0)),IF(K50="Терминальные операции",INDEX(Терминал!I:I,MATCH(A50,Терминал!A:A,0)),IF(K50="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!I:I,MATCH(A50,'ЖД грузы'!A:A,0)),""))))),"")</f>
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J50" s="7" t="str">
         <f>IFERROR(IF(K50="Обработка судовых документов",INDEX('Судовые документы'!J:J,MATCH(A50,'Судовые документы'!A:A,0)),IF(K50="Оформление таможенных документов",INDEX('Таможенные документы'!J:J,MATCH(A50,'Таможенные документы'!A:A,0)),IF(K50="Оформление экспортных грузов",INDEX('Экспортные грузы'!J:J,MATCH(A50,'Экспортные грузы'!A:A,0)),IF(K50="Терминальные операции",INDEX(Терминал!J:J,MATCH(A50,Терминал!A:A,0)),IF(K50="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!J:J,MATCH(A50,'ЖД грузы'!A:A,0)),""))))),"")</f>
@@ -5977,7 +5943,7 @@
       </c>
       <c r="I51" s="18">
         <f>IFERROR(IF(K51="Обработка судовых документов",INDEX('Судовые документы'!I:I,MATCH(A51,'Судовые документы'!A:A,0)),IF(K51="Оформление таможенных документов",INDEX('Таможенные документы'!I:I,MATCH(A51,'Таможенные документы'!A:A,0)),IF(K51="Оформление экспортных грузов",INDEX('Экспортные грузы'!I:I,MATCH(A51,'Экспортные грузы'!A:A,0)),IF(K51="Терминальные операции",INDEX(Терминал!I:I,MATCH(A51,Терминал!A:A,0)),IF(K51="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!I:I,MATCH(A51,'ЖД грузы'!A:A,0)),""))))),"")</f>
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J51" s="16" t="str">
         <f>IFERROR(IF(K51="Обработка судовых документов",INDEX('Судовые документы'!J:J,MATCH(A51,'Судовые документы'!A:A,0)),IF(K51="Оформление таможенных документов",INDEX('Таможенные документы'!J:J,MATCH(A51,'Таможенные документы'!A:A,0)),IF(K51="Оформление экспортных грузов",INDEX('Экспортные грузы'!J:J,MATCH(A51,'Экспортные грузы'!A:A,0)),IF(K51="Терминальные операции",INDEX(Терминал!J:J,MATCH(A51,Терминал!A:A,0)),IF(K51="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!J:J,MATCH(A51,'ЖД грузы'!A:A,0)),""))))),"")</f>
@@ -5996,19 +5962,19 @@
       </c>
     </row>
     <row r="52" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="127" t="s">
+      <c r="A52" s="120" t="s">
         <v>25</v>
       </c>
-      <c r="B52" s="122"/>
-      <c r="C52" s="122"/>
-      <c r="D52" s="122"/>
-      <c r="E52" s="122"/>
-      <c r="F52" s="122"/>
-      <c r="G52" s="122"/>
-      <c r="H52" s="128"/>
-      <c r="I52" s="103">
+      <c r="B52" s="115"/>
+      <c r="C52" s="115"/>
+      <c r="D52" s="115"/>
+      <c r="E52" s="115"/>
+      <c r="F52" s="115"/>
+      <c r="G52" s="115"/>
+      <c r="H52" s="121"/>
+      <c r="I52" s="102">
         <f>SUM('Судовые документы'!I6:I12)+SUM('Таможенные документы'!I6:I10)+SUM('Экспортные грузы'!I6:I10)+SUM(Терминал!I6:I21)+SUM('ЖД грузы'!I6:I15)</f>
-        <v>6385</v>
+        <v>3231</v>
       </c>
       <c r="J52" s="21"/>
       <c r="K52" s="21"/>
@@ -6058,51 +6024,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="125" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="120"/>
-      <c r="C1" s="120"/>
-      <c r="D1" s="120"/>
-      <c r="E1" s="120"/>
-      <c r="F1" s="120"/>
-      <c r="G1" s="120"/>
-      <c r="H1" s="120"/>
-      <c r="I1" s="120"/>
-      <c r="J1" s="120"/>
-      <c r="K1" s="120"/>
-      <c r="L1" s="120"/>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
+      <c r="I1" s="113"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="130" t="s">
+      <c r="A2" s="123" t="s">
         <v>60</v>
       </c>
-      <c r="B2" s="120"/>
-      <c r="C2" s="120"/>
-      <c r="D2" s="120"/>
-      <c r="E2" s="120"/>
-      <c r="F2" s="120"/>
-      <c r="G2" s="120"/>
-      <c r="H2" s="120"/>
-      <c r="I2" s="120"/>
-      <c r="J2" s="120"/>
-      <c r="K2" s="120"/>
-      <c r="L2" s="120"/>
+      <c r="B2" s="113"/>
+      <c r="C2" s="113"/>
+      <c r="D2" s="113"/>
+      <c r="E2" s="113"/>
+      <c r="F2" s="113"/>
+      <c r="G2" s="113"/>
+      <c r="H2" s="113"/>
+      <c r="I2" s="113"/>
+      <c r="J2" s="113"/>
+      <c r="K2" s="113"/>
+      <c r="L2" s="113"/>
     </row>
     <row r="3" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="53" t="s">
+      <c r="A3" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="54" t="s">
+      <c r="B3" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="55" t="s">
+      <c r="C3" s="54" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="56" t="s">
+      <c r="D3" s="55" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="57" t="s">
+      <c r="E3" s="56" t="s">
         <v>34</v>
       </c>
       <c r="G3" s="23"/>
@@ -6112,25 +6078,25 @@
       <c r="K3" s="23"/>
     </row>
     <row r="4" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="58">
+      <c r="A4" s="57">
         <f>COUNTA(A6:A12)</f>
         <v>7</v>
       </c>
-      <c r="B4" s="59">
+      <c r="B4" s="58">
         <f>COUNTIF(G6:G12,"Установлено")+COUNTIF(G6:G12,"Не СОЛВО")+COUNTIF(G6:G12,"Выполнено")</f>
-        <v>3</v>
-      </c>
-      <c r="C4" s="60">
+        <v>2</v>
+      </c>
+      <c r="C4" s="59">
         <f>COUNTIF(G6:G12,"В работе")+COUNTIF(G6:G12,"Тестирование")+COUNTIF(G6:G12,"Разработка")+COUNTIF(G6:G12,"ОПЭ")+COUNTIF(G6:G12,"На приемке")</f>
         <v>3</v>
       </c>
-      <c r="D4" s="118">
+      <c r="D4" s="108">
         <f>SUM(I6:I12)</f>
-        <v>553</v>
-      </c>
-      <c r="E4" s="61">
+        <v>513</v>
+      </c>
+      <c r="E4" s="60">
         <f>IF(COUNTA(A6:A12)=0,0,(COUNTIF(G6:G12,"Установлено")+COUNTIF(G6:G12,"Не СОЛВО")+COUNTIF(G6:G12,"Выполнено"))/COUNTA(A6:A12))</f>
-        <v>0.42857142857142855</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="G4" s="23"/>
       <c r="H4" s="23"/>
@@ -6139,40 +6105,40 @@
       <c r="K4" s="23"/>
     </row>
     <row r="5" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="84" t="s">
+      <c r="A5" s="83" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="84" t="s">
+      <c r="B5" s="83" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="84" t="s">
+      <c r="C5" s="83" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="84" t="s">
+      <c r="D5" s="83" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="84" t="s">
+      <c r="E5" s="83" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="85" t="s">
+      <c r="F5" s="84" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="85" t="s">
+      <c r="G5" s="84" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="84" t="s">
+      <c r="H5" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="84" t="s">
+      <c r="I5" s="83" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="85" t="s">
+      <c r="J5" s="84" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="84" t="s">
+      <c r="K5" s="83" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="84" t="s">
+      <c r="L5" s="83" t="s">
         <v>13</v>
       </c>
     </row>
@@ -6180,22 +6146,22 @@
       <c r="A6" s="3">
         <v>1</v>
       </c>
-      <c r="B6" s="62" t="s">
+      <c r="B6" s="61" t="s">
         <v>61</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="D6" s="63" t="s">
+      <c r="D6" s="62" t="s">
         <v>63</v>
       </c>
-      <c r="E6" s="64" t="s">
+      <c r="E6" s="63" t="s">
         <v>64</v>
       </c>
-      <c r="F6" s="94" t="s">
+      <c r="F6" s="93" t="s">
         <v>29</v>
       </c>
-      <c r="G6" s="95" t="s">
+      <c r="G6" s="94" t="s">
         <v>42</v>
       </c>
       <c r="H6" s="8" t="s">
@@ -6204,11 +6170,11 @@
       <c r="I6" s="9">
         <v>235</v>
       </c>
-      <c r="J6" s="65" t="s">
-        <v>69</v>
-      </c>
-      <c r="K6" s="66"/>
-      <c r="L6" s="82" t="s">
+      <c r="J6" s="64" t="s">
+        <v>68</v>
+      </c>
+      <c r="K6" s="65"/>
+      <c r="L6" s="81" t="s">
         <v>66</v>
       </c>
     </row>
@@ -6216,33 +6182,33 @@
       <c r="A7" s="12">
         <v>2</v>
       </c>
-      <c r="B7" s="67" t="s">
-        <v>67</v>
+      <c r="B7" s="66">
+        <v>3323631</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="D7" s="68" t="s">
-        <v>68</v>
-      </c>
-      <c r="E7" s="69" t="s">
+      <c r="D7" s="67" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" s="68" t="s">
         <v>64</v>
       </c>
-      <c r="F7" s="94" t="s">
+      <c r="F7" s="93" t="s">
         <v>53</v>
       </c>
-      <c r="G7" s="95" t="s">
+      <c r="G7" s="94" t="s">
         <v>42</v>
       </c>
       <c r="H7" s="17" t="s">
         <v>48</v>
       </c>
       <c r="I7" s="18"/>
-      <c r="J7" s="70" t="s">
+      <c r="J7" s="69" t="s">
         <v>65</v>
       </c>
-      <c r="K7" s="71"/>
-      <c r="L7" s="83" t="s">
+      <c r="K7" s="70"/>
+      <c r="L7" s="82" t="s">
         <v>66</v>
       </c>
     </row>
@@ -6250,22 +6216,22 @@
       <c r="A8" s="3">
         <v>3</v>
       </c>
-      <c r="B8" s="62" t="s">
+      <c r="B8" s="61" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="D8" s="62" t="s">
         <v>71</v>
       </c>
-      <c r="D8" s="63" t="s">
-        <v>72</v>
-      </c>
-      <c r="E8" s="64" t="s">
+      <c r="E8" s="63" t="s">
         <v>40</v>
       </c>
-      <c r="F8" s="96" t="s">
+      <c r="F8" s="95" t="s">
         <v>40</v>
       </c>
-      <c r="G8" s="97" t="s">
+      <c r="G8" s="96" t="s">
         <v>38</v>
       </c>
       <c r="H8" s="8" t="s">
@@ -6274,11 +6240,11 @@
       <c r="I8" s="9">
         <v>144</v>
       </c>
-      <c r="J8" s="65" t="s">
-        <v>69</v>
-      </c>
-      <c r="K8" s="66"/>
-      <c r="L8" s="82" t="s">
+      <c r="J8" s="64" t="s">
+        <v>68</v>
+      </c>
+      <c r="K8" s="65"/>
+      <c r="L8" s="81" t="s">
         <v>66</v>
       </c>
     </row>
@@ -6286,31 +6252,35 @@
       <c r="A9" s="12">
         <v>4</v>
       </c>
-      <c r="B9" s="67" t="s">
+      <c r="B9" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="D9" s="67" t="s">
         <v>74</v>
       </c>
-      <c r="D9" s="68" t="s">
+      <c r="E9" s="68" t="s">
         <v>75</v>
       </c>
-      <c r="E9" s="69" t="s">
-        <v>76</v>
-      </c>
-      <c r="F9" s="97" t="s">
+      <c r="F9" s="96" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="98" t="s">
-        <v>56</v>
-      </c>
-      <c r="H9" s="17"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="70" t="s">
-        <v>69</v>
-      </c>
-      <c r="K9" s="71"/>
-      <c r="L9" s="83" t="s">
+      <c r="G9" s="97" t="s">
+        <v>216</v>
+      </c>
+      <c r="H9" s="44" t="s">
+        <v>41</v>
+      </c>
+      <c r="I9" s="18">
+        <v>110</v>
+      </c>
+      <c r="J9" s="69" t="s">
+        <v>68</v>
+      </c>
+      <c r="K9" s="70"/>
+      <c r="L9" s="82" t="s">
         <v>66</v>
       </c>
     </row>
@@ -6318,29 +6288,31 @@
       <c r="A10" s="3">
         <v>5</v>
       </c>
-      <c r="B10" s="62"/>
+      <c r="B10" s="61"/>
       <c r="C10" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D10" s="62" t="s">
         <v>77</v>
       </c>
-      <c r="D10" s="63" t="s">
-        <v>78</v>
-      </c>
-      <c r="E10" s="64" t="s">
-        <v>76</v>
-      </c>
-      <c r="F10" s="97" t="s">
+      <c r="E10" s="63" t="s">
+        <v>75</v>
+      </c>
+      <c r="F10" s="96" t="s">
         <v>28</v>
       </c>
-      <c r="G10" s="98" t="s">
+      <c r="G10" s="97" t="s">
         <v>56</v>
       </c>
-      <c r="H10" s="8"/>
+      <c r="H10" s="8" t="s">
+        <v>56</v>
+      </c>
       <c r="I10" s="9"/>
-      <c r="J10" s="65" t="s">
-        <v>69</v>
-      </c>
-      <c r="K10" s="66"/>
-      <c r="L10" s="82" t="s">
+      <c r="J10" s="64" t="s">
+        <v>68</v>
+      </c>
+      <c r="K10" s="65"/>
+      <c r="L10" s="81" t="s">
         <v>66</v>
       </c>
     </row>
@@ -6348,35 +6320,35 @@
       <c r="A11" s="12">
         <v>6</v>
       </c>
-      <c r="B11" s="67" t="s">
+      <c r="B11" s="66" t="s">
+        <v>78</v>
+      </c>
+      <c r="C11" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="D11" s="67" t="s">
         <v>80</v>
       </c>
-      <c r="D11" s="68" t="s">
-        <v>81</v>
-      </c>
-      <c r="E11" s="69" t="s">
+      <c r="E11" s="68" t="s">
         <v>64</v>
       </c>
-      <c r="F11" s="94" t="s">
+      <c r="F11" s="93" t="s">
         <v>29</v>
       </c>
-      <c r="G11" s="94" t="s">
+      <c r="G11" s="93" t="s">
         <v>45</v>
       </c>
       <c r="H11" s="17" t="s">
         <v>48</v>
       </c>
       <c r="I11" s="18">
-        <v>34</v>
-      </c>
-      <c r="J11" s="70" t="s">
-        <v>69</v>
-      </c>
-      <c r="K11" s="71"/>
-      <c r="L11" s="83" t="s">
+        <v>24</v>
+      </c>
+      <c r="J11" s="69" t="s">
+        <v>68</v>
+      </c>
+      <c r="K11" s="70"/>
+      <c r="L11" s="82" t="s">
         <v>66</v>
       </c>
     </row>
@@ -6384,55 +6356,53 @@
       <c r="A12" s="3">
         <v>7</v>
       </c>
-      <c r="B12" s="62" t="s">
+      <c r="B12" s="61" t="s">
+        <v>81</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="D12" s="62" t="s">
         <v>83</v>
       </c>
-      <c r="D12" s="63" t="s">
-        <v>84</v>
-      </c>
-      <c r="E12" s="64" t="s">
-        <v>85</v>
-      </c>
-      <c r="F12" s="94" t="s">
+      <c r="E12" s="63">
+        <v>2026</v>
+      </c>
+      <c r="F12" s="93" t="s">
         <v>29</v>
       </c>
-      <c r="G12" s="99" t="s">
+      <c r="G12" s="98" t="s">
         <v>47</v>
       </c>
       <c r="H12" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I12" s="9">
-        <v>140</v>
-      </c>
-      <c r="J12" s="72" t="s">
+      <c r="I12" s="9"/>
+      <c r="J12" s="71" t="s">
         <v>65</v>
       </c>
-      <c r="K12" s="66"/>
-      <c r="L12" s="82" t="s">
+      <c r="K12" s="65"/>
+      <c r="L12" s="81" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="131" t="s">
-        <v>86</v>
-      </c>
-      <c r="B13" s="122"/>
-      <c r="C13" s="122"/>
-      <c r="D13" s="122"/>
-      <c r="E13" s="122"/>
-      <c r="F13" s="122"/>
-      <c r="G13" s="122"/>
-      <c r="H13" s="128"/>
-      <c r="I13" s="115">
+      <c r="A13" s="124" t="s">
+        <v>85</v>
+      </c>
+      <c r="B13" s="115"/>
+      <c r="C13" s="115"/>
+      <c r="D13" s="115"/>
+      <c r="E13" s="115"/>
+      <c r="F13" s="115"/>
+      <c r="G13" s="115"/>
+      <c r="H13" s="121"/>
+      <c r="I13" s="105">
         <f>SUM(I6:I12)</f>
-        <v>553</v>
-      </c>
-      <c r="J13" s="86"/>
-      <c r="K13" s="86"/>
+        <v>513</v>
+      </c>
+      <c r="J13" s="85"/>
+      <c r="K13" s="85"/>
     </row>
     <row r="14" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="23"/>
@@ -6455,60 +6425,60 @@
     <mergeCell ref="A1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="F6:F1000">
-    <cfRule type="cellIs" dxfId="86" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="79" priority="21" operator="equal">
       <formula>"Согласовано"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="85" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="78" priority="22" operator="equal">
       <formula>"Закрыто"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="84" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="77" priority="23" operator="equal">
       <formula>"В работе"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="83" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="76" priority="24" operator="equal">
       <formula>"На согласовании"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6:G1000">
-    <cfRule type="cellIs" dxfId="82" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="75" priority="25" operator="equal">
       <formula>"Ошибка"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="81" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="74" priority="26" operator="equal">
       <formula>"Отменено"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G6:G1000">
-    <cfRule type="cellIs" dxfId="80" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="73" priority="27" operator="equal">
       <formula>"Установлено"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="79" priority="28" operator="equal">
+    <cfRule type="cellIs" dxfId="72" priority="28" operator="equal">
       <formula>"Разработка"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="78" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="71" priority="29" operator="equal">
       <formula>"Тестирование"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="77" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="70" priority="30" operator="equal">
       <formula>"На приемке"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="76" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="69" priority="31" operator="equal">
       <formula>"ОПЭ"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J6:J12">
-    <cfRule type="cellIs" dxfId="75" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="68" priority="1" operator="equal">
       <formula>"Нет"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="74" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="67" priority="2" operator="equal">
       <formula>"Да"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L6:L1000">
-    <cfRule type="cellIs" dxfId="73" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="34" operator="equal">
       <formula>"Высокий"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="72" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="65" priority="35" operator="equal">
       <formula>"Средний"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="71" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="36" operator="equal">
       <formula>"Низкий"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6519,6 +6489,9 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="H8" twoDigitTextYear="1"/>
+  </ignoredErrors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
@@ -6568,51 +6541,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="134" t="s">
-        <v>87</v>
-      </c>
-      <c r="B1" s="120"/>
-      <c r="C1" s="120"/>
-      <c r="D1" s="120"/>
-      <c r="E1" s="120"/>
-      <c r="F1" s="120"/>
-      <c r="G1" s="120"/>
-      <c r="H1" s="120"/>
-      <c r="I1" s="120"/>
-      <c r="J1" s="120"/>
-      <c r="K1" s="120"/>
-      <c r="L1" s="120"/>
+      <c r="A1" s="127" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
+      <c r="I1" s="113"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="130" t="s">
+      <c r="A2" s="123" t="s">
         <v>60</v>
       </c>
-      <c r="B2" s="120"/>
-      <c r="C2" s="120"/>
-      <c r="D2" s="120"/>
-      <c r="E2" s="120"/>
-      <c r="F2" s="120"/>
-      <c r="G2" s="120"/>
-      <c r="H2" s="120"/>
-      <c r="I2" s="120"/>
-      <c r="J2" s="120"/>
-      <c r="K2" s="120"/>
-      <c r="L2" s="120"/>
+      <c r="B2" s="113"/>
+      <c r="C2" s="113"/>
+      <c r="D2" s="113"/>
+      <c r="E2" s="113"/>
+      <c r="F2" s="113"/>
+      <c r="G2" s="113"/>
+      <c r="H2" s="113"/>
+      <c r="I2" s="113"/>
+      <c r="J2" s="113"/>
+      <c r="K2" s="113"/>
+      <c r="L2" s="113"/>
     </row>
     <row r="3" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="53" t="s">
+      <c r="A3" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="54" t="s">
+      <c r="B3" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="55" t="s">
+      <c r="C3" s="54" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="56" t="s">
+      <c r="D3" s="55" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="57" t="s">
+      <c r="E3" s="56" t="s">
         <v>34</v>
       </c>
       <c r="G3" s="23"/>
@@ -6622,23 +6595,23 @@
       <c r="K3" s="23"/>
     </row>
     <row r="4" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="58">
+      <c r="A4" s="57">
         <f>COUNTA(A6:A10)</f>
         <v>5</v>
       </c>
-      <c r="B4" s="59">
+      <c r="B4" s="58">
         <f>COUNTIF(G6:G10,"Установлено")+COUNTIF(G6:G10,"Не СОЛВО")+COUNTIF(G6:G10,"Выполнено")</f>
         <v>1</v>
       </c>
-      <c r="C4" s="60">
+      <c r="C4" s="59">
         <f>COUNTIF(G6:G10,"В работе")+COUNTIF(G6:G10,"Тестирование")+COUNTIF(G6:G10,"Разработка")+COUNTIF(G6:G10,"ОПЭ")+COUNTIF(G6:G10,"На приемке")</f>
         <v>0</v>
       </c>
-      <c r="D4" s="118">
+      <c r="D4" s="108">
         <f>SUM(I6:I10)</f>
-        <v>2400</v>
-      </c>
-      <c r="E4" s="61">
+        <v>780</v>
+      </c>
+      <c r="E4" s="60">
         <f>IF(COUNTA(A6:A10)=0,0,(COUNTIF(G6:G10,"Установлено")+COUNTIF(G6:G10,"Не СОЛВО")+COUNTIF(G6:G10,"Выполнено"))/COUNTA(A6:A10))</f>
         <v>0.2</v>
       </c>
@@ -6649,40 +6622,40 @@
       <c r="K4" s="23"/>
     </row>
     <row r="5" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="87" t="s">
+      <c r="A5" s="86" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="87" t="s">
+      <c r="B5" s="86" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="87" t="s">
+      <c r="C5" s="86" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="87" t="s">
+      <c r="D5" s="86" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="87" t="s">
+      <c r="E5" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="87" t="s">
+      <c r="F5" s="86" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="87" t="s">
+      <c r="G5" s="86" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="87" t="s">
+      <c r="H5" s="86" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="87" t="s">
+      <c r="I5" s="86" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="87" t="s">
+      <c r="J5" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="87" t="s">
+      <c r="K5" s="86" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="87" t="s">
+      <c r="L5" s="86" t="s">
         <v>13</v>
       </c>
     </row>
@@ -6690,22 +6663,22 @@
       <c r="A6" s="3">
         <v>8</v>
       </c>
-      <c r="B6" s="62" t="s">
+      <c r="B6" s="61" t="s">
+        <v>87</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="62" t="s">
         <v>89</v>
       </c>
-      <c r="D6" s="63" t="s">
-        <v>90</v>
-      </c>
-      <c r="E6" s="64" t="s">
-        <v>76</v>
-      </c>
-      <c r="F6" s="94" t="s">
+      <c r="E6" s="63" t="s">
+        <v>75</v>
+      </c>
+      <c r="F6" s="93" t="s">
         <v>29</v>
       </c>
-      <c r="G6" s="97" t="s">
+      <c r="G6" s="96" t="s">
         <v>38</v>
       </c>
       <c r="H6" s="8" t="s">
@@ -6714,11 +6687,11 @@
       <c r="I6" s="9">
         <v>780</v>
       </c>
-      <c r="J6" s="65" t="s">
-        <v>69</v>
-      </c>
-      <c r="K6" s="66"/>
-      <c r="L6" s="82" t="s">
+      <c r="J6" s="64" t="s">
+        <v>68</v>
+      </c>
+      <c r="K6" s="65"/>
+      <c r="L6" s="81" t="s">
         <v>66</v>
       </c>
     </row>
@@ -6726,35 +6699,33 @@
       <c r="A7" s="12">
         <v>9</v>
       </c>
-      <c r="B7" s="67" t="s">
+      <c r="B7" s="66" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="D7" s="67" t="s">
         <v>93</v>
       </c>
-      <c r="D7" s="68" t="s">
-        <v>94</v>
-      </c>
-      <c r="E7" s="69" t="s">
-        <v>85</v>
-      </c>
-      <c r="F7" s="94" t="s">
+      <c r="E7" s="68" t="s">
+        <v>84</v>
+      </c>
+      <c r="F7" s="93" t="s">
         <v>29</v>
       </c>
-      <c r="G7" s="99" t="s">
+      <c r="G7" s="98" t="s">
         <v>47</v>
       </c>
       <c r="H7" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="I7" s="18">
-        <v>70</v>
-      </c>
-      <c r="J7" s="65" t="s">
+      <c r="I7" s="18"/>
+      <c r="J7" s="64" t="s">
         <v>65</v>
       </c>
-      <c r="K7" s="71"/>
-      <c r="L7" s="82" t="s">
+      <c r="K7" s="70"/>
+      <c r="L7" s="81" t="s">
         <v>66</v>
       </c>
     </row>
@@ -6762,35 +6733,33 @@
       <c r="A8" s="3">
         <v>10</v>
       </c>
-      <c r="B8" s="62" t="s">
+      <c r="B8" s="61" t="s">
+        <v>94</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="D8" s="62" t="s">
         <v>96</v>
       </c>
-      <c r="D8" s="63" t="s">
-        <v>97</v>
-      </c>
-      <c r="E8" s="64" t="s">
-        <v>85</v>
-      </c>
-      <c r="F8" s="94" t="s">
+      <c r="E8" s="63" t="s">
+        <v>84</v>
+      </c>
+      <c r="F8" s="93" t="s">
         <v>29</v>
       </c>
-      <c r="G8" s="99" t="s">
+      <c r="G8" s="98" t="s">
         <v>47</v>
       </c>
       <c r="H8" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I8" s="9">
-        <v>680</v>
-      </c>
-      <c r="J8" s="65" t="s">
+      <c r="I8" s="9"/>
+      <c r="J8" s="64" t="s">
         <v>65</v>
       </c>
-      <c r="K8" s="66"/>
-      <c r="L8" s="82" t="s">
+      <c r="K8" s="65"/>
+      <c r="L8" s="81" t="s">
         <v>66</v>
       </c>
     </row>
@@ -6798,35 +6767,33 @@
       <c r="A9" s="12">
         <v>11</v>
       </c>
-      <c r="B9" s="67" t="s">
+      <c r="B9" s="66" t="s">
+        <v>97</v>
+      </c>
+      <c r="C9" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="D9" s="67" t="s">
         <v>99</v>
       </c>
-      <c r="D9" s="68" t="s">
-        <v>100</v>
-      </c>
-      <c r="E9" s="69" t="s">
-        <v>85</v>
-      </c>
-      <c r="F9" s="94" t="s">
+      <c r="E9" s="68" t="s">
+        <v>84</v>
+      </c>
+      <c r="F9" s="93" t="s">
         <v>29</v>
       </c>
-      <c r="G9" s="99" t="s">
+      <c r="G9" s="98" t="s">
         <v>47</v>
       </c>
       <c r="H9" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="I9" s="18">
-        <v>460</v>
-      </c>
-      <c r="J9" s="65" t="s">
+      <c r="I9" s="18"/>
+      <c r="J9" s="64" t="s">
         <v>65</v>
       </c>
-      <c r="K9" s="71"/>
-      <c r="L9" s="82" t="s">
+      <c r="K9" s="70"/>
+      <c r="L9" s="81" t="s">
         <v>66</v>
       </c>
     </row>
@@ -6834,55 +6801,51 @@
       <c r="A10" s="3">
         <v>12</v>
       </c>
-      <c r="B10" s="62" t="s">
+      <c r="B10" s="61"/>
+      <c r="C10" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D10" s="62" t="s">
         <v>101</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="D10" s="63" t="s">
-        <v>103</v>
-      </c>
-      <c r="E10" s="64" t="s">
-        <v>85</v>
-      </c>
-      <c r="F10" s="94" t="s">
+      <c r="E10" s="63" t="s">
+        <v>84</v>
+      </c>
+      <c r="F10" s="93" t="s">
         <v>29</v>
       </c>
-      <c r="G10" s="99" t="s">
+      <c r="G10" s="98" t="s">
         <v>47</v>
       </c>
       <c r="H10" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I10" s="9">
-        <v>410</v>
-      </c>
-      <c r="J10" s="65" t="s">
+      <c r="I10" s="9"/>
+      <c r="J10" s="64" t="s">
         <v>65</v>
       </c>
-      <c r="K10" s="66"/>
-      <c r="L10" s="82" t="s">
+      <c r="K10" s="65"/>
+      <c r="L10" s="81" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="133" t="s">
-        <v>86</v>
-      </c>
-      <c r="B11" s="122"/>
-      <c r="C11" s="122"/>
-      <c r="D11" s="122"/>
-      <c r="E11" s="122"/>
-      <c r="F11" s="122"/>
-      <c r="G11" s="122"/>
-      <c r="H11" s="128"/>
-      <c r="I11" s="116">
+      <c r="A11" s="126" t="s">
+        <v>85</v>
+      </c>
+      <c r="B11" s="115"/>
+      <c r="C11" s="115"/>
+      <c r="D11" s="115"/>
+      <c r="E11" s="115"/>
+      <c r="F11" s="115"/>
+      <c r="G11" s="115"/>
+      <c r="H11" s="121"/>
+      <c r="I11" s="106">
         <f>SUM(I6:I10)</f>
-        <v>2400</v>
-      </c>
-      <c r="J11" s="88"/>
-      <c r="K11" s="88"/>
+        <v>780</v>
+      </c>
+      <c r="J11" s="87"/>
+      <c r="K11" s="87"/>
     </row>
     <row r="12" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="23"/>
@@ -6905,60 +6868,60 @@
     <mergeCell ref="A1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="F6:F1000">
-    <cfRule type="cellIs" dxfId="70" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="63" priority="24" operator="equal">
       <formula>"Согласовано"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="62" priority="25" operator="equal">
       <formula>"Закрыто"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="68" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="61" priority="26" operator="equal">
       <formula>"В работе"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="67" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="60" priority="27" operator="equal">
       <formula>"На согласовании"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6:G1000">
-    <cfRule type="cellIs" dxfId="66" priority="28" operator="equal">
+    <cfRule type="cellIs" dxfId="59" priority="28" operator="equal">
       <formula>"Ошибка"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="65" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="29" operator="equal">
       <formula>"Отменено"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G6:G1000">
-    <cfRule type="cellIs" dxfId="64" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="30" operator="equal">
       <formula>"Установлено"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="63" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="56" priority="31" operator="equal">
       <formula>"Разработка"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="62" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="55" priority="32" operator="equal">
       <formula>"Тестирование"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="61" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="54" priority="33" operator="equal">
       <formula>"На приемке"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="53" priority="34" operator="equal">
       <formula>"ОПЭ"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J6:J10">
-    <cfRule type="cellIs" dxfId="59" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="52" priority="1" operator="equal">
       <formula>"Нет"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="2" operator="equal">
       <formula>"Да"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L6:L1000">
-    <cfRule type="cellIs" dxfId="57" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="50" priority="3" operator="equal">
       <formula>"Высокий"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="56" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="4" operator="equal">
       <formula>"Средний"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="55" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="5" operator="equal">
       <formula>"Низкий"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7018,51 +6981,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="132" t="s">
-        <v>104</v>
-      </c>
-      <c r="B1" s="120"/>
-      <c r="C1" s="120"/>
-      <c r="D1" s="120"/>
-      <c r="E1" s="120"/>
-      <c r="F1" s="120"/>
-      <c r="G1" s="120"/>
-      <c r="H1" s="120"/>
-      <c r="I1" s="120"/>
-      <c r="J1" s="120"/>
-      <c r="K1" s="120"/>
-      <c r="L1" s="120"/>
+      <c r="A1" s="125" t="s">
+        <v>102</v>
+      </c>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
+      <c r="I1" s="113"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="130" t="s">
+      <c r="A2" s="123" t="s">
         <v>60</v>
       </c>
-      <c r="B2" s="120"/>
-      <c r="C2" s="120"/>
-      <c r="D2" s="120"/>
-      <c r="E2" s="120"/>
-      <c r="F2" s="120"/>
-      <c r="G2" s="120"/>
-      <c r="H2" s="120"/>
-      <c r="I2" s="120"/>
-      <c r="J2" s="120"/>
-      <c r="K2" s="120"/>
-      <c r="L2" s="120"/>
+      <c r="B2" s="113"/>
+      <c r="C2" s="113"/>
+      <c r="D2" s="113"/>
+      <c r="E2" s="113"/>
+      <c r="F2" s="113"/>
+      <c r="G2" s="113"/>
+      <c r="H2" s="113"/>
+      <c r="I2" s="113"/>
+      <c r="J2" s="113"/>
+      <c r="K2" s="113"/>
+      <c r="L2" s="113"/>
     </row>
     <row r="3" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="53" t="s">
+      <c r="A3" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="54" t="s">
+      <c r="B3" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="55" t="s">
+      <c r="C3" s="54" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="56" t="s">
+      <c r="D3" s="55" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="57" t="s">
+      <c r="E3" s="56" t="s">
         <v>34</v>
       </c>
       <c r="G3" s="23"/>
@@ -7072,23 +7035,23 @@
       <c r="K3" s="23"/>
     </row>
     <row r="4" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="58">
+      <c r="A4" s="57">
         <f>COUNTA(A6:A10)</f>
         <v>5</v>
       </c>
-      <c r="B4" s="59">
+      <c r="B4" s="58">
         <f>COUNTIF(G6:G10,"Установлено")+COUNTIF(G6:G10,"Не СОЛВО")+COUNTIF(G6:G10,"Выполнено")</f>
         <v>2</v>
       </c>
-      <c r="C4" s="60">
+      <c r="C4" s="59">
         <f>COUNTIF(G6:G10,"В работе")+COUNTIF(G6:G10,"Тестирование")+COUNTIF(G6:G10,"Разработка")+COUNTIF(G6:G10,"ОПЭ")+COUNTIF(G6:G10,"На приемке")</f>
         <v>1</v>
       </c>
-      <c r="D4" s="118">
+      <c r="D4" s="108">
         <f>SUM(I6:I10)</f>
-        <v>1012</v>
-      </c>
-      <c r="E4" s="61">
+        <v>532</v>
+      </c>
+      <c r="E4" s="60">
         <f>IF(COUNTA(A6:A10)=0,0,(COUNTIF(G6:G10,"Установлено")+COUNTIF(G6:G10,"Не СОЛВО")+COUNTIF(G6:G10,"Выполнено"))/COUNTA(A6:A10))</f>
         <v>0.4</v>
       </c>
@@ -7099,40 +7062,40 @@
       <c r="K4" s="23"/>
     </row>
     <row r="5" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="84" t="s">
+      <c r="A5" s="83" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="84" t="s">
+      <c r="B5" s="83" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="84" t="s">
+      <c r="C5" s="83" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="84" t="s">
+      <c r="D5" s="83" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="84" t="s">
+      <c r="E5" s="83" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="84" t="s">
+      <c r="F5" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="84" t="s">
+      <c r="G5" s="83" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="84" t="s">
+      <c r="H5" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="84" t="s">
+      <c r="I5" s="83" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="84" t="s">
+      <c r="J5" s="83" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="84" t="s">
+      <c r="K5" s="83" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="84" t="s">
+      <c r="L5" s="83" t="s">
         <v>13</v>
       </c>
     </row>
@@ -7140,35 +7103,33 @@
       <c r="A6" s="3">
         <v>13</v>
       </c>
-      <c r="B6" s="62" t="s">
-        <v>105</v>
+      <c r="B6" s="61" t="s">
+        <v>210</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="D6" s="63" t="s">
-        <v>107</v>
-      </c>
-      <c r="E6" s="64" t="s">
+        <v>103</v>
+      </c>
+      <c r="D6" s="62" t="s">
+        <v>104</v>
+      </c>
+      <c r="E6" s="63" t="s">
         <v>64</v>
       </c>
-      <c r="F6" s="96" t="s">
+      <c r="F6" s="95" t="s">
         <v>40</v>
       </c>
-      <c r="G6" s="99" t="s">
+      <c r="G6" s="98" t="s">
         <v>47</v>
       </c>
       <c r="H6" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="I6" s="9">
-        <v>270</v>
-      </c>
-      <c r="J6" s="65" t="s">
+      <c r="I6" s="9"/>
+      <c r="J6" s="64" t="s">
         <v>65</v>
       </c>
-      <c r="K6" s="66"/>
-      <c r="L6" s="82" t="s">
+      <c r="K6" s="65"/>
+      <c r="L6" s="81" t="s">
         <v>66</v>
       </c>
     </row>
@@ -7176,22 +7137,22 @@
       <c r="A7" s="12">
         <v>14</v>
       </c>
-      <c r="B7" s="67" t="s">
-        <v>108</v>
+      <c r="B7" s="66" t="s">
+        <v>105</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="D7" s="68" t="s">
-        <v>110</v>
-      </c>
-      <c r="E7" s="69" t="s">
+        <v>106</v>
+      </c>
+      <c r="D7" s="67" t="s">
+        <v>107</v>
+      </c>
+      <c r="E7" s="68" t="s">
         <v>64</v>
       </c>
-      <c r="F7" s="94" t="s">
+      <c r="F7" s="93" t="s">
         <v>29</v>
       </c>
-      <c r="G7" s="95" t="s">
+      <c r="G7" s="94" t="s">
         <v>42</v>
       </c>
       <c r="H7" s="17" t="s">
@@ -7200,11 +7161,11 @@
       <c r="I7" s="18">
         <v>340</v>
       </c>
-      <c r="J7" s="65" t="s">
-        <v>69</v>
-      </c>
-      <c r="K7" s="71"/>
-      <c r="L7" s="82" t="s">
+      <c r="J7" s="64" t="s">
+        <v>68</v>
+      </c>
+      <c r="K7" s="70"/>
+      <c r="L7" s="81" t="s">
         <v>66</v>
       </c>
     </row>
@@ -7212,33 +7173,33 @@
       <c r="A8" s="3">
         <v>15</v>
       </c>
-      <c r="B8" s="62" t="s">
-        <v>111</v>
+      <c r="B8" s="61" t="s">
+        <v>108</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="D8" s="63" t="s">
-        <v>113</v>
-      </c>
-      <c r="E8" s="64" t="s">
-        <v>76</v>
-      </c>
-      <c r="F8" s="97" t="s">
+        <v>109</v>
+      </c>
+      <c r="D8" s="62" t="s">
+        <v>110</v>
+      </c>
+      <c r="E8" s="63" t="s">
+        <v>75</v>
+      </c>
+      <c r="F8" s="96" t="s">
         <v>28</v>
       </c>
-      <c r="G8" s="97" t="s">
+      <c r="G8" s="96" t="s">
         <v>38</v>
       </c>
       <c r="H8" s="8" t="s">
         <v>44</v>
       </c>
       <c r="I8" s="9"/>
-      <c r="J8" s="65" t="s">
-        <v>69</v>
-      </c>
-      <c r="K8" s="66"/>
-      <c r="L8" s="82" t="s">
+      <c r="J8" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="K8" s="65"/>
+      <c r="L8" s="81" t="s">
         <v>66</v>
       </c>
     </row>
@@ -7246,22 +7207,22 @@
       <c r="A9" s="12">
         <v>16</v>
       </c>
-      <c r="B9" s="67" t="s">
-        <v>114</v>
+      <c r="B9" s="66" t="s">
+        <v>111</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="D9" s="68" t="s">
-        <v>116</v>
-      </c>
-      <c r="E9" s="69" t="s">
+        <v>112</v>
+      </c>
+      <c r="D9" s="67" t="s">
+        <v>113</v>
+      </c>
+      <c r="E9" s="68" t="s">
         <v>64</v>
       </c>
-      <c r="F9" s="95" t="s">
+      <c r="F9" s="94" t="s">
         <v>42</v>
       </c>
-      <c r="G9" s="97" t="s">
+      <c r="G9" s="96" t="s">
         <v>38</v>
       </c>
       <c r="H9" s="17" t="s">
@@ -7270,11 +7231,11 @@
       <c r="I9" s="18">
         <v>192</v>
       </c>
-      <c r="J9" s="65" t="s">
-        <v>69</v>
-      </c>
-      <c r="K9" s="71"/>
-      <c r="L9" s="82" t="s">
+      <c r="J9" s="64" t="s">
+        <v>68</v>
+      </c>
+      <c r="K9" s="70"/>
+      <c r="L9" s="81" t="s">
         <v>66</v>
       </c>
     </row>
@@ -7282,55 +7243,53 @@
       <c r="A10" s="3">
         <v>17</v>
       </c>
-      <c r="B10" s="62" t="s">
-        <v>117</v>
+      <c r="B10" s="61" t="s">
+        <v>211</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="D10" s="63" t="s">
-        <v>119</v>
-      </c>
-      <c r="E10" s="64" t="s">
-        <v>85</v>
-      </c>
-      <c r="F10" s="98" t="s">
+        <v>114</v>
+      </c>
+      <c r="D10" s="62" t="s">
+        <v>115</v>
+      </c>
+      <c r="E10" s="63" t="s">
+        <v>84</v>
+      </c>
+      <c r="F10" s="97" t="s">
         <v>53</v>
       </c>
-      <c r="G10" s="98" t="s">
+      <c r="G10" s="97" t="s">
         <v>53</v>
       </c>
       <c r="H10" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I10" s="9">
-        <v>210</v>
-      </c>
-      <c r="J10" s="65" t="s">
+      <c r="I10" s="9"/>
+      <c r="J10" s="64" t="s">
         <v>65</v>
       </c>
-      <c r="K10" s="66"/>
-      <c r="L10" s="82" t="s">
+      <c r="K10" s="65"/>
+      <c r="L10" s="81" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="131" t="s">
-        <v>86</v>
-      </c>
-      <c r="B11" s="122"/>
-      <c r="C11" s="122"/>
-      <c r="D11" s="122"/>
-      <c r="E11" s="122"/>
-      <c r="F11" s="122"/>
-      <c r="G11" s="122"/>
-      <c r="H11" s="128"/>
-      <c r="I11" s="115">
+      <c r="A11" s="124" t="s">
+        <v>85</v>
+      </c>
+      <c r="B11" s="115"/>
+      <c r="C11" s="115"/>
+      <c r="D11" s="115"/>
+      <c r="E11" s="115"/>
+      <c r="F11" s="115"/>
+      <c r="G11" s="115"/>
+      <c r="H11" s="121"/>
+      <c r="I11" s="105">
         <f>SUM(I6:I10)</f>
-        <v>1012</v>
-      </c>
-      <c r="J11" s="86"/>
-      <c r="K11" s="86"/>
+        <v>532</v>
+      </c>
+      <c r="J11" s="85"/>
+      <c r="K11" s="85"/>
     </row>
     <row r="12" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="23"/>
@@ -7353,60 +7312,60 @@
     <mergeCell ref="A1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="F6:F1000">
-    <cfRule type="cellIs" dxfId="54" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="24" operator="equal">
       <formula>"Согласовано"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="53" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="25" operator="equal">
       <formula>"Закрыто"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="52" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="26" operator="equal">
       <formula>"В работе"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="51" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="27" operator="equal">
       <formula>"На согласовании"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6:G1000">
-    <cfRule type="cellIs" dxfId="50" priority="28" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="28" operator="equal">
       <formula>"Ошибка"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="29" operator="equal">
       <formula>"Отменено"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G6:G1000">
-    <cfRule type="cellIs" dxfId="48" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="30" operator="equal">
       <formula>"Установлено"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="47" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="31" operator="equal">
       <formula>"Разработка"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="32" operator="equal">
       <formula>"Тестирование"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="45" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="33" operator="equal">
       <formula>"На приемке"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="44" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="34" operator="equal">
       <formula>"ОПЭ"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J6:J10">
-    <cfRule type="cellIs" dxfId="43" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="1" operator="equal">
       <formula>"Нет"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="2" operator="equal">
       <formula>"Да"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L6:L1000">
-    <cfRule type="cellIs" dxfId="41" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="3" operator="equal">
       <formula>"Высокий"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="4" operator="equal">
       <formula>"Средний"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="39" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="5" operator="equal">
       <formula>"Низкий"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7466,51 +7425,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="135" t="s">
-        <v>120</v>
-      </c>
-      <c r="B1" s="120"/>
-      <c r="C1" s="120"/>
-      <c r="D1" s="120"/>
-      <c r="E1" s="120"/>
-      <c r="F1" s="120"/>
-      <c r="G1" s="120"/>
-      <c r="H1" s="120"/>
-      <c r="I1" s="120"/>
-      <c r="J1" s="120"/>
-      <c r="K1" s="120"/>
-      <c r="L1" s="120"/>
+      <c r="A1" s="128" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
+      <c r="I1" s="113"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="130" t="s">
+      <c r="A2" s="123" t="s">
         <v>60</v>
       </c>
-      <c r="B2" s="120"/>
-      <c r="C2" s="120"/>
-      <c r="D2" s="120"/>
-      <c r="E2" s="120"/>
-      <c r="F2" s="120"/>
-      <c r="G2" s="120"/>
-      <c r="H2" s="120"/>
-      <c r="I2" s="120"/>
-      <c r="J2" s="120"/>
-      <c r="K2" s="120"/>
-      <c r="L2" s="120"/>
+      <c r="B2" s="113"/>
+      <c r="C2" s="113"/>
+      <c r="D2" s="113"/>
+      <c r="E2" s="113"/>
+      <c r="F2" s="113"/>
+      <c r="G2" s="113"/>
+      <c r="H2" s="113"/>
+      <c r="I2" s="113"/>
+      <c r="J2" s="113"/>
+      <c r="K2" s="113"/>
+      <c r="L2" s="113"/>
     </row>
     <row r="3" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="53" t="s">
+      <c r="A3" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="54" t="s">
+      <c r="B3" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="55" t="s">
+      <c r="C3" s="54" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="56" t="s">
+      <c r="D3" s="55" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="57" t="s">
+      <c r="E3" s="56" t="s">
         <v>34</v>
       </c>
       <c r="G3" s="23"/>
@@ -7520,23 +7479,23 @@
       <c r="K3" s="23"/>
     </row>
     <row r="4" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="58">
+      <c r="A4" s="57">
         <f>COUNTA(A6:A21)</f>
         <v>16</v>
       </c>
-      <c r="B4" s="59">
+      <c r="B4" s="58">
         <f>COUNTIF(G6:G21,"Установлено")+COUNTIF(G6:G21,"Не СОЛВО")+COUNTIF(G6:G21,"Выполнено")</f>
         <v>8</v>
       </c>
-      <c r="C4" s="60">
+      <c r="C4" s="59">
         <f>COUNTIF(G6:G21,"В работе")+COUNTIF(G6:G21,"Тестирование")+COUNTIF(G6:G21,"Разработка")+COUNTIF(G6:G21,"ОПЭ")+COUNTIF(G6:G21,"На приемке")</f>
         <v>2</v>
       </c>
-      <c r="D4" s="118">
+      <c r="D4" s="108">
         <f>SUM(I6:I21)</f>
-        <v>1141</v>
-      </c>
-      <c r="E4" s="61">
+        <v>1231</v>
+      </c>
+      <c r="E4" s="60">
         <f>IF(COUNTA(A6:A21)=0,0,(COUNTIF(G6:G21,"Установлено")+COUNTIF(G6:G21,"Не СОЛВО")+COUNTIF(G6:G21,"Выполнено"))/COUNTA(A6:A21))</f>
         <v>0.5</v>
       </c>
@@ -7547,40 +7506,40 @@
       <c r="K4" s="23"/>
     </row>
     <row r="5" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="89" t="s">
+      <c r="A5" s="88" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="89" t="s">
+      <c r="B5" s="88" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="89" t="s">
+      <c r="C5" s="88" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="89" t="s">
+      <c r="D5" s="88" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="89" t="s">
+      <c r="E5" s="88" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="89" t="s">
+      <c r="F5" s="88" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="89" t="s">
+      <c r="G5" s="88" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="89" t="s">
+      <c r="H5" s="88" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="89" t="s">
+      <c r="I5" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="89" t="s">
+      <c r="J5" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="89" t="s">
+      <c r="K5" s="88" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="89" t="s">
+      <c r="L5" s="88" t="s">
         <v>13</v>
       </c>
     </row>
@@ -7588,35 +7547,33 @@
       <c r="A6" s="3">
         <v>18</v>
       </c>
-      <c r="B6" s="62" t="s">
-        <v>121</v>
+      <c r="B6" s="61" t="s">
+        <v>117</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="D6" s="63" t="s">
-        <v>123</v>
-      </c>
-      <c r="E6" s="64" t="s">
-        <v>85</v>
-      </c>
-      <c r="F6" s="94" t="s">
+        <v>118</v>
+      </c>
+      <c r="D6" s="62" t="s">
+        <v>119</v>
+      </c>
+      <c r="E6" s="63" t="s">
+        <v>84</v>
+      </c>
+      <c r="F6" s="93" t="s">
         <v>29</v>
       </c>
-      <c r="G6" s="98" t="s">
+      <c r="G6" s="97" t="s">
         <v>51</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="I6" s="9">
-        <v>250</v>
-      </c>
-      <c r="J6" s="65" t="s">
+        <v>214</v>
+      </c>
+      <c r="I6" s="9"/>
+      <c r="J6" s="64" t="s">
         <v>65</v>
       </c>
-      <c r="K6" s="66"/>
-      <c r="L6" s="82" t="s">
+      <c r="K6" s="65"/>
+      <c r="L6" s="81" t="s">
         <v>66</v>
       </c>
     </row>
@@ -7624,33 +7581,35 @@
       <c r="A7" s="12">
         <v>19</v>
       </c>
-      <c r="B7" s="67" t="s">
-        <v>124</v>
+      <c r="B7" s="66" t="s">
+        <v>120</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="D7" s="68" t="s">
-        <v>126</v>
-      </c>
-      <c r="E7" s="69" t="s">
-        <v>76</v>
-      </c>
-      <c r="F7" s="97" t="s">
+        <v>121</v>
+      </c>
+      <c r="D7" s="67" t="s">
+        <v>122</v>
+      </c>
+      <c r="E7" s="68" t="s">
+        <v>75</v>
+      </c>
+      <c r="F7" s="96" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="97" t="s">
-        <v>211</v>
+      <c r="G7" s="96" t="s">
+        <v>203</v>
       </c>
       <c r="H7" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="I7" s="18"/>
-      <c r="J7" s="65" t="s">
-        <v>69</v>
-      </c>
-      <c r="K7" s="71"/>
-      <c r="L7" s="82" t="s">
+      <c r="I7" s="18">
+        <v>70</v>
+      </c>
+      <c r="J7" s="64" t="s">
+        <v>68</v>
+      </c>
+      <c r="K7" s="70"/>
+      <c r="L7" s="81" t="s">
         <v>66</v>
       </c>
     </row>
@@ -7658,22 +7617,22 @@
       <c r="A8" s="3">
         <v>20</v>
       </c>
-      <c r="B8" s="62" t="s">
-        <v>127</v>
+      <c r="B8" s="61" t="s">
+        <v>123</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="D8" s="63" t="s">
-        <v>129</v>
-      </c>
-      <c r="E8" s="64" t="s">
+        <v>124</v>
+      </c>
+      <c r="D8" s="62" t="s">
+        <v>125</v>
+      </c>
+      <c r="E8" s="63" t="s">
         <v>40</v>
       </c>
-      <c r="F8" s="96" t="s">
+      <c r="F8" s="95" t="s">
         <v>40</v>
       </c>
-      <c r="G8" s="97" t="s">
+      <c r="G8" s="96" t="s">
         <v>38</v>
       </c>
       <c r="H8" s="8" t="s">
@@ -7682,11 +7641,11 @@
       <c r="I8" s="9">
         <v>96</v>
       </c>
-      <c r="J8" s="65" t="s">
-        <v>69</v>
-      </c>
-      <c r="K8" s="66"/>
-      <c r="L8" s="82" t="s">
+      <c r="J8" s="64" t="s">
+        <v>68</v>
+      </c>
+      <c r="K8" s="65"/>
+      <c r="L8" s="81" t="s">
         <v>66</v>
       </c>
     </row>
@@ -7694,35 +7653,35 @@
       <c r="A9" s="12">
         <v>21</v>
       </c>
-      <c r="B9" s="67" t="s">
-        <v>130</v>
+      <c r="B9" s="66" t="s">
+        <v>126</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="D9" s="68" t="s">
-        <v>132</v>
-      </c>
-      <c r="E9" s="69" t="s">
-        <v>85</v>
-      </c>
-      <c r="F9" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="D9" s="67" t="s">
+        <v>128</v>
+      </c>
+      <c r="E9" s="68" t="s">
+        <v>84</v>
+      </c>
+      <c r="F9" s="93" t="s">
         <v>29</v>
       </c>
-      <c r="G9" s="100" t="s">
+      <c r="G9" s="99" t="s">
         <v>49</v>
       </c>
       <c r="H9" s="17" t="s">
         <v>52</v>
       </c>
       <c r="I9" s="18">
-        <v>350</v>
-      </c>
-      <c r="J9" s="65" t="s">
-        <v>65</v>
-      </c>
-      <c r="K9" s="71"/>
-      <c r="L9" s="82" t="s">
+        <v>320</v>
+      </c>
+      <c r="J9" s="64" t="s">
+        <v>68</v>
+      </c>
+      <c r="K9" s="70"/>
+      <c r="L9" s="81" t="s">
         <v>66</v>
       </c>
     </row>
@@ -7730,22 +7689,22 @@
       <c r="A10" s="3">
         <v>22</v>
       </c>
-      <c r="B10" s="62" t="s">
-        <v>133</v>
+      <c r="B10" s="61" t="s">
+        <v>129</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="D10" s="63" t="s">
-        <v>135</v>
-      </c>
-      <c r="E10" s="64" t="s">
+        <v>130</v>
+      </c>
+      <c r="D10" s="62" t="s">
+        <v>131</v>
+      </c>
+      <c r="E10" s="63" t="s">
         <v>40</v>
       </c>
-      <c r="F10" s="96" t="s">
+      <c r="F10" s="95" t="s">
         <v>40</v>
       </c>
-      <c r="G10" s="97" t="s">
+      <c r="G10" s="96" t="s">
         <v>38</v>
       </c>
       <c r="H10" s="8" t="s">
@@ -7754,11 +7713,11 @@
       <c r="I10" s="9">
         <v>23</v>
       </c>
-      <c r="J10" s="65" t="s">
-        <v>69</v>
-      </c>
-      <c r="K10" s="66"/>
-      <c r="L10" s="82" t="s">
+      <c r="J10" s="64" t="s">
+        <v>68</v>
+      </c>
+      <c r="K10" s="65"/>
+      <c r="L10" s="81" t="s">
         <v>66</v>
       </c>
     </row>
@@ -7766,33 +7725,35 @@
       <c r="A11" s="12">
         <v>23</v>
       </c>
-      <c r="B11" s="67" t="s">
-        <v>136</v>
+      <c r="B11" s="66" t="s">
+        <v>132</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="D11" s="68" t="s">
-        <v>138</v>
-      </c>
-      <c r="E11" s="69" t="s">
-        <v>76</v>
-      </c>
-      <c r="F11" s="97" t="s">
+        <v>133</v>
+      </c>
+      <c r="D11" s="67" t="s">
+        <v>134</v>
+      </c>
+      <c r="E11" s="68" t="s">
+        <v>75</v>
+      </c>
+      <c r="F11" s="96" t="s">
         <v>28</v>
       </c>
-      <c r="G11" s="97" t="s">
+      <c r="G11" s="96" t="s">
         <v>38</v>
       </c>
       <c r="H11" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="I11" s="18"/>
-      <c r="J11" s="65" t="s">
-        <v>69</v>
-      </c>
-      <c r="K11" s="71"/>
-      <c r="L11" s="82" t="s">
+      <c r="I11" s="18">
+        <v>60</v>
+      </c>
+      <c r="J11" s="64" t="s">
+        <v>68</v>
+      </c>
+      <c r="K11" s="70"/>
+      <c r="L11" s="81" t="s">
         <v>66</v>
       </c>
     </row>
@@ -7800,33 +7761,35 @@
       <c r="A12" s="3">
         <v>24</v>
       </c>
-      <c r="B12" s="62" t="s">
+      <c r="B12" s="61" t="s">
+        <v>132</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="D12" s="62" t="s">
         <v>136</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="D12" s="63" t="s">
-        <v>140</v>
-      </c>
-      <c r="E12" s="64" t="s">
-        <v>76</v>
-      </c>
-      <c r="F12" s="97" t="s">
+      <c r="E12" s="63" t="s">
+        <v>75</v>
+      </c>
+      <c r="F12" s="96" t="s">
         <v>28</v>
       </c>
-      <c r="G12" s="97" t="s">
+      <c r="G12" s="96" t="s">
         <v>38</v>
       </c>
       <c r="H12" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="I12" s="9"/>
-      <c r="J12" s="65" t="s">
-        <v>69</v>
-      </c>
-      <c r="K12" s="66"/>
-      <c r="L12" s="82" t="s">
+      <c r="I12" s="9">
+        <v>20</v>
+      </c>
+      <c r="J12" s="64" t="s">
+        <v>68</v>
+      </c>
+      <c r="K12" s="65"/>
+      <c r="L12" s="81" t="s">
         <v>66</v>
       </c>
     </row>
@@ -7834,35 +7797,33 @@
       <c r="A13" s="12">
         <v>25</v>
       </c>
-      <c r="B13" s="67" t="s">
-        <v>141</v>
+      <c r="B13" s="66" t="s">
+        <v>137</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="D13" s="68" t="s">
-        <v>143</v>
-      </c>
-      <c r="E13" s="69" t="s">
-        <v>85</v>
-      </c>
-      <c r="F13" s="94" t="s">
+        <v>138</v>
+      </c>
+      <c r="D13" s="67" t="s">
+        <v>139</v>
+      </c>
+      <c r="E13" s="68" t="s">
+        <v>84</v>
+      </c>
+      <c r="F13" s="93" t="s">
         <v>29</v>
       </c>
-      <c r="G13" s="98" t="s">
+      <c r="G13" s="97" t="s">
         <v>51</v>
       </c>
       <c r="H13" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="I13" s="18">
-        <v>26</v>
-      </c>
-      <c r="J13" s="65" t="s">
+        <v>214</v>
+      </c>
+      <c r="I13" s="18"/>
+      <c r="J13" s="64" t="s">
         <v>65</v>
       </c>
-      <c r="K13" s="71"/>
-      <c r="L13" s="82" t="s">
+      <c r="K13" s="70"/>
+      <c r="L13" s="81" t="s">
         <v>66</v>
       </c>
     </row>
@@ -7870,31 +7831,33 @@
       <c r="A14" s="3">
         <v>26</v>
       </c>
-      <c r="B14" s="62" t="s">
-        <v>144</v>
+      <c r="B14" s="61" t="s">
+        <v>140</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="D14" s="63" t="s">
-        <v>146</v>
-      </c>
-      <c r="E14" s="64" t="s">
-        <v>76</v>
-      </c>
-      <c r="F14" s="97" t="s">
+        <v>141</v>
+      </c>
+      <c r="D14" s="62" t="s">
+        <v>142</v>
+      </c>
+      <c r="E14" s="63" t="s">
+        <v>75</v>
+      </c>
+      <c r="F14" s="96" t="s">
         <v>28</v>
       </c>
-      <c r="G14" s="98" t="s">
+      <c r="G14" s="97" t="s">
         <v>56</v>
       </c>
-      <c r="H14" s="8"/>
+      <c r="H14" s="8" t="s">
+        <v>56</v>
+      </c>
       <c r="I14" s="9"/>
-      <c r="J14" s="65" t="s">
-        <v>69</v>
-      </c>
-      <c r="K14" s="66"/>
-      <c r="L14" s="82" t="s">
+      <c r="J14" s="64" t="s">
+        <v>68</v>
+      </c>
+      <c r="K14" s="65"/>
+      <c r="L14" s="81" t="s">
         <v>66</v>
       </c>
     </row>
@@ -7902,33 +7865,35 @@
       <c r="A15" s="12">
         <v>27</v>
       </c>
-      <c r="B15" s="67" t="s">
-        <v>147</v>
+      <c r="B15" s="66" t="s">
+        <v>143</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="D15" s="68" t="s">
-        <v>149</v>
-      </c>
-      <c r="E15" s="69" t="s">
+        <v>144</v>
+      </c>
+      <c r="D15" s="67" t="s">
+        <v>145</v>
+      </c>
+      <c r="E15" s="68" t="s">
         <v>40</v>
       </c>
-      <c r="F15" s="96" t="s">
+      <c r="F15" s="95" t="s">
         <v>40</v>
       </c>
-      <c r="G15" s="97" t="s">
+      <c r="G15" s="96" t="s">
         <v>38</v>
       </c>
       <c r="H15" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="I15" s="18"/>
-      <c r="J15" s="65" t="s">
-        <v>69</v>
-      </c>
-      <c r="K15" s="71"/>
-      <c r="L15" s="82" t="s">
+        <v>43</v>
+      </c>
+      <c r="I15" s="18">
+        <v>140</v>
+      </c>
+      <c r="J15" s="64" t="s">
+        <v>68</v>
+      </c>
+      <c r="K15" s="70"/>
+      <c r="L15" s="81" t="s">
         <v>66</v>
       </c>
     </row>
@@ -7936,33 +7901,33 @@
       <c r="A16" s="3">
         <v>28</v>
       </c>
-      <c r="B16" s="62" t="s">
+      <c r="B16" s="61" t="s">
+        <v>143</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="D16" s="62" t="s">
         <v>147</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="D16" s="63" t="s">
-        <v>151</v>
-      </c>
-      <c r="E16" s="64" t="s">
+      <c r="E16" s="63" t="s">
         <v>40</v>
       </c>
-      <c r="F16" s="96" t="s">
+      <c r="F16" s="95" t="s">
         <v>40</v>
       </c>
-      <c r="G16" s="97" t="s">
+      <c r="G16" s="96" t="s">
         <v>38</v>
       </c>
       <c r="H16" s="8" t="s">
         <v>41</v>
       </c>
       <c r="I16" s="9"/>
-      <c r="J16" s="65" t="s">
-        <v>69</v>
-      </c>
-      <c r="K16" s="66"/>
-      <c r="L16" s="82" t="s">
+      <c r="J16" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="K16" s="65"/>
+      <c r="L16" s="81" t="s">
         <v>66</v>
       </c>
     </row>
@@ -7970,22 +7935,22 @@
       <c r="A17" s="12">
         <v>29</v>
       </c>
-      <c r="B17" s="67" t="s">
-        <v>152</v>
+      <c r="B17" s="66" t="s">
+        <v>212</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>153</v>
-      </c>
-      <c r="D17" s="68" t="s">
-        <v>154</v>
-      </c>
-      <c r="E17" s="69" t="s">
-        <v>85</v>
-      </c>
-      <c r="F17" s="94" t="s">
+        <v>148</v>
+      </c>
+      <c r="D17" s="67" t="s">
+        <v>149</v>
+      </c>
+      <c r="E17" s="68" t="s">
+        <v>84</v>
+      </c>
+      <c r="F17" s="93" t="s">
         <v>29</v>
       </c>
-      <c r="G17" s="95" t="s">
+      <c r="G17" s="94" t="s">
         <v>42</v>
       </c>
       <c r="H17" s="17" t="s">
@@ -7994,11 +7959,11 @@
       <c r="I17" s="18">
         <v>8</v>
       </c>
-      <c r="J17" s="65" t="s">
-        <v>69</v>
-      </c>
-      <c r="K17" s="71"/>
-      <c r="L17" s="82" t="s">
+      <c r="J17" s="64" t="s">
+        <v>68</v>
+      </c>
+      <c r="K17" s="70"/>
+      <c r="L17" s="81" t="s">
         <v>66</v>
       </c>
     </row>
@@ -8006,22 +7971,22 @@
       <c r="A18" s="3">
         <v>30</v>
       </c>
-      <c r="B18" s="62" t="s">
-        <v>155</v>
+      <c r="B18" s="61" t="s">
+        <v>150</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="D18" s="63" t="s">
-        <v>157</v>
-      </c>
-      <c r="E18" s="64" t="s">
+        <v>151</v>
+      </c>
+      <c r="D18" s="62" t="s">
+        <v>152</v>
+      </c>
+      <c r="E18" s="63" t="s">
         <v>40</v>
       </c>
-      <c r="F18" s="96" t="s">
+      <c r="F18" s="95" t="s">
         <v>40</v>
       </c>
-      <c r="G18" s="97" t="s">
+      <c r="G18" s="96" t="s">
         <v>38</v>
       </c>
       <c r="H18" s="8" t="s">
@@ -8030,11 +7995,11 @@
       <c r="I18" s="9">
         <v>130</v>
       </c>
-      <c r="J18" s="65" t="s">
-        <v>69</v>
-      </c>
-      <c r="K18" s="66"/>
-      <c r="L18" s="82" t="s">
+      <c r="J18" s="64" t="s">
+        <v>68</v>
+      </c>
+      <c r="K18" s="65"/>
+      <c r="L18" s="81" t="s">
         <v>66</v>
       </c>
     </row>
@@ -8042,33 +8007,33 @@
       <c r="A19" s="12">
         <v>31</v>
       </c>
-      <c r="B19" s="67" t="s">
-        <v>158</v>
+      <c r="B19" s="66" t="s">
+        <v>153</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="D19" s="68" t="s">
-        <v>160</v>
-      </c>
-      <c r="E19" s="69" t="s">
-        <v>161</v>
-      </c>
-      <c r="F19" s="94" t="s">
+        <v>154</v>
+      </c>
+      <c r="D19" s="67" t="s">
+        <v>155</v>
+      </c>
+      <c r="E19" s="68" t="s">
+        <v>84</v>
+      </c>
+      <c r="F19" s="93" t="s">
         <v>29</v>
       </c>
-      <c r="G19" s="99" t="s">
+      <c r="G19" s="98" t="s">
         <v>47</v>
       </c>
       <c r="H19" s="17" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I19" s="18"/>
-      <c r="J19" s="65" t="s">
+      <c r="J19" s="64" t="s">
         <v>65</v>
       </c>
-      <c r="K19" s="71"/>
-      <c r="L19" s="82" t="s">
+      <c r="K19" s="70"/>
+      <c r="L19" s="81" t="s">
         <v>66</v>
       </c>
     </row>
@@ -8076,35 +8041,35 @@
       <c r="A20" s="3">
         <v>32</v>
       </c>
-      <c r="B20" s="62" t="s">
-        <v>162</v>
+      <c r="B20" s="61" t="s">
+        <v>213</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="D20" s="63" t="s">
-        <v>164</v>
-      </c>
-      <c r="E20" s="64" t="s">
-        <v>85</v>
-      </c>
-      <c r="F20" s="94" t="s">
+        <v>157</v>
+      </c>
+      <c r="D20" s="62" t="s">
+        <v>158</v>
+      </c>
+      <c r="E20" s="63" t="s">
+        <v>84</v>
+      </c>
+      <c r="F20" s="93" t="s">
         <v>29</v>
       </c>
-      <c r="G20" s="95" t="s">
+      <c r="G20" s="94" t="s">
         <v>42</v>
       </c>
       <c r="H20" s="8" t="s">
         <v>48</v>
       </c>
       <c r="I20" s="9">
-        <v>118</v>
-      </c>
-      <c r="J20" s="65" t="s">
-        <v>69</v>
-      </c>
-      <c r="K20" s="66"/>
-      <c r="L20" s="82" t="s">
+        <v>110</v>
+      </c>
+      <c r="J20" s="64" t="s">
+        <v>68</v>
+      </c>
+      <c r="K20" s="65"/>
+      <c r="L20" s="81" t="s">
         <v>66</v>
       </c>
     </row>
@@ -8112,55 +8077,55 @@
       <c r="A21" s="12">
         <v>33</v>
       </c>
-      <c r="B21" s="67" t="s">
-        <v>165</v>
+      <c r="B21" s="66" t="s">
+        <v>159</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="D21" s="68" t="s">
-        <v>167</v>
-      </c>
-      <c r="E21" s="69" t="s">
-        <v>85</v>
-      </c>
-      <c r="F21" s="94" t="s">
+        <v>160</v>
+      </c>
+      <c r="D21" s="67" t="s">
+        <v>161</v>
+      </c>
+      <c r="E21" s="68" t="s">
+        <v>84</v>
+      </c>
+      <c r="F21" s="93" t="s">
         <v>29</v>
       </c>
-      <c r="G21" s="100" t="s">
+      <c r="G21" s="99" t="s">
         <v>49</v>
       </c>
       <c r="H21" s="17" t="s">
         <v>52</v>
       </c>
       <c r="I21" s="18">
-        <v>140</v>
-      </c>
-      <c r="J21" s="65" t="s">
-        <v>65</v>
-      </c>
-      <c r="K21" s="71"/>
-      <c r="L21" s="82" t="s">
+        <v>254</v>
+      </c>
+      <c r="J21" s="64" t="s">
+        <v>68</v>
+      </c>
+      <c r="K21" s="70"/>
+      <c r="L21" s="81" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="136" t="s">
-        <v>86</v>
-      </c>
-      <c r="B22" s="122"/>
-      <c r="C22" s="122"/>
-      <c r="D22" s="122"/>
-      <c r="E22" s="122"/>
-      <c r="F22" s="122"/>
-      <c r="G22" s="122"/>
-      <c r="H22" s="128"/>
-      <c r="I22" s="114">
+      <c r="A22" s="129" t="s">
+        <v>85</v>
+      </c>
+      <c r="B22" s="115"/>
+      <c r="C22" s="115"/>
+      <c r="D22" s="115"/>
+      <c r="E22" s="115"/>
+      <c r="F22" s="115"/>
+      <c r="G22" s="115"/>
+      <c r="H22" s="121"/>
+      <c r="I22" s="104">
         <f>SUM(I6:I21)</f>
-        <v>1141</v>
-      </c>
-      <c r="J22" s="90"/>
-      <c r="K22" s="90"/>
+        <v>1231</v>
+      </c>
+      <c r="J22" s="89"/>
+      <c r="K22" s="89"/>
     </row>
     <row r="23" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="23"/>
@@ -8183,60 +8148,60 @@
     <mergeCell ref="A22:H22"/>
   </mergeCells>
   <conditionalFormatting sqref="F6:F1000">
-    <cfRule type="cellIs" dxfId="38" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="24" operator="equal">
       <formula>"Согласовано"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="25" operator="equal">
       <formula>"Закрыто"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="26" operator="equal">
       <formula>"В работе"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="27" operator="equal">
       <formula>"На согласовании"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6:G1000">
-    <cfRule type="cellIs" dxfId="34" priority="28" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="28" operator="equal">
       <formula>"Ошибка"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="29" operator="equal">
       <formula>"Отменено"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G6:G1000">
-    <cfRule type="cellIs" dxfId="32" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="30" operator="equal">
       <formula>"Установлено"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="31" operator="equal">
       <formula>"Разработка"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="32" operator="equal">
       <formula>"Тестирование"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="33" operator="equal">
       <formula>"На приемке"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="34" operator="equal">
       <formula>"ОПЭ"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J6:J21">
-    <cfRule type="cellIs" dxfId="27" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
       <formula>"Нет"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="2" operator="equal">
       <formula>"Да"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L6:L1000">
-    <cfRule type="cellIs" dxfId="25" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="3" operator="equal">
       <formula>"Высокий"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="4" operator="equal">
       <formula>"Средний"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="5" operator="equal">
       <formula>"Низкий"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8296,51 +8261,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="138" t="s">
-        <v>168</v>
-      </c>
-      <c r="B1" s="120"/>
-      <c r="C1" s="120"/>
-      <c r="D1" s="120"/>
-      <c r="E1" s="120"/>
-      <c r="F1" s="120"/>
-      <c r="G1" s="120"/>
-      <c r="H1" s="120"/>
-      <c r="I1" s="120"/>
-      <c r="J1" s="120"/>
-      <c r="K1" s="120"/>
-      <c r="L1" s="120"/>
+      <c r="A1" s="131" t="s">
+        <v>162</v>
+      </c>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
+      <c r="I1" s="113"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="130" t="s">
+      <c r="A2" s="123" t="s">
         <v>60</v>
       </c>
-      <c r="B2" s="120"/>
-      <c r="C2" s="120"/>
-      <c r="D2" s="120"/>
-      <c r="E2" s="120"/>
-      <c r="F2" s="120"/>
-      <c r="G2" s="120"/>
-      <c r="H2" s="120"/>
-      <c r="I2" s="120"/>
-      <c r="J2" s="120"/>
-      <c r="K2" s="120"/>
-      <c r="L2" s="120"/>
+      <c r="B2" s="113"/>
+      <c r="C2" s="113"/>
+      <c r="D2" s="113"/>
+      <c r="E2" s="113"/>
+      <c r="F2" s="113"/>
+      <c r="G2" s="113"/>
+      <c r="H2" s="113"/>
+      <c r="I2" s="113"/>
+      <c r="J2" s="113"/>
+      <c r="K2" s="113"/>
+      <c r="L2" s="113"/>
     </row>
     <row r="3" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="53" t="s">
+      <c r="A3" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="54" t="s">
+      <c r="B3" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="55" t="s">
+      <c r="C3" s="54" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="56" t="s">
+      <c r="D3" s="55" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="57" t="s">
+      <c r="E3" s="56" t="s">
         <v>34</v>
       </c>
       <c r="G3" s="23"/>
@@ -8350,23 +8315,23 @@
       <c r="K3" s="23"/>
     </row>
     <row r="4" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="58">
+      <c r="A4" s="57">
         <f>COUNTA(A6:A15)</f>
         <v>10</v>
       </c>
-      <c r="B4" s="59">
+      <c r="B4" s="58">
         <f>COUNTIF(G6:G15,"Установлено")+COUNTIF(G6:G15,"Не СОЛВО")+COUNTIF(G6:G15,"Выполнено")</f>
         <v>1</v>
       </c>
-      <c r="C4" s="60">
+      <c r="C4" s="59">
         <f>COUNTIF(G6:G15,"В работе")+COUNTIF(G6:G15,"Тестирование")+COUNTIF(G6:G15,"Разработка")+COUNTIF(G6:G15,"ОПЭ")+COUNTIF(G6:G15,"На приемке")</f>
         <v>1</v>
       </c>
-      <c r="D4" s="118">
+      <c r="D4" s="108">
         <f>SUM(I6:I15)</f>
-        <v>1279</v>
-      </c>
-      <c r="E4" s="61">
+        <v>175</v>
+      </c>
+      <c r="E4" s="60">
         <f>IF(COUNTA(A6:A15)=0,0,(COUNTIF(G6:G15,"Установлено")+COUNTIF(G6:G15,"Не СОЛВО")+COUNTIF(G6:G15,"Выполнено"))/COUNTA(A6:A15))</f>
         <v>0.1</v>
       </c>
@@ -8377,40 +8342,40 @@
       <c r="K4" s="23"/>
     </row>
     <row r="5" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="91" t="s">
+      <c r="A5" s="90" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="91" t="s">
+      <c r="B5" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="91" t="s">
+      <c r="C5" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="91" t="s">
+      <c r="D5" s="90" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="91" t="s">
+      <c r="E5" s="90" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="91" t="s">
+      <c r="F5" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="91" t="s">
+      <c r="G5" s="90" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="91" t="s">
+      <c r="H5" s="90" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="91" t="s">
+      <c r="I5" s="90" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="91" t="s">
+      <c r="J5" s="90" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="91" t="s">
+      <c r="K5" s="90" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="91" t="s">
+      <c r="L5" s="90" t="s">
         <v>13</v>
       </c>
     </row>
@@ -8418,33 +8383,33 @@
       <c r="A6" s="3">
         <v>34</v>
       </c>
-      <c r="B6" s="62" t="s">
-        <v>169</v>
+      <c r="B6" s="61" t="s">
+        <v>163</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="D6" s="63" t="s">
-        <v>171</v>
-      </c>
-      <c r="E6" s="64" t="s">
-        <v>76</v>
-      </c>
-      <c r="F6" s="97" t="s">
+        <v>164</v>
+      </c>
+      <c r="D6" s="62" t="s">
+        <v>165</v>
+      </c>
+      <c r="E6" s="63" t="s">
+        <v>75</v>
+      </c>
+      <c r="F6" s="96" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="97" t="s">
+      <c r="G6" s="96" t="s">
         <v>38</v>
       </c>
       <c r="H6" s="8" t="s">
         <v>44</v>
       </c>
       <c r="I6" s="9"/>
-      <c r="J6" s="65" t="s">
-        <v>69</v>
-      </c>
-      <c r="K6" s="66"/>
-      <c r="L6" s="82" t="s">
+      <c r="J6" s="64" t="s">
+        <v>68</v>
+      </c>
+      <c r="K6" s="65"/>
+      <c r="L6" s="81" t="s">
         <v>66</v>
       </c>
     </row>
@@ -8452,33 +8417,33 @@
       <c r="A7" s="12">
         <v>35</v>
       </c>
-      <c r="B7" s="67" t="s">
-        <v>172</v>
+      <c r="B7" s="66" t="s">
+        <v>166</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="D7" s="68" t="s">
-        <v>174</v>
-      </c>
-      <c r="E7" s="69" t="s">
-        <v>175</v>
-      </c>
-      <c r="F7" s="94" t="s">
+        <v>167</v>
+      </c>
+      <c r="D7" s="67" t="s">
+        <v>168</v>
+      </c>
+      <c r="E7" s="68" t="s">
+        <v>169</v>
+      </c>
+      <c r="F7" s="93" t="s">
         <v>29</v>
       </c>
-      <c r="G7" s="99" t="s">
+      <c r="G7" s="98" t="s">
         <v>47</v>
       </c>
       <c r="H7" s="17" t="s">
         <v>52</v>
       </c>
       <c r="I7" s="18"/>
-      <c r="J7" s="65" t="s">
+      <c r="J7" s="64" t="s">
         <v>65</v>
       </c>
-      <c r="K7" s="71"/>
-      <c r="L7" s="82" t="s">
+      <c r="K7" s="70"/>
+      <c r="L7" s="81" t="s">
         <v>66</v>
       </c>
     </row>
@@ -8486,35 +8451,31 @@
       <c r="A8" s="3">
         <v>36</v>
       </c>
-      <c r="B8" s="62" t="s">
-        <v>176</v>
-      </c>
+      <c r="B8" s="61"/>
       <c r="C8" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="D8" s="63" t="s">
-        <v>178</v>
-      </c>
-      <c r="E8" s="64" t="s">
-        <v>161</v>
-      </c>
-      <c r="F8" s="94" t="s">
+        <v>170</v>
+      </c>
+      <c r="D8" s="62" t="s">
+        <v>171</v>
+      </c>
+      <c r="E8" s="63" t="s">
+        <v>156</v>
+      </c>
+      <c r="F8" s="93" t="s">
         <v>29</v>
       </c>
-      <c r="G8" s="100" t="s">
+      <c r="G8" s="99" t="s">
         <v>49</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="I8" s="9">
-        <v>860</v>
-      </c>
-      <c r="J8" s="65" t="s">
+        <v>214</v>
+      </c>
+      <c r="I8" s="9"/>
+      <c r="J8" s="64" t="s">
         <v>65</v>
       </c>
-      <c r="K8" s="66"/>
-      <c r="L8" s="82" t="s">
+      <c r="K8" s="65"/>
+      <c r="L8" s="81" t="s">
         <v>66</v>
       </c>
     </row>
@@ -8522,35 +8483,33 @@
       <c r="A9" s="12">
         <v>37</v>
       </c>
-      <c r="B9" s="67" t="s">
-        <v>179</v>
+      <c r="B9" s="66" t="s">
+        <v>172</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="D9" s="68" t="s">
-        <v>181</v>
-      </c>
-      <c r="E9" s="69" t="s">
-        <v>85</v>
-      </c>
-      <c r="F9" s="94" t="s">
+        <v>173</v>
+      </c>
+      <c r="D9" s="67" t="s">
+        <v>174</v>
+      </c>
+      <c r="E9" s="68" t="s">
+        <v>84</v>
+      </c>
+      <c r="F9" s="93" t="s">
         <v>29</v>
       </c>
-      <c r="G9" s="100" t="s">
+      <c r="G9" s="99" t="s">
         <v>49</v>
       </c>
       <c r="H9" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="I9" s="18">
-        <v>120</v>
-      </c>
-      <c r="J9" s="65" t="s">
+      <c r="I9" s="18"/>
+      <c r="J9" s="64" t="s">
         <v>65</v>
       </c>
-      <c r="K9" s="71"/>
-      <c r="L9" s="82" t="s">
+      <c r="K9" s="70"/>
+      <c r="L9" s="81" t="s">
         <v>66</v>
       </c>
     </row>
@@ -8558,22 +8517,22 @@
       <c r="A10" s="3">
         <v>38</v>
       </c>
-      <c r="B10" s="62" t="s">
-        <v>182</v>
+      <c r="B10" s="61" t="s">
+        <v>215</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="D10" s="63" t="s">
-        <v>184</v>
-      </c>
-      <c r="E10" s="64" t="s">
-        <v>85</v>
-      </c>
-      <c r="F10" s="94" t="s">
+        <v>175</v>
+      </c>
+      <c r="D10" s="62" t="s">
+        <v>176</v>
+      </c>
+      <c r="E10" s="63" t="s">
+        <v>84</v>
+      </c>
+      <c r="F10" s="93" t="s">
         <v>29</v>
       </c>
-      <c r="G10" s="95" t="s">
+      <c r="G10" s="94" t="s">
         <v>42</v>
       </c>
       <c r="H10" s="8" t="s">
@@ -8582,11 +8541,11 @@
       <c r="I10" s="9">
         <v>175</v>
       </c>
-      <c r="J10" s="65" t="s">
-        <v>69</v>
-      </c>
-      <c r="K10" s="66"/>
-      <c r="L10" s="82" t="s">
+      <c r="J10" s="64" t="s">
+        <v>68</v>
+      </c>
+      <c r="K10" s="65"/>
+      <c r="L10" s="81" t="s">
         <v>66</v>
       </c>
     </row>
@@ -8594,35 +8553,33 @@
       <c r="A11" s="12">
         <v>39</v>
       </c>
-      <c r="B11" s="67" t="s">
-        <v>185</v>
+      <c r="B11" s="66" t="s">
+        <v>177</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>186</v>
-      </c>
-      <c r="D11" s="68" t="s">
-        <v>187</v>
-      </c>
-      <c r="E11" s="69" t="s">
-        <v>85</v>
-      </c>
-      <c r="F11" s="94" t="s">
+        <v>178</v>
+      </c>
+      <c r="D11" s="67" t="s">
+        <v>179</v>
+      </c>
+      <c r="E11" s="68" t="s">
+        <v>84</v>
+      </c>
+      <c r="F11" s="93" t="s">
         <v>29</v>
       </c>
-      <c r="G11" s="98" t="s">
+      <c r="G11" s="97" t="s">
         <v>51</v>
       </c>
       <c r="H11" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="I11" s="18">
-        <v>26</v>
-      </c>
-      <c r="J11" s="65" t="s">
+      <c r="I11" s="18"/>
+      <c r="J11" s="64" t="s">
         <v>65</v>
       </c>
-      <c r="K11" s="71"/>
-      <c r="L11" s="82" t="s">
+      <c r="K11" s="70"/>
+      <c r="L11" s="81" t="s">
         <v>66</v>
       </c>
     </row>
@@ -8630,35 +8587,33 @@
       <c r="A12" s="3">
         <v>40</v>
       </c>
-      <c r="B12" s="62" t="s">
-        <v>188</v>
+      <c r="B12" s="61" t="s">
+        <v>180</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="D12" s="63" t="s">
-        <v>190</v>
-      </c>
-      <c r="E12" s="64" t="s">
-        <v>85</v>
-      </c>
-      <c r="F12" s="94" t="s">
+        <v>181</v>
+      </c>
+      <c r="D12" s="62" t="s">
+        <v>182</v>
+      </c>
+      <c r="E12" s="63" t="s">
+        <v>84</v>
+      </c>
+      <c r="F12" s="93" t="s">
         <v>29</v>
       </c>
-      <c r="G12" s="98" t="s">
+      <c r="G12" s="97" t="s">
         <v>51</v>
       </c>
       <c r="H12" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I12" s="9">
-        <v>36</v>
-      </c>
-      <c r="J12" s="65" t="s">
+      <c r="I12" s="9"/>
+      <c r="J12" s="64" t="s">
         <v>65</v>
       </c>
-      <c r="K12" s="66"/>
-      <c r="L12" s="82" t="s">
+      <c r="K12" s="65"/>
+      <c r="L12" s="81" t="s">
         <v>66</v>
       </c>
     </row>
@@ -8666,35 +8621,33 @@
       <c r="A13" s="12">
         <v>41</v>
       </c>
-      <c r="B13" s="67" t="s">
-        <v>191</v>
+      <c r="B13" s="66" t="s">
+        <v>183</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>192</v>
-      </c>
-      <c r="D13" s="68" t="s">
-        <v>193</v>
-      </c>
-      <c r="E13" s="69" t="s">
-        <v>85</v>
-      </c>
-      <c r="F13" s="94" t="s">
+        <v>184</v>
+      </c>
+      <c r="D13" s="67" t="s">
+        <v>185</v>
+      </c>
+      <c r="E13" s="68" t="s">
+        <v>84</v>
+      </c>
+      <c r="F13" s="93" t="s">
         <v>29</v>
       </c>
-      <c r="G13" s="98" t="s">
+      <c r="G13" s="97" t="s">
         <v>51</v>
       </c>
       <c r="H13" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="I13" s="18">
-        <v>18</v>
-      </c>
-      <c r="J13" s="65" t="s">
+      <c r="I13" s="18"/>
+      <c r="J13" s="64" t="s">
         <v>65</v>
       </c>
-      <c r="K13" s="71"/>
-      <c r="L13" s="82" t="s">
+      <c r="K13" s="70"/>
+      <c r="L13" s="81" t="s">
         <v>66</v>
       </c>
     </row>
@@ -8702,35 +8655,33 @@
       <c r="A14" s="3">
         <v>42</v>
       </c>
-      <c r="B14" s="62" t="s">
-        <v>194</v>
+      <c r="B14" s="61" t="s">
+        <v>186</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="D14" s="63" t="s">
-        <v>196</v>
-      </c>
-      <c r="E14" s="64" t="s">
-        <v>85</v>
-      </c>
-      <c r="F14" s="94" t="s">
+        <v>187</v>
+      </c>
+      <c r="D14" s="62" t="s">
+        <v>188</v>
+      </c>
+      <c r="E14" s="63" t="s">
+        <v>84</v>
+      </c>
+      <c r="F14" s="93" t="s">
         <v>29</v>
       </c>
-      <c r="G14" s="98" t="s">
+      <c r="G14" s="97" t="s">
         <v>51</v>
       </c>
       <c r="H14" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I14" s="9">
-        <v>14</v>
-      </c>
-      <c r="J14" s="65" t="s">
+      <c r="I14" s="9"/>
+      <c r="J14" s="64" t="s">
         <v>65</v>
       </c>
-      <c r="K14" s="66"/>
-      <c r="L14" s="82" t="s">
+      <c r="K14" s="65"/>
+      <c r="L14" s="81" t="s">
         <v>66</v>
       </c>
     </row>
@@ -8738,55 +8689,53 @@
       <c r="A15" s="12">
         <v>43</v>
       </c>
-      <c r="B15" s="67" t="s">
-        <v>197</v>
+      <c r="B15" s="66" t="s">
+        <v>189</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>198</v>
-      </c>
-      <c r="D15" s="68" t="s">
-        <v>199</v>
-      </c>
-      <c r="E15" s="69" t="s">
-        <v>85</v>
-      </c>
-      <c r="F15" s="99" t="s">
+        <v>190</v>
+      </c>
+      <c r="D15" s="67" t="s">
+        <v>191</v>
+      </c>
+      <c r="E15" s="68" t="s">
+        <v>84</v>
+      </c>
+      <c r="F15" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="G15" s="99" t="s">
+      <c r="G15" s="98" t="s">
         <v>47</v>
       </c>
       <c r="H15" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="I15" s="18">
-        <v>30</v>
-      </c>
-      <c r="J15" s="65" t="s">
+      <c r="I15" s="18"/>
+      <c r="J15" s="64" t="s">
         <v>65</v>
       </c>
-      <c r="K15" s="71"/>
-      <c r="L15" s="82" t="s">
+      <c r="K15" s="70"/>
+      <c r="L15" s="81" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="137" t="s">
-        <v>86</v>
-      </c>
-      <c r="B16" s="122"/>
-      <c r="C16" s="122"/>
-      <c r="D16" s="122"/>
-      <c r="E16" s="122"/>
-      <c r="F16" s="122"/>
-      <c r="G16" s="122"/>
-      <c r="H16" s="128"/>
-      <c r="I16" s="117">
+      <c r="A16" s="130" t="s">
+        <v>85</v>
+      </c>
+      <c r="B16" s="115"/>
+      <c r="C16" s="115"/>
+      <c r="D16" s="115"/>
+      <c r="E16" s="115"/>
+      <c r="F16" s="115"/>
+      <c r="G16" s="115"/>
+      <c r="H16" s="121"/>
+      <c r="I16" s="107">
         <f>SUM(I6:I15)</f>
-        <v>1279</v>
-      </c>
-      <c r="J16" s="92"/>
-      <c r="K16" s="92"/>
+        <v>175</v>
+      </c>
+      <c r="J16" s="91"/>
+      <c r="K16" s="91"/>
     </row>
     <row r="17" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="23"/>
@@ -8809,60 +8758,60 @@
     <mergeCell ref="A1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="F6:F1000">
-    <cfRule type="cellIs" dxfId="22" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="24" operator="equal">
       <formula>"Согласовано"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="25" operator="equal">
       <formula>"Закрыто"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="26" operator="equal">
       <formula>"В работе"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="27" operator="equal">
       <formula>"На согласовании"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6:G1000">
-    <cfRule type="cellIs" dxfId="18" priority="28" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="28" operator="equal">
       <formula>"Ошибка"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="29" operator="equal">
       <formula>"Отменено"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G6:G1000">
-    <cfRule type="cellIs" dxfId="16" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="30" operator="equal">
       <formula>"Установлено"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="31" operator="equal">
       <formula>"Разработка"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="32" operator="equal">
       <formula>"Тестирование"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="33" operator="equal">
       <formula>"На приемке"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="34" operator="equal">
       <formula>"ОПЭ"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J6:J15">
-    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>"Нет"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
       <formula>"Да"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L6:L1000">
-    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>"Высокий"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
       <formula>"Средний"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
       <formula>"Низкий"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8914,51 +8863,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="139" t="s">
-        <v>200</v>
-      </c>
-      <c r="B1" s="120"/>
-      <c r="C1" s="120"/>
+      <c r="A1" s="132" t="s">
+        <v>192</v>
+      </c>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
     </row>
     <row r="2" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="73" t="s">
-        <v>201</v>
-      </c>
-      <c r="B2" s="73" t="s">
-        <v>202</v>
-      </c>
-      <c r="C2" s="73" t="s">
-        <v>203</v>
+      <c r="A2" s="72" t="s">
+        <v>193</v>
+      </c>
+      <c r="B2" s="72" t="s">
+        <v>194</v>
+      </c>
+      <c r="C2" s="72" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="75" t="s">
-        <v>204</v>
+      <c r="A3" s="74" t="s">
+        <v>196</v>
       </c>
       <c r="B3" s="11">
         <v>2026</v>
       </c>
-      <c r="C3" s="75"/>
+      <c r="C3" s="74"/>
     </row>
     <row r="4" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="74" t="s">
-        <v>205</v>
+      <c r="A4" s="73" t="s">
+        <v>197</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>206</v>
-      </c>
-      <c r="C4" s="74" t="s">
-        <v>207</v>
+        <v>198</v>
+      </c>
+      <c r="C4" s="73" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="75" t="s">
-        <v>208</v>
+      <c r="A5" s="74" t="s">
+        <v>200</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>209</v>
-      </c>
-      <c r="C5" s="75"/>
+        <v>201</v>
+      </c>
+      <c r="C5" s="74"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/registry.xlsx.xlsx
+++ b/registry.xlsx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\szamyatin\Desktop\Реестр\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F16DA1D-E666-4380-A9F6-9D49AD960423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{056FFEEE-FF45-40F6-B55B-DB71313504A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="960" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="960" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="📊 Дашборд" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="216">
   <si>
     <t>РЕЕСТР ЗАДАЧ АВТОМАТИЗАЦИИ СЦ СОЛВО 2026</t>
   </si>
@@ -202,9 +202,6 @@
   </si>
   <si>
     <t>Оценка</t>
-  </si>
-  <si>
-    <t>7.4.10/1</t>
   </si>
   <si>
     <t>Ожидает рассмотрения</t>
@@ -2969,7 +2966,7 @@
         <v>9</v>
       </c>
       <c r="F16" s="92" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G16" s="92" t="s">
         <v>10</v>
@@ -3141,7 +3138,7 @@
     </row>
     <row r="23" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="50" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B23" s="42">
         <f>COUNTIF('Судовые документы'!G6:G12,"Ожидает рассмотрения")+COUNTIF('Таможенные документы'!G6:G10,"Ожидает рассмотрения")+COUNTIF('Экспортные грузы'!G6:G10,"Ожидает рассмотрения")+COUNTIF(Терминал!G6:G21,"Ожидает рассмотрения")+COUNTIF('ЖД грузы'!G6:G15,"Ожидает рассмотрения")</f>
@@ -3153,22 +3150,22 @@
       </c>
       <c r="D23" s="23"/>
       <c r="E23" s="44" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F23" s="42">
-        <f>COUNTIF('Судовые документы'!H6:H12,"7.4.10/1")+COUNTIF('Таможенные документы'!H6:H10,"7.4.10/1")+COUNTIF('Экспортные грузы'!H6:H10,"7.4.10/1")+COUNTIF(Терминал!H6:H21,"7.4.10/1")+COUNTIF('ЖД грузы'!H6:H15,"7.4.10/1")</f>
-        <v>0</v>
+        <f>COUNTIF('Судовые документы'!H6:H12,"7.4.11")+COUNTIF('Таможенные документы'!H6:H10,"7.4.11")+COUNTIF('Экспортные грузы'!H6:H10,"7.4.11")+COUNTIF(Терминал!H6:H21,"7.4.11")+COUNTIF('ЖД грузы'!H6:H15,"7.4.11")</f>
+        <v>16</v>
       </c>
       <c r="G23" s="103">
-        <f>SUMIF('Судовые документы'!H6:H12,"7.4.10/1",'Судовые документы'!I6:I12)+SUMIF('Таможенные документы'!H6:H10,"7.4.10/1",'Таможенные документы'!I6:I10)+SUMIF('Экспортные грузы'!H6:H10,"7.4.10/1",'Экспортные грузы'!I6:I10)+SUMIF(Терминал!H6:H21,"7.4.10/1",Терминал!I6:I21)+SUMIF('ЖД грузы'!H6:H15,"7.4.10/1",'ЖД грузы'!I6:I15)</f>
-        <v>0</v>
+        <f>SUMIF('Судовые документы'!H6:H12,"7.4.11",'Судовые документы'!I6:I12)+SUMIF('Таможенные документы'!H6:H10,"7.4.11",'Таможенные документы'!I6:I10)+SUMIF('Экспортные грузы'!H6:H10,"7.4.11",'Экспортные грузы'!I6:I10)+SUMIF(Терминал!H6:H21,"7.4.11",Терминал!I6:I21)+SUMIF('ЖД грузы'!H6:H15,"7.4.11",'ЖД грузы'!I6:I15)</f>
+        <v>574</v>
       </c>
       <c r="H23" s="23"/>
       <c r="I23" s="23"/>
     </row>
     <row r="24" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="50" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B24" s="42">
         <f>COUNTIF('Судовые документы'!G6:G12,"Приостановлена")+COUNTIF('Таможенные документы'!G6:G10,"Приостановлена")+COUNTIF('Экспортные грузы'!G6:G10,"Приостановлена")+COUNTIF(Терминал!G6:G21,"Приостановлена")+COUNTIF('ЖД грузы'!G6:G15,"Приостановлена")</f>
@@ -3180,22 +3177,22 @@
       </c>
       <c r="D24" s="23"/>
       <c r="E24" s="44" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F24" s="42">
-        <f>COUNTIF('Судовые документы'!H6:H12,"7.4.11")+COUNTIF('Таможенные документы'!H6:H10,"7.4.11")+COUNTIF('Экспортные грузы'!H6:H10,"7.4.11")+COUNTIF(Терминал!H6:H21,"7.4.11")+COUNTIF('ЖД грузы'!H6:H15,"7.4.11")</f>
-        <v>16</v>
+        <f>COUNTIF('Судовые документы'!H6:H12,"7.4.12")+COUNTIF('Таможенные документы'!H6:H10,"7.4.12")+COUNTIF('Экспортные грузы'!H6:H10,"7.4.12")+COUNTIF(Терминал!H6:H21,"7.4.12")+COUNTIF('ЖД грузы'!H6:H15,"7.4.12")</f>
+        <v>0</v>
       </c>
       <c r="G24" s="103">
-        <f>SUMIF('Судовые документы'!H6:H12,"7.4.11",'Судовые документы'!I6:I12)+SUMIF('Таможенные документы'!H6:H10,"7.4.11",'Таможенные документы'!I6:I10)+SUMIF('Экспортные грузы'!H6:H10,"7.4.11",'Экспортные грузы'!I6:I10)+SUMIF(Терминал!H6:H21,"7.4.11",Терминал!I6:I21)+SUMIF('ЖД грузы'!H6:H15,"7.4.11",'ЖД грузы'!I6:I15)</f>
-        <v>574</v>
+        <f>SUMIF('Судовые документы'!H6:H12,"7.4.12",'Судовые документы'!I6:I12)+SUMIF('Таможенные документы'!H6:H10,"7.4.12",'Таможенные документы'!I6:I10)+SUMIF('Экспортные грузы'!H6:H10,"7.4.12",'Экспортные грузы'!I6:I10)+SUMIF(Терминал!H6:H21,"7.4.12",Терминал!I6:I21)+SUMIF('ЖД грузы'!H6:H15,"7.4.12",'ЖД грузы'!I6:I15)</f>
+        <v>0</v>
       </c>
       <c r="H24" s="23"/>
       <c r="I24" s="23"/>
     </row>
     <row r="25" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="45" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B25" s="42">
         <f>COUNTIF('Судовые документы'!G6:G12,"На приемке")+COUNTIF('Таможенные документы'!G6:G10,"На приемке")+COUNTIF('Экспортные грузы'!G6:G10,"На приемке")+COUNTIF(Терминал!G6:G21,"На приемке")+COUNTIF('ЖД грузы'!G6:G15,"На приемке")</f>
@@ -3207,14 +3204,14 @@
       </c>
       <c r="D25" s="23"/>
       <c r="E25" s="44" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F25" s="42">
-        <f>COUNTIF('Судовые документы'!H6:H12,"7.4.12")+COUNTIF('Таможенные документы'!H6:H10,"7.4.12")+COUNTIF('Экспортные грузы'!H6:H10,"7.4.12")+COUNTIF(Терминал!H6:H21,"7.4.12")+COUNTIF('ЖД грузы'!H6:H15,"7.4.12")</f>
-        <v>0</v>
+        <f>COUNTIF('Судовые документы'!H6:H12,"Не СОЛВО")+COUNTIF('Таможенные документы'!H6:H10,"Не СОЛВО")+COUNTIF('Экспортные грузы'!H6:H10,"Не СОЛВО")+COUNTIF(Терминал!H6:H21,"Не СОЛВО")+COUNTIF('ЖД грузы'!H6:H15,"Не СОЛВО")</f>
+        <v>2</v>
       </c>
       <c r="G25" s="103">
-        <f>SUMIF('Судовые документы'!H6:H12,"7.4.12",'Судовые документы'!I6:I12)+SUMIF('Таможенные документы'!H6:H10,"7.4.12",'Таможенные документы'!I6:I10)+SUMIF('Экспортные грузы'!H6:H10,"7.4.12",'Экспортные грузы'!I6:I10)+SUMIF(Терминал!H6:H21,"7.4.12",Терминал!I6:I21)+SUMIF('ЖД грузы'!H6:H15,"7.4.12",'ЖД грузы'!I6:I15)</f>
+        <f>SUMIF('Судовые документы'!H7:H13,"Не СОЛВО",'Судовые документы'!I7:I13)+SUMIF('Таможенные документы'!H7:H11,"Не СОЛВО",'Таможенные документы'!I7:I11)+SUMIF('Экспортные грузы'!H7:H11,"Не СОЛВО",'Экспортные грузы'!I7:I11)+SUMIF(Терминал!H7:H22,"Не СОЛВО",Терминал!I7:I22)+SUMIF('ЖД грузы'!H7:H16,"Не СОЛВО",'ЖД грузы'!I7:I16)</f>
         <v>0</v>
       </c>
       <c r="H25" s="23"/>
@@ -3222,7 +3219,7 @@
     </row>
     <row r="26" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="75" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B26" s="76">
         <f>COUNTIF('Судовые документы'!G6:G12,"Не СОЛВО")+COUNTIF('Таможенные документы'!G6:G10,"Не СОЛВО")+COUNTIF('Экспортные грузы'!G6:G10,"Не СОЛВО")+COUNTIF(Терминал!G6:G21,"Не СОЛВО")+COUNTIF('ЖД грузы'!G6:G15,"Не СОЛВО")</f>
@@ -3233,15 +3230,15 @@
         <v>4.6511627906976744E-2</v>
       </c>
       <c r="D26" s="23"/>
-      <c r="E26" s="44" t="s">
-        <v>56</v>
+      <c r="E26" s="142" t="s">
+        <v>213</v>
       </c>
       <c r="F26" s="42">
-        <f>COUNTIF('Судовые документы'!H6:H12,"Не СОЛВО")+COUNTIF('Таможенные документы'!H6:H10,"Не СОЛВО")+COUNTIF('Экспортные грузы'!H6:H10,"Не СОЛВО")+COUNTIF(Терминал!H6:H21,"Не СОЛВО")+COUNTIF('ЖД грузы'!H6:H15,"Не СОЛВО")</f>
-        <v>2</v>
+        <f>COUNTIF('Судовые документы'!H6:H12,"Н/Д")+COUNTIF('Таможенные документы'!H6:H10,"Н/Д")+COUNTIF('Экспортные грузы'!H6:H10,"Н/Д")+COUNTIF(Терминал!H6:H21,"Н/Д")+COUNTIF('ЖД грузы'!H6:H15,"Н/Д")</f>
+        <v>3</v>
       </c>
       <c r="G26" s="103">
-        <f>SUMIF('Судовые документы'!H7:H13,"Не СОЛВО",'Судовые документы'!I7:I13)+SUMIF('Таможенные документы'!H7:H11,"Не СОЛВО",'Таможенные документы'!I7:I11)+SUMIF('Экспортные грузы'!H7:H11,"Не СОЛВО",'Экспортные грузы'!I7:I11)+SUMIF(Терминал!H7:H22,"Не СОЛВО",Терминал!I7:I22)+SUMIF('ЖД грузы'!H7:H16,"Не СОЛВО",'ЖД грузы'!I7:I16)</f>
+        <f>SUMIF('Судовые документы'!H8:H14,"7.4.12",'Судовые документы'!I8:I14)+SUMIF('Таможенные документы'!H8:H12,"7.4.12",'Таможенные документы'!I8:I12)+SUMIF('Экспортные грузы'!H8:H12,"7.4.12",'Экспортные грузы'!I8:I12)+SUMIF(Терминал!H8:H23,"7.4.12",Терминал!I8:I23)+SUMIF('ЖД грузы'!H8:H17,"7.4.12",'ЖД грузы'!I8:I17)</f>
         <v>0</v>
       </c>
       <c r="H26" s="23"/>
@@ -3249,7 +3246,7 @@
     </row>
     <row r="27" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="75" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B27" s="76">
         <f>COUNTIF('Судовые документы'!H6:H12,"Н/Д")+COUNTIF('Таможенные документы'!H6:H10,"Н/Д")+COUNTIF('Экспортные грузы'!H6:H10,"Н/Д")+COUNTIF(Терминал!H6:H21,"Н/Д")+COUNTIF('ЖД грузы'!H6:H15,"Н/Д")</f>
@@ -3260,23 +3257,23 @@
         <v>6.9767441860465115E-2</v>
       </c>
       <c r="D27" s="23"/>
-      <c r="E27" s="142" t="s">
-        <v>214</v>
-      </c>
-      <c r="F27" s="42">
-        <f>COUNTIF('Судовые документы'!H6:H12,"Н/Д")+COUNTIF('Таможенные документы'!H6:H10,"Н/Д")+COUNTIF('Экспортные грузы'!H6:H10,"Н/Д")+COUNTIF(Терминал!H6:H21,"Н/Д")+COUNTIF('ЖД грузы'!H6:H15,"Н/Д")</f>
-        <v>3</v>
-      </c>
-      <c r="G27" s="103">
-        <f>SUMIF('Судовые документы'!H8:H14,"7.4.12",'Судовые документы'!I8:I14)+SUMIF('Таможенные документы'!H8:H12,"7.4.12",'Таможенные документы'!I8:I12)+SUMIF('Экспортные грузы'!H8:H12,"7.4.12",'Экспортные грузы'!I8:I12)+SUMIF(Терминал!H8:H23,"7.4.12",Терминал!I8:I23)+SUMIF('ЖД грузы'!H8:H17,"7.4.12",'ЖД грузы'!I8:I17)</f>
-        <v>0</v>
+      <c r="E27" s="78" t="s">
+        <v>56</v>
+      </c>
+      <c r="F27" s="79">
+        <f>IFERROR(SUM(F17:F26),"0")</f>
+        <v>43</v>
+      </c>
+      <c r="G27" s="101">
+        <f>IFERROR(SUM(G17:G25),"0")</f>
+        <v>3231</v>
       </c>
       <c r="H27" s="23"/>
       <c r="I27" s="23"/>
     </row>
     <row r="28" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="78" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B28" s="79">
         <f>IFERROR(SUM(B16:B27),"0")</f>
@@ -3287,23 +3284,12 @@
         <v>1.0232558139534884</v>
       </c>
       <c r="D28" s="23"/>
-      <c r="E28" s="78" t="s">
-        <v>57</v>
-      </c>
-      <c r="F28" s="79">
-        <f>IFERROR(SUM(F17:F27),"0")</f>
-        <v>43</v>
-      </c>
-      <c r="G28" s="101">
-        <f>IFERROR(SUM(G17:G26),"0")</f>
-        <v>3231</v>
-      </c>
       <c r="H28" s="23"/>
       <c r="I28" s="23"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="51" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B29" s="23"/>
       <c r="C29" s="23"/>
@@ -3350,7 +3336,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
@@ -3380,17 +3366,17 @@
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -3405,17 +3391,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -3434,13 +3420,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -3451,31 +3437,31 @@
         <v>45</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B3" t="s">
         <v>42</v>
       </c>
       <c r="C3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B5" t="s">
         <v>40</v>
@@ -3483,7 +3469,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B6" t="s">
         <v>38</v>
@@ -3491,15 +3477,15 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
   </sheetData>
@@ -3954,7 +3940,7 @@
         <v>Обработка на т/х порожних контейнеров (каботаж)</v>
       </c>
       <c r="D11" s="136" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E11" s="137">
         <v>2026</v>
@@ -3966,19 +3952,19 @@
         <v>47</v>
       </c>
       <c r="H11" s="138" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I11" s="139">
         <v>0</v>
       </c>
       <c r="J11" s="137" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K11" s="140" t="s">
         <v>16</v>
       </c>
       <c r="L11" s="141" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M11" s="137">
         <f>IFERROR(IF(K11="Обработка судовых документов",INDEX('Судовые документы'!K:K,MATCH(A11,'Судовые документы'!A:A,0)),IF(K11="Оформление таможенных документов",INDEX('Таможенные документы'!K:K,MATCH(A11,'Таможенные документы'!A:A,0)),IF(K11="Оформление экспортных грузов",INDEX('Экспортные грузы'!K:K,MATCH(A11,'Экспортные грузы'!A:A,0)),IF(K11="Терминальные операции",INDEX(Терминал!K:K,MATCH(A11,Терминал!A:A,0)),IF(K11="Документальное оформление ЖД грузов",INDEX('ЖД грузы'!K:K,MATCH(A11,'ЖД грузы'!A:A,0)),""))))),"")</f>
@@ -5985,7 +5971,7 @@
       <c r="M52" s="21"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1" sort="0" autoFilter="0" selectUnlockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="hT6i0hk5giw6TRLaKRPJZMajl9a7IMuMCxbJShzOKHbpGmN/xI/xjcsGDMsgxjezd6WKWnaqqYydlKZP1ta6dA==" saltValue="YpkI3Wrm47mHu6ypbemddA==" spinCount="100000" sheet="1" selectLockedCells="1" sort="0" autoFilter="0" selectUnlockedCells="1"/>
   <autoFilter ref="A3:M52" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="8">
     <mergeCell ref="A2:M2"/>
@@ -6025,7 +6011,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="125" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B1" s="113"/>
       <c r="C1" s="113"/>
@@ -6041,7 +6027,7 @@
     </row>
     <row r="2" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="123" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B2" s="113"/>
       <c r="C2" s="113"/>
@@ -6147,16 +6133,16 @@
         <v>1</v>
       </c>
       <c r="B6" s="61" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="62" t="s">
         <v>62</v>
       </c>
-      <c r="D6" s="62" t="s">
+      <c r="E6" s="63" t="s">
         <v>63</v>
-      </c>
-      <c r="E6" s="63" t="s">
-        <v>64</v>
       </c>
       <c r="F6" s="93" t="s">
         <v>29</v>
@@ -6171,11 +6157,11 @@
         <v>235</v>
       </c>
       <c r="J6" s="64" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K6" s="65"/>
       <c r="L6" s="81" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6186,16 +6172,16 @@
         <v>3323631</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D7" s="67" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E7" s="68" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F7" s="93" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G7" s="94" t="s">
         <v>42</v>
@@ -6205,11 +6191,11 @@
       </c>
       <c r="I7" s="18"/>
       <c r="J7" s="69" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K7" s="70"/>
       <c r="L7" s="82" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6217,13 +6203,13 @@
         <v>3</v>
       </c>
       <c r="B8" s="61" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="D8" s="62" t="s">
         <v>70</v>
-      </c>
-      <c r="D8" s="62" t="s">
-        <v>71</v>
       </c>
       <c r="E8" s="63" t="s">
         <v>40</v>
@@ -6241,11 +6227,11 @@
         <v>144</v>
       </c>
       <c r="J8" s="64" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K8" s="65"/>
       <c r="L8" s="81" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6253,22 +6239,22 @@
         <v>4</v>
       </c>
       <c r="B9" s="66" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="D9" s="67" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="67" t="s">
+      <c r="E9" s="68" t="s">
         <v>74</v>
-      </c>
-      <c r="E9" s="68" t="s">
-        <v>75</v>
       </c>
       <c r="F9" s="96" t="s">
         <v>28</v>
       </c>
       <c r="G9" s="97" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H9" s="44" t="s">
         <v>41</v>
@@ -6277,11 +6263,11 @@
         <v>110</v>
       </c>
       <c r="J9" s="69" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K9" s="70"/>
       <c r="L9" s="82" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6290,30 +6276,30 @@
       </c>
       <c r="B10" s="61"/>
       <c r="C10" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D10" s="62" t="s">
         <v>76</v>
       </c>
-      <c r="D10" s="62" t="s">
-        <v>77</v>
-      </c>
       <c r="E10" s="63" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F10" s="96" t="s">
         <v>28</v>
       </c>
       <c r="G10" s="97" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I10" s="9"/>
       <c r="J10" s="64" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K10" s="65"/>
       <c r="L10" s="81" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6321,16 +6307,16 @@
         <v>6</v>
       </c>
       <c r="B11" s="66" t="s">
+        <v>77</v>
+      </c>
+      <c r="C11" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="D11" s="67" t="s">
         <v>79</v>
       </c>
-      <c r="D11" s="67" t="s">
-        <v>80</v>
-      </c>
       <c r="E11" s="68" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F11" s="93" t="s">
         <v>29</v>
@@ -6345,11 +6331,11 @@
         <v>24</v>
       </c>
       <c r="J11" s="69" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K11" s="70"/>
       <c r="L11" s="82" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6357,13 +6343,13 @@
         <v>7</v>
       </c>
       <c r="B12" s="61" t="s">
+        <v>80</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="D12" s="62" t="s">
         <v>82</v>
-      </c>
-      <c r="D12" s="62" t="s">
-        <v>83</v>
       </c>
       <c r="E12" s="63">
         <v>2026</v>
@@ -6375,20 +6361,20 @@
         <v>47</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I12" s="9"/>
       <c r="J12" s="71" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K12" s="65"/>
       <c r="L12" s="81" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="124" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B13" s="115"/>
       <c r="C13" s="115"/>
@@ -6542,7 +6528,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="127" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B1" s="113"/>
       <c r="C1" s="113"/>
@@ -6558,7 +6544,7 @@
     </row>
     <row r="2" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="123" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B2" s="113"/>
       <c r="C2" s="113"/>
@@ -6664,16 +6650,16 @@
         <v>8</v>
       </c>
       <c r="B6" s="61" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="62" t="s">
         <v>88</v>
       </c>
-      <c r="D6" s="62" t="s">
-        <v>89</v>
-      </c>
       <c r="E6" s="63" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F6" s="93" t="s">
         <v>29</v>
@@ -6688,11 +6674,11 @@
         <v>780</v>
       </c>
       <c r="J6" s="64" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K6" s="65"/>
       <c r="L6" s="81" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6700,16 +6686,16 @@
         <v>9</v>
       </c>
       <c r="B7" s="66" t="s">
+        <v>90</v>
+      </c>
+      <c r="C7" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="D7" s="67" t="s">
         <v>92</v>
       </c>
-      <c r="D7" s="67" t="s">
-        <v>93</v>
-      </c>
       <c r="E7" s="68" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F7" s="93" t="s">
         <v>29</v>
@@ -6718,15 +6704,15 @@
         <v>47</v>
       </c>
       <c r="H7" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I7" s="18"/>
       <c r="J7" s="64" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K7" s="70"/>
       <c r="L7" s="81" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6734,16 +6720,16 @@
         <v>10</v>
       </c>
       <c r="B8" s="61" t="s">
+        <v>93</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="D8" s="62" t="s">
         <v>95</v>
       </c>
-      <c r="D8" s="62" t="s">
-        <v>96</v>
-      </c>
       <c r="E8" s="63" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F8" s="93" t="s">
         <v>29</v>
@@ -6752,15 +6738,15 @@
         <v>47</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I8" s="9"/>
       <c r="J8" s="64" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K8" s="65"/>
       <c r="L8" s="81" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6768,16 +6754,16 @@
         <v>11</v>
       </c>
       <c r="B9" s="66" t="s">
+        <v>96</v>
+      </c>
+      <c r="C9" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="D9" s="67" t="s">
         <v>98</v>
       </c>
-      <c r="D9" s="67" t="s">
-        <v>99</v>
-      </c>
       <c r="E9" s="68" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F9" s="93" t="s">
         <v>29</v>
@@ -6786,15 +6772,15 @@
         <v>47</v>
       </c>
       <c r="H9" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I9" s="18"/>
       <c r="J9" s="64" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K9" s="70"/>
       <c r="L9" s="81" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6803,13 +6789,13 @@
       </c>
       <c r="B10" s="61"/>
       <c r="C10" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D10" s="62" t="s">
         <v>100</v>
       </c>
-      <c r="D10" s="62" t="s">
-        <v>101</v>
-      </c>
       <c r="E10" s="63" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F10" s="93" t="s">
         <v>29</v>
@@ -6818,20 +6804,20 @@
         <v>47</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I10" s="9"/>
       <c r="J10" s="64" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K10" s="65"/>
       <c r="L10" s="81" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="126" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B11" s="115"/>
       <c r="C11" s="115"/>
@@ -6982,7 +6968,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="125" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B1" s="113"/>
       <c r="C1" s="113"/>
@@ -6998,7 +6984,7 @@
     </row>
     <row r="2" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="123" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B2" s="113"/>
       <c r="C2" s="113"/>
@@ -7104,16 +7090,16 @@
         <v>13</v>
       </c>
       <c r="B6" s="61" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C6" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D6" s="62" t="s">
         <v>103</v>
       </c>
-      <c r="D6" s="62" t="s">
-        <v>104</v>
-      </c>
       <c r="E6" s="63" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F6" s="95" t="s">
         <v>40</v>
@@ -7126,11 +7112,11 @@
       </c>
       <c r="I6" s="9"/>
       <c r="J6" s="64" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K6" s="65"/>
       <c r="L6" s="81" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7138,16 +7124,16 @@
         <v>14</v>
       </c>
       <c r="B7" s="66" t="s">
+        <v>104</v>
+      </c>
+      <c r="C7" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="D7" s="67" t="s">
         <v>106</v>
       </c>
-      <c r="D7" s="67" t="s">
-        <v>107</v>
-      </c>
       <c r="E7" s="68" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F7" s="93" t="s">
         <v>29</v>
@@ -7162,11 +7148,11 @@
         <v>340</v>
       </c>
       <c r="J7" s="64" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K7" s="70"/>
       <c r="L7" s="81" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7174,16 +7160,16 @@
         <v>15</v>
       </c>
       <c r="B8" s="61" t="s">
+        <v>107</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="D8" s="62" t="s">
         <v>109</v>
       </c>
-      <c r="D8" s="62" t="s">
-        <v>110</v>
-      </c>
       <c r="E8" s="63" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F8" s="96" t="s">
         <v>28</v>
@@ -7196,11 +7182,11 @@
       </c>
       <c r="I8" s="9"/>
       <c r="J8" s="64" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K8" s="65"/>
       <c r="L8" s="81" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7208,16 +7194,16 @@
         <v>16</v>
       </c>
       <c r="B9" s="66" t="s">
+        <v>110</v>
+      </c>
+      <c r="C9" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="D9" s="67" t="s">
         <v>112</v>
       </c>
-      <c r="D9" s="67" t="s">
-        <v>113</v>
-      </c>
       <c r="E9" s="68" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F9" s="94" t="s">
         <v>42</v>
@@ -7232,11 +7218,11 @@
         <v>192</v>
       </c>
       <c r="J9" s="64" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K9" s="70"/>
       <c r="L9" s="81" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7244,38 +7230,38 @@
         <v>17</v>
       </c>
       <c r="B10" s="61" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C10" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="D10" s="62" t="s">
         <v>114</v>
       </c>
-      <c r="D10" s="62" t="s">
-        <v>115</v>
-      </c>
       <c r="E10" s="63" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F10" s="97" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G10" s="97" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I10" s="9"/>
       <c r="J10" s="64" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K10" s="65"/>
       <c r="L10" s="81" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="124" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B11" s="115"/>
       <c r="C11" s="115"/>
@@ -7426,7 +7412,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="128" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B1" s="113"/>
       <c r="C1" s="113"/>
@@ -7442,7 +7428,7 @@
     </row>
     <row r="2" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="123" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B2" s="113"/>
       <c r="C2" s="113"/>
@@ -7548,33 +7534,33 @@
         <v>18</v>
       </c>
       <c r="B6" s="61" t="s">
+        <v>116</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="62" t="s">
         <v>118</v>
       </c>
-      <c r="D6" s="62" t="s">
-        <v>119</v>
-      </c>
       <c r="E6" s="63" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F6" s="93" t="s">
         <v>29</v>
       </c>
       <c r="G6" s="97" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I6" s="9"/>
       <c r="J6" s="64" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K6" s="65"/>
       <c r="L6" s="81" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7582,22 +7568,22 @@
         <v>19</v>
       </c>
       <c r="B7" s="66" t="s">
+        <v>119</v>
+      </c>
+      <c r="C7" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="D7" s="67" t="s">
         <v>121</v>
       </c>
-      <c r="D7" s="67" t="s">
-        <v>122</v>
-      </c>
       <c r="E7" s="68" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F7" s="96" t="s">
         <v>28</v>
       </c>
       <c r="G7" s="96" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H7" s="17" t="s">
         <v>44</v>
@@ -7606,11 +7592,11 @@
         <v>70</v>
       </c>
       <c r="J7" s="64" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K7" s="70"/>
       <c r="L7" s="81" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7618,13 +7604,13 @@
         <v>20</v>
       </c>
       <c r="B8" s="61" t="s">
+        <v>122</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="D8" s="62" t="s">
         <v>124</v>
-      </c>
-      <c r="D8" s="62" t="s">
-        <v>125</v>
       </c>
       <c r="E8" s="63" t="s">
         <v>40</v>
@@ -7642,11 +7628,11 @@
         <v>96</v>
       </c>
       <c r="J8" s="64" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K8" s="65"/>
       <c r="L8" s="81" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7654,16 +7640,16 @@
         <v>21</v>
       </c>
       <c r="B9" s="66" t="s">
+        <v>125</v>
+      </c>
+      <c r="C9" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="D9" s="67" t="s">
         <v>127</v>
       </c>
-      <c r="D9" s="67" t="s">
-        <v>128</v>
-      </c>
       <c r="E9" s="68" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F9" s="93" t="s">
         <v>29</v>
@@ -7672,17 +7658,17 @@
         <v>49</v>
       </c>
       <c r="H9" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I9" s="18">
         <v>320</v>
       </c>
       <c r="J9" s="64" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K9" s="70"/>
       <c r="L9" s="81" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7690,13 +7676,13 @@
         <v>22</v>
       </c>
       <c r="B10" s="61" t="s">
+        <v>128</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="D10" s="62" t="s">
         <v>130</v>
-      </c>
-      <c r="D10" s="62" t="s">
-        <v>131</v>
       </c>
       <c r="E10" s="63" t="s">
         <v>40</v>
@@ -7714,11 +7700,11 @@
         <v>23</v>
       </c>
       <c r="J10" s="64" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K10" s="65"/>
       <c r="L10" s="81" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7726,16 +7712,16 @@
         <v>23</v>
       </c>
       <c r="B11" s="66" t="s">
+        <v>131</v>
+      </c>
+      <c r="C11" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="D11" s="67" t="s">
         <v>133</v>
       </c>
-      <c r="D11" s="67" t="s">
-        <v>134</v>
-      </c>
       <c r="E11" s="68" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F11" s="96" t="s">
         <v>28</v>
@@ -7750,11 +7736,11 @@
         <v>60</v>
       </c>
       <c r="J11" s="64" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K11" s="70"/>
       <c r="L11" s="81" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7762,16 +7748,16 @@
         <v>24</v>
       </c>
       <c r="B12" s="61" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C12" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="D12" s="62" t="s">
         <v>135</v>
       </c>
-      <c r="D12" s="62" t="s">
-        <v>136</v>
-      </c>
       <c r="E12" s="63" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F12" s="96" t="s">
         <v>28</v>
@@ -7786,11 +7772,11 @@
         <v>20</v>
       </c>
       <c r="J12" s="64" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K12" s="65"/>
       <c r="L12" s="81" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7798,33 +7784,33 @@
         <v>25</v>
       </c>
       <c r="B13" s="66" t="s">
+        <v>136</v>
+      </c>
+      <c r="C13" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="D13" s="67" t="s">
         <v>138</v>
       </c>
-      <c r="D13" s="67" t="s">
-        <v>139</v>
-      </c>
       <c r="E13" s="68" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F13" s="93" t="s">
         <v>29</v>
       </c>
       <c r="G13" s="97" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H13" s="17" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I13" s="18"/>
       <c r="J13" s="64" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K13" s="70"/>
       <c r="L13" s="81" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7832,33 +7818,33 @@
         <v>26</v>
       </c>
       <c r="B14" s="61" t="s">
+        <v>139</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="D14" s="62" t="s">
         <v>141</v>
       </c>
-      <c r="D14" s="62" t="s">
-        <v>142</v>
-      </c>
       <c r="E14" s="63" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F14" s="96" t="s">
         <v>28</v>
       </c>
       <c r="G14" s="97" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I14" s="9"/>
       <c r="J14" s="64" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K14" s="65"/>
       <c r="L14" s="81" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7866,13 +7852,13 @@
         <v>27</v>
       </c>
       <c r="B15" s="66" t="s">
+        <v>142</v>
+      </c>
+      <c r="C15" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="D15" s="67" t="s">
         <v>144</v>
-      </c>
-      <c r="D15" s="67" t="s">
-        <v>145</v>
       </c>
       <c r="E15" s="68" t="s">
         <v>40</v>
@@ -7890,11 +7876,11 @@
         <v>140</v>
       </c>
       <c r="J15" s="64" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K15" s="70"/>
       <c r="L15" s="81" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7902,13 +7888,13 @@
         <v>28</v>
       </c>
       <c r="B16" s="61" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C16" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="D16" s="62" t="s">
         <v>146</v>
-      </c>
-      <c r="D16" s="62" t="s">
-        <v>147</v>
       </c>
       <c r="E16" s="63" t="s">
         <v>40</v>
@@ -7924,11 +7910,11 @@
       </c>
       <c r="I16" s="9"/>
       <c r="J16" s="64" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K16" s="65"/>
       <c r="L16" s="81" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7936,16 +7922,16 @@
         <v>29</v>
       </c>
       <c r="B17" s="66" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C17" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="D17" s="67" t="s">
         <v>148</v>
       </c>
-      <c r="D17" s="67" t="s">
-        <v>149</v>
-      </c>
       <c r="E17" s="68" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F17" s="93" t="s">
         <v>29</v>
@@ -7960,11 +7946,11 @@
         <v>8</v>
       </c>
       <c r="J17" s="64" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K17" s="70"/>
       <c r="L17" s="81" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7972,13 +7958,13 @@
         <v>30</v>
       </c>
       <c r="B18" s="61" t="s">
+        <v>149</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="D18" s="62" t="s">
         <v>151</v>
-      </c>
-      <c r="D18" s="62" t="s">
-        <v>152</v>
       </c>
       <c r="E18" s="63" t="s">
         <v>40</v>
@@ -7996,11 +7982,11 @@
         <v>130</v>
       </c>
       <c r="J18" s="64" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K18" s="65"/>
       <c r="L18" s="81" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -8008,16 +7994,16 @@
         <v>31</v>
       </c>
       <c r="B19" s="66" t="s">
+        <v>152</v>
+      </c>
+      <c r="C19" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="C19" s="14" t="s">
+      <c r="D19" s="67" t="s">
         <v>154</v>
       </c>
-      <c r="D19" s="67" t="s">
-        <v>155</v>
-      </c>
       <c r="E19" s="68" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F19" s="93" t="s">
         <v>29</v>
@@ -8026,15 +8012,15 @@
         <v>47</v>
       </c>
       <c r="H19" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I19" s="18"/>
       <c r="J19" s="64" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K19" s="70"/>
       <c r="L19" s="81" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -8042,16 +8028,16 @@
         <v>32</v>
       </c>
       <c r="B20" s="61" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C20" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="D20" s="62" t="s">
         <v>157</v>
       </c>
-      <c r="D20" s="62" t="s">
-        <v>158</v>
-      </c>
       <c r="E20" s="63" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F20" s="93" t="s">
         <v>29</v>
@@ -8066,11 +8052,11 @@
         <v>110</v>
       </c>
       <c r="J20" s="64" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K20" s="65"/>
       <c r="L20" s="81" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -8078,16 +8064,16 @@
         <v>33</v>
       </c>
       <c r="B21" s="66" t="s">
+        <v>158</v>
+      </c>
+      <c r="C21" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="C21" s="14" t="s">
+      <c r="D21" s="67" t="s">
         <v>160</v>
       </c>
-      <c r="D21" s="67" t="s">
-        <v>161</v>
-      </c>
       <c r="E21" s="68" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F21" s="93" t="s">
         <v>29</v>
@@ -8096,22 +8082,22 @@
         <v>49</v>
       </c>
       <c r="H21" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I21" s="18">
         <v>254</v>
       </c>
       <c r="J21" s="64" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K21" s="70"/>
       <c r="L21" s="81" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="129" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B22" s="115"/>
       <c r="C22" s="115"/>
@@ -8262,7 +8248,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="131" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B1" s="113"/>
       <c r="C1" s="113"/>
@@ -8278,7 +8264,7 @@
     </row>
     <row r="2" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="123" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B2" s="113"/>
       <c r="C2" s="113"/>
@@ -8384,16 +8370,16 @@
         <v>34</v>
       </c>
       <c r="B6" s="61" t="s">
+        <v>162</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="62" t="s">
         <v>164</v>
       </c>
-      <c r="D6" s="62" t="s">
-        <v>165</v>
-      </c>
       <c r="E6" s="63" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F6" s="96" t="s">
         <v>28</v>
@@ -8406,11 +8392,11 @@
       </c>
       <c r="I6" s="9"/>
       <c r="J6" s="64" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K6" s="65"/>
       <c r="L6" s="81" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -8418,16 +8404,16 @@
         <v>35</v>
       </c>
       <c r="B7" s="66" t="s">
+        <v>165</v>
+      </c>
+      <c r="C7" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="D7" s="67" t="s">
         <v>167</v>
       </c>
-      <c r="D7" s="67" t="s">
+      <c r="E7" s="68" t="s">
         <v>168</v>
-      </c>
-      <c r="E7" s="68" t="s">
-        <v>169</v>
       </c>
       <c r="F7" s="93" t="s">
         <v>29</v>
@@ -8436,15 +8422,15 @@
         <v>47</v>
       </c>
       <c r="H7" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I7" s="18"/>
       <c r="J7" s="64" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K7" s="70"/>
       <c r="L7" s="81" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -8453,13 +8439,13 @@
       </c>
       <c r="B8" s="61"/>
       <c r="C8" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="D8" s="62" t="s">
         <v>170</v>
       </c>
-      <c r="D8" s="62" t="s">
-        <v>171</v>
-      </c>
       <c r="E8" s="63" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F8" s="93" t="s">
         <v>29</v>
@@ -8468,15 +8454,15 @@
         <v>49</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I8" s="9"/>
       <c r="J8" s="64" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K8" s="65"/>
       <c r="L8" s="81" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -8484,16 +8470,16 @@
         <v>37</v>
       </c>
       <c r="B9" s="66" t="s">
+        <v>171</v>
+      </c>
+      <c r="C9" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="D9" s="67" t="s">
         <v>173</v>
       </c>
-      <c r="D9" s="67" t="s">
-        <v>174</v>
-      </c>
       <c r="E9" s="68" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F9" s="93" t="s">
         <v>29</v>
@@ -8502,15 +8488,15 @@
         <v>49</v>
       </c>
       <c r="H9" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I9" s="18"/>
       <c r="J9" s="64" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K9" s="70"/>
       <c r="L9" s="81" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -8518,16 +8504,16 @@
         <v>38</v>
       </c>
       <c r="B10" s="61" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C10" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="D10" s="62" t="s">
         <v>175</v>
       </c>
-      <c r="D10" s="62" t="s">
-        <v>176</v>
-      </c>
       <c r="E10" s="63" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F10" s="93" t="s">
         <v>29</v>
@@ -8542,11 +8528,11 @@
         <v>175</v>
       </c>
       <c r="J10" s="64" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K10" s="65"/>
       <c r="L10" s="81" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -8554,33 +8540,33 @@
         <v>39</v>
       </c>
       <c r="B11" s="66" t="s">
+        <v>176</v>
+      </c>
+      <c r="C11" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="D11" s="67" t="s">
         <v>178</v>
       </c>
-      <c r="D11" s="67" t="s">
-        <v>179</v>
-      </c>
       <c r="E11" s="68" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F11" s="93" t="s">
         <v>29</v>
       </c>
       <c r="G11" s="97" t="s">
+        <v>50</v>
+      </c>
+      <c r="H11" s="17" t="s">
         <v>51</v>
-      </c>
-      <c r="H11" s="17" t="s">
-        <v>52</v>
       </c>
       <c r="I11" s="18"/>
       <c r="J11" s="64" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K11" s="70"/>
       <c r="L11" s="81" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -8588,33 +8574,33 @@
         <v>40</v>
       </c>
       <c r="B12" s="61" t="s">
+        <v>179</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="D12" s="62" t="s">
         <v>181</v>
       </c>
-      <c r="D12" s="62" t="s">
-        <v>182</v>
-      </c>
       <c r="E12" s="63" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F12" s="93" t="s">
         <v>29</v>
       </c>
       <c r="G12" s="97" t="s">
+        <v>50</v>
+      </c>
+      <c r="H12" s="8" t="s">
         <v>51</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>52</v>
       </c>
       <c r="I12" s="9"/>
       <c r="J12" s="64" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K12" s="65"/>
       <c r="L12" s="81" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -8622,33 +8608,33 @@
         <v>41</v>
       </c>
       <c r="B13" s="66" t="s">
+        <v>182</v>
+      </c>
+      <c r="C13" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="D13" s="67" t="s">
         <v>184</v>
       </c>
-      <c r="D13" s="67" t="s">
-        <v>185</v>
-      </c>
       <c r="E13" s="68" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F13" s="93" t="s">
         <v>29</v>
       </c>
       <c r="G13" s="97" t="s">
+        <v>50</v>
+      </c>
+      <c r="H13" s="17" t="s">
         <v>51</v>
-      </c>
-      <c r="H13" s="17" t="s">
-        <v>52</v>
       </c>
       <c r="I13" s="18"/>
       <c r="J13" s="64" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K13" s="70"/>
       <c r="L13" s="81" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -8656,33 +8642,33 @@
         <v>42</v>
       </c>
       <c r="B14" s="61" t="s">
+        <v>185</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="D14" s="62" t="s">
         <v>187</v>
       </c>
-      <c r="D14" s="62" t="s">
-        <v>188</v>
-      </c>
       <c r="E14" s="63" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F14" s="93" t="s">
         <v>29</v>
       </c>
       <c r="G14" s="97" t="s">
+        <v>50</v>
+      </c>
+      <c r="H14" s="8" t="s">
         <v>51</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>52</v>
       </c>
       <c r="I14" s="9"/>
       <c r="J14" s="64" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K14" s="65"/>
       <c r="L14" s="81" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -8690,16 +8676,16 @@
         <v>43</v>
       </c>
       <c r="B15" s="66" t="s">
+        <v>188</v>
+      </c>
+      <c r="C15" s="14" t="s">
         <v>189</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="D15" s="67" t="s">
         <v>190</v>
       </c>
-      <c r="D15" s="67" t="s">
-        <v>191</v>
-      </c>
       <c r="E15" s="68" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F15" s="98" t="s">
         <v>47</v>
@@ -8708,20 +8694,20 @@
         <v>47</v>
       </c>
       <c r="H15" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I15" s="18"/>
       <c r="J15" s="64" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K15" s="70"/>
       <c r="L15" s="81" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="130" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B16" s="115"/>
       <c r="C16" s="115"/>
@@ -8864,25 +8850,25 @@
   <sheetData>
     <row r="1" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="132" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B1" s="113"/>
       <c r="C1" s="113"/>
     </row>
     <row r="2" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="72" t="s">
+        <v>192</v>
+      </c>
+      <c r="B2" s="72" t="s">
         <v>193</v>
       </c>
-      <c r="B2" s="72" t="s">
+      <c r="C2" s="72" t="s">
         <v>194</v>
-      </c>
-      <c r="C2" s="72" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="74" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B3" s="11">
         <v>2026</v>
@@ -8891,21 +8877,21 @@
     </row>
     <row r="4" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="73" t="s">
+        <v>196</v>
+      </c>
+      <c r="B4" s="20" t="s">
         <v>197</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="C4" s="73" t="s">
         <v>198</v>
-      </c>
-      <c r="C4" s="73" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="74" t="s">
+        <v>199</v>
+      </c>
+      <c r="B5" s="11" t="s">
         <v>200</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>201</v>
       </c>
       <c r="C5" s="74"/>
     </row>
@@ -8948,7 +8934,7 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
